--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -1281,6 +1281,15 @@
   </x:si>
   <x:si>
     <x:t>VAN HOLLEN FOR CONGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VEASEY, MARC ALLISON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00506832</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARC VEASEY CONGRESSIONAL CAMPAIGN COMMITTEE</x:t>
   </x:si>
   <x:si>
     <x:t>VUKMIR, LEAH</x:t>
@@ -1490,8 +1499,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G206" totalsRowShown="0">
-  <x:autoFilter ref="A1:G206"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G207" totalsRowShown="0">
+  <x:autoFilter ref="A1:G207"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1506,8 +1515,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H154" totalsRowShown="0">
-  <x:autoFilter ref="A1:H154"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H155" totalsRowShown="0">
+  <x:autoFilter ref="A1:H155"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1810,7 +1819,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G206"/>
+  <x:dimension ref="A1:G207"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3427,7 +3436,7 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>-575</x:v>
+        <x:v>-1700</x:v>
       </x:c>
       <x:c r="G70" s="2">
         <x:v>45349</x:v>
@@ -3450,7 +3459,7 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>-200</x:v>
+        <x:v>-575</x:v>
       </x:c>
       <x:c r="G71" s="2">
         <x:v>45349</x:v>
@@ -3473,7 +3482,7 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>-1700</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G72" s="2">
         <x:v>45349</x:v>
@@ -6037,10 +6046,10 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="B184" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
         <x:v>423</x:v>
@@ -6049,10 +6058,10 @@
         <x:v>424</x:v>
       </x:c>
       <x:c r="F184" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G184" s="2">
-        <x:v>43465</x:v>
+        <x:v>46000</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:7">
@@ -6060,10 +6069,10 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B185" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
         <x:v>426</x:v>
@@ -6072,10 +6081,10 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F185" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G185" s="2">
-        <x:v>44845</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:7">
@@ -6083,10 +6092,10 @@
         <x:v>428</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
         <x:v>429</x:v>
@@ -6095,10 +6104,10 @@
         <x:v>430</x:v>
       </x:c>
       <x:c r="F186" s="1">
-        <x:v>-300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G186" s="2">
-        <x:v>44645</x:v>
+        <x:v>44845</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:7">
@@ -6106,10 +6115,10 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B187" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
         <x:v>432</x:v>
@@ -6118,33 +6127,33 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="F187" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G187" s="2">
-        <x:v>41900</x:v>
+        <x:v>44645</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:7">
       <x:c r="A188" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B188" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F188" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G188" s="2">
-        <x:v>41813</x:v>
+        <x:v>41900</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:7">
@@ -6152,10 +6161,10 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B189" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
         <x:v>435</x:v>
@@ -6164,10 +6173,10 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="F189" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G189" s="2">
-        <x:v>43573</x:v>
+        <x:v>41813</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
@@ -6187,15 +6196,15 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="F190" s="1">
-        <x:v>-100</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G190" s="2">
-        <x:v>42236</x:v>
+        <x:v>43573</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
       <x:c r="A191" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
         <x:v>54</x:v>
@@ -6204,13 +6213,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F191" s="1">
-        <x:v>-10</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G191" s="2">
         <x:v>42236</x:v>
@@ -6221,10 +6230,10 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B192" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
         <x:v>441</x:v>
@@ -6233,10 +6242,10 @@
         <x:v>442</x:v>
       </x:c>
       <x:c r="F192" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G192" s="2">
-        <x:v>44804</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:7">
@@ -6244,10 +6253,10 @@
         <x:v>443</x:v>
       </x:c>
       <x:c r="B193" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C193" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
         <x:v>444</x:v>
@@ -6259,7 +6268,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G193" s="2">
-        <x:v>37787</x:v>
+        <x:v>44804</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:7">
@@ -6267,10 +6276,10 @@
         <x:v>446</x:v>
       </x:c>
       <x:c r="B194" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C194" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
         <x:v>447</x:v>
@@ -6279,10 +6288,10 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="F194" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G194" s="2">
-        <x:v>45551</x:v>
+        <x:v>37787</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:7">
@@ -6290,10 +6299,10 @@
         <x:v>449</x:v>
       </x:c>
       <x:c r="B195" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C195" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
         <x:v>450</x:v>
@@ -6302,33 +6311,33 @@
         <x:v>451</x:v>
       </x:c>
       <x:c r="F195" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G195" s="2">
-        <x:v>37736</x:v>
+        <x:v>45551</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:7">
       <x:c r="A196" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B196" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D196" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F196" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G196" s="2">
-        <x:v>41453</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:7">
@@ -6336,73 +6345,73 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="B197" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C197" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="D197" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E197" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F197" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G197" s="2">
-        <x:v>37736</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:7">
       <x:c r="A198" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B198" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C198" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D198" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E198" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F198" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G198" s="2">
-        <x:v>41453</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:7">
       <x:c r="A199" s="1" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B199" s="1" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="C199" s="1" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D199" s="1" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="B199" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C199" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D199" s="1" t="s">
+      <x:c r="E199" s="1" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="E199" s="1" t="s">
-        <x:v>455</x:v>
-      </x:c>
       <x:c r="F199" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G199" s="2">
-        <x:v>45077</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
       <x:c r="A200" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B200" s="1" t="s">
         <x:v>34</x:v>
@@ -6411,13 +6420,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E200" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F200" s="1">
-        <x:v>-950</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G200" s="2">
         <x:v>45077</x:v>
@@ -6425,7 +6434,7 @@
     </x:row>
     <x:row r="201" spans="1:7">
       <x:c r="A201" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B201" s="1" t="s">
         <x:v>34</x:v>
@@ -6434,13 +6443,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F201" s="1">
-        <x:v>-713</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G201" s="2">
         <x:v>45077</x:v>
@@ -6448,7 +6457,7 @@
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
         <x:v>34</x:v>
@@ -6457,13 +6466,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D202" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E202" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F202" s="1">
-        <x:v>-475</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G202" s="2">
         <x:v>45077</x:v>
@@ -6471,7 +6480,7 @@
     </x:row>
     <x:row r="203" spans="1:7">
       <x:c r="A203" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B203" s="1" t="s">
         <x:v>34</x:v>
@@ -6480,13 +6489,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D203" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F203" s="1">
-        <x:v>-238</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G203" s="2">
         <x:v>45077</x:v>
@@ -6497,10 +6506,10 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B204" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C204" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D204" s="1" t="s">
         <x:v>457</x:v>
@@ -6509,10 +6518,10 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="F204" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G204" s="2">
-        <x:v>40178</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:7">
@@ -6520,10 +6529,10 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="B205" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C205" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D205" s="1" t="s">
         <x:v>460</x:v>
@@ -6532,15 +6541,15 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="F205" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G205" s="2">
-        <x:v>39629</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:7">
       <x:c r="A206" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B206" s="1" t="s">
         <x:v>71</x:v>
@@ -6549,15 +6558,38 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F206" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G206" s="2">
+        <x:v>39629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:7">
+      <x:c r="A207" s="1" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B207" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C207" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D207" s="1" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="E207" s="1" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="F207" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G207" s="2">
         <x:v>39660</x:v>
       </x:c>
     </x:row>
@@ -6577,7 +6609,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H154"/>
+  <x:dimension ref="A1:H155"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="9" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -6608,13 +6640,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -10158,10 +10190,10 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
         <x:v>423</x:v>
@@ -10170,13 +10202,13 @@
         <x:v>424</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G138" s="1" t="s">
         <x:v>422</x:v>
       </x:c>
       <x:c r="H138" s="1">
-        <x:v>0</x:v>
+        <x:v>84497</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:8">
@@ -10184,10 +10216,10 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
         <x:v>426</x:v>
@@ -10196,13 +10228,13 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G139" s="1" t="s">
         <x:v>425</x:v>
       </x:c>
       <x:c r="H139" s="1">
-        <x:v>28400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:8">
@@ -10210,10 +10242,10 @@
         <x:v>428</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
         <x:v>429</x:v>
@@ -10222,13 +10254,13 @@
         <x:v>430</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G140" s="1" t="s">
         <x:v>428</x:v>
       </x:c>
       <x:c r="H140" s="1">
-        <x:v>22566</x:v>
+        <x:v>28400</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:8">
@@ -10236,10 +10268,10 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
         <x:v>432</x:v>
@@ -10248,39 +10280,39 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
         <x:v>431</x:v>
       </x:c>
       <x:c r="H141" s="1">
-        <x:v>3750</x:v>
+        <x:v>22566</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:8">
       <x:c r="A142" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="H142" s="1">
-        <x:v>10000</x:v>
+        <x:v>3750</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:8">
@@ -10288,10 +10320,10 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
         <x:v>435</x:v>
@@ -10300,13 +10332,13 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
         <x:v>434</x:v>
       </x:c>
       <x:c r="H143" s="1">
-        <x:v>18414</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:8">
@@ -10326,13 +10358,13 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-110</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
         <x:v>437</x:v>
       </x:c>
       <x:c r="H144" s="1">
-        <x:v>5170</x:v>
+        <x:v>18414</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:8">
@@ -10340,10 +10372,10 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
         <x:v>441</x:v>
@@ -10352,13 +10384,13 @@
         <x:v>442</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-110</x:v>
       </x:c>
       <x:c r="G145" s="1" t="s">
         <x:v>440</x:v>
       </x:c>
       <x:c r="H145" s="1">
-        <x:v>6000</x:v>
+        <x:v>5170</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:8">
@@ -10366,10 +10398,10 @@
         <x:v>443</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
         <x:v>444</x:v>
@@ -10384,7 +10416,7 @@
         <x:v>443</x:v>
       </x:c>
       <x:c r="H146" s="1">
-        <x:v>10972</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:8">
@@ -10392,10 +10424,10 @@
         <x:v>446</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
         <x:v>447</x:v>
@@ -10404,13 +10436,13 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="H147" s="1">
-        <x:v>57350</x:v>
+        <x:v>10972</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:8">
@@ -10418,10 +10450,10 @@
         <x:v>449</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
         <x:v>450</x:v>
@@ -10430,39 +10462,39 @@
         <x:v>451</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
         <x:v>449</x:v>
       </x:c>
       <x:c r="H148" s="1">
-        <x:v>2500</x:v>
+        <x:v>57350</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:8">
       <x:c r="A149" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="H149" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:8">
@@ -10470,77 +10502,77 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
         <x:v>452</x:v>
       </x:c>
       <x:c r="H150" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:8">
       <x:c r="A151" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="H151" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:8">
       <x:c r="A152" s="1" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B152" s="1" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="C152" s="1" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D152" s="1" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="B152" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C152" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D152" s="1" t="s">
+      <x:c r="E152" s="1" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="E152" s="1" t="s">
+      <x:c r="F152" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G152" s="1" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="F152" s="1">
-        <x:v>-5131</x:v>
-      </x:c>
-      <x:c r="G152" s="1" t="s">
-        <x:v>453</x:v>
-      </x:c>
       <x:c r="H152" s="1">
-        <x:v>83966</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:8">
@@ -10548,10 +10580,10 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
         <x:v>457</x:v>
@@ -10560,13 +10592,13 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5131</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
         <x:v>456</x:v>
       </x:c>
       <x:c r="H153" s="1">
-        <x:v>6000</x:v>
+        <x:v>83966</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:8">
@@ -10574,10 +10606,10 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
         <x:v>460</x:v>
@@ -10592,6 +10624,32 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="H154" s="1">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:8">
+      <x:c r="A155" s="1" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B155" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C155" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D155" s="1" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="E155" s="1" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="F155" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G155" s="1" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="H155" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -704,6 +704,15 @@
     <x:t>FUND FOR A CONSERVATIVE FUTURE II</x:t>
   </x:si>
   <x:si>
+    <x:t>JACK, BRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00872473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRIAN JACK FOR CONGRESS</x:t>
+  </x:si>
+  <x:si>
     <x:t>JEFFRIES, HAKEEM</x:t>
   </x:si>
   <x:si>
@@ -726,6 +735,15 @@
   </x:si>
   <x:si>
     <x:t>MIDDLE GROUND PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JORDAN, JAMES D.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00416594</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JIM JORDAN FOR CONGRESS</x:t>
   </x:si>
   <x:si>
     <x:t>JUSTICE, JAMES CONLEY II</x:t>
@@ -1499,8 +1517,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G207" totalsRowShown="0">
-  <x:autoFilter ref="A1:G207"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G209" totalsRowShown="0">
+  <x:autoFilter ref="A1:G209"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1515,8 +1533,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H155" totalsRowShown="0">
-  <x:autoFilter ref="A1:H155"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H157" totalsRowShown="0">
+  <x:autoFilter ref="A1:H157"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1819,7 +1837,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G207"/>
+  <x:dimension ref="A1:G209"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3907,33 +3925,33 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C91" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D91" s="1" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="C91" s="1" t="s">
+      <x:c r="E91" s="1" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="D91" s="1" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="E91" s="1" t="s">
-        <x:v>233</x:v>
-      </x:c>
       <x:c r="F91" s="1">
-        <x:v>-2800</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G91" s="2">
-        <x:v>41893</x:v>
+        <x:v>46044</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B92" s="1" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C92" s="1" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="B92" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C92" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
         <x:v>235</x:v>
@@ -3942,10 +3960,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2800</x:v>
       </x:c>
       <x:c r="G92" s="2">
-        <x:v>38717</x:v>
+        <x:v>41893</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
@@ -3953,10 +3971,10 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
         <x:v>238</x:v>
@@ -3965,10 +3983,10 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G93" s="2">
-        <x:v>45617</x:v>
+        <x:v>38717</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
@@ -3976,10 +3994,10 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
         <x:v>241</x:v>
@@ -3988,56 +4006,56 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G94" s="2">
-        <x:v>40602</x:v>
+        <x:v>46051</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="F95" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G95" s="2">
-        <x:v>40602</x:v>
+        <x:v>45617</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G96" s="2">
-        <x:v>44727</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
@@ -4045,10 +4063,10 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
         <x:v>247</x:v>
@@ -4060,7 +4078,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G97" s="2">
-        <x:v>38990</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
@@ -4068,10 +4086,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
         <x:v>250</x:v>
@@ -4083,7 +4101,7 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G98" s="2">
-        <x:v>38292</x:v>
+        <x:v>44727</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
@@ -4091,10 +4109,10 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
         <x:v>253</x:v>
@@ -4106,7 +4124,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G99" s="2">
-        <x:v>39512</x:v>
+        <x:v>38990</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
@@ -4114,10 +4132,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
         <x:v>256</x:v>
@@ -4126,10 +4144,10 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G100" s="2">
-        <x:v>45517</x:v>
+        <x:v>38292</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
@@ -4137,10 +4155,10 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
         <x:v>259</x:v>
@@ -4152,7 +4170,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G101" s="2">
-        <x:v>40178</x:v>
+        <x:v>39512</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
@@ -4160,10 +4178,10 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
         <x:v>262</x:v>
@@ -4172,38 +4190,38 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>-500</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G102" s="2">
-        <x:v>45533</x:v>
+        <x:v>45517</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>-9</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G103" s="2">
-        <x:v>45533</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
         <x:v>34</x:v>
@@ -4212,13 +4230,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>-1</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G104" s="2">
         <x:v>45533</x:v>
@@ -4226,25 +4244,25 @@
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G105" s="2">
-        <x:v>44893</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -4264,10 +4282,10 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>-475</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G106" s="2">
-        <x:v>45077</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -4275,10 +4293,10 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
         <x:v>271</x:v>
@@ -4287,10 +4305,10 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-250</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G107" s="2">
-        <x:v>43799</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
@@ -4298,10 +4316,10 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
         <x:v>274</x:v>
@@ -4310,10 +4328,10 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G108" s="2">
-        <x:v>37855</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
@@ -4321,10 +4339,10 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
         <x:v>277</x:v>
@@ -4333,10 +4351,10 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G109" s="2">
-        <x:v>44716</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
@@ -4344,10 +4362,10 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
         <x:v>280</x:v>
@@ -4359,7 +4377,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G110" s="2">
-        <x:v>42004</x:v>
+        <x:v>37855</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
@@ -4367,10 +4385,10 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
         <x:v>283</x:v>
@@ -4379,38 +4397,38 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G111" s="2">
-        <x:v>43167</x:v>
+        <x:v>44716</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G112" s="2">
-        <x:v>44893</x:v>
+        <x:v>42004</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
         <x:v>87</x:v>
@@ -4419,10 +4437,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F113" s="1">
         <x:v>-1350</x:v>
@@ -4433,7 +4451,7 @@
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
         <x:v>106</x:v>
@@ -4442,10 +4460,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F114" s="1">
         <x:v>-2000</x:v>
@@ -4456,48 +4474,48 @@
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F115" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G115" s="2">
-        <x:v>40602</x:v>
+        <x:v>43167</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="1" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B116" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C116" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D116" s="1" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="B116" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C116" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D116" s="1" t="s">
+      <x:c r="E116" s="1" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="E116" s="1" t="s">
-        <x:v>291</x:v>
       </x:c>
       <x:c r="F116" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G116" s="2">
-        <x:v>40422</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
@@ -4517,10 +4535,10 @@
         <x:v>294</x:v>
       </x:c>
       <x:c r="F117" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G117" s="2">
-        <x:v>42818</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
@@ -4528,10 +4546,10 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
         <x:v>296</x:v>
@@ -4543,7 +4561,7 @@
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G118" s="2">
-        <x:v>45107</x:v>
+        <x:v>40422</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
@@ -4551,10 +4569,10 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
         <x:v>299</x:v>
@@ -4563,10 +4581,10 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="F119" s="1">
-        <x:v>-1</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G119" s="2">
-        <x:v>45408</x:v>
+        <x:v>42818</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7">
@@ -4574,10 +4592,10 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
         <x:v>302</x:v>
@@ -4586,10 +4604,10 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G120" s="2">
-        <x:v>43390</x:v>
+        <x:v>45107</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
@@ -4597,125 +4615,125 @@
         <x:v>304</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C121" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D121" s="1" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="C121" s="1" t="s">
+      <x:c r="E121" s="1" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="D121" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="E121" s="1" t="s">
-        <x:v>308</x:v>
-      </x:c>
       <x:c r="F121" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G121" s="2">
-        <x:v>43282</x:v>
+        <x:v>45408</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7">
       <x:c r="A122" s="1" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B122" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C122" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D122" s="1" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E122" s="1" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="B122" s="1" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C122" s="1" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D122" s="1" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="E122" s="1" t="s">
-        <x:v>311</x:v>
-      </x:c>
       <x:c r="F122" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G122" s="2">
-        <x:v>44013</x:v>
+        <x:v>43390</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:7">
       <x:c r="A123" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F123" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G123" s="2">
-        <x:v>44022</x:v>
+        <x:v>43282</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="E124" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="F124" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G124" s="2">
-        <x:v>41926</x:v>
+        <x:v>44013</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="1" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B125" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C125" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D125" s="1" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="E125" s="1" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="B125" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C125" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D125" s="1" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="E125" s="1" t="s">
-        <x:v>319</x:v>
-      </x:c>
       <x:c r="F125" s="1">
-        <x:v>-20</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G125" s="2">
-        <x:v>41698</x:v>
+        <x:v>44022</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:7">
       <x:c r="A126" s="1" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B126" s="1" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="C126" s="1" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="B126" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C126" s="1" t="s">
-        <x:v>9</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
         <x:v>321</x:v>
@@ -4724,10 +4742,10 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="F126" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G126" s="2">
-        <x:v>45484</x:v>
+        <x:v>41926</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7">
@@ -4735,10 +4753,10 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
         <x:v>324</x:v>
@@ -4747,38 +4765,38 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="F127" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G127" s="2">
-        <x:v>45957</x:v>
+        <x:v>41698</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7">
       <x:c r="A128" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F128" s="1">
-        <x:v>-1650</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G128" s="2">
-        <x:v>45959</x:v>
+        <x:v>45484</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
       <x:c r="A129" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
         <x:v>34</x:v>
@@ -4787,21 +4805,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-1650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G129" s="2">
-        <x:v>45977</x:v>
+        <x:v>45957</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
         <x:v>34</x:v>
@@ -4810,21 +4828,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="G130" s="2">
-        <x:v>45977</x:v>
+        <x:v>45959</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
         <x:v>34</x:v>
@@ -4833,13 +4851,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="G131" s="2">
         <x:v>45977</x:v>
@@ -4847,7 +4865,7 @@
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
         <x:v>34</x:v>
@@ -4856,13 +4874,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>-1800</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G132" s="2">
         <x:v>45977</x:v>
@@ -4870,7 +4888,7 @@
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
         <x:v>34</x:v>
@@ -4879,13 +4897,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G133" s="2">
         <x:v>45977</x:v>
@@ -4893,7 +4911,7 @@
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
         <x:v>34</x:v>
@@ -4902,13 +4920,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1800</x:v>
       </x:c>
       <x:c r="G134" s="2">
         <x:v>45977</x:v>
@@ -4916,7 +4934,7 @@
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
         <x:v>34</x:v>
@@ -4925,13 +4943,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F135" s="1">
-        <x:v>-36</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G135" s="2">
         <x:v>45977</x:v>
@@ -4939,7 +4957,7 @@
     </x:row>
     <x:row r="136" spans="1:7">
       <x:c r="A136" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
         <x:v>34</x:v>
@@ -4948,13 +4966,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F136" s="1">
-        <x:v>-9</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G136" s="2">
         <x:v>45977</x:v>
@@ -4962,7 +4980,7 @@
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
         <x:v>34</x:v>
@@ -4971,13 +4989,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-3</x:v>
+        <x:v>-36</x:v>
       </x:c>
       <x:c r="G137" s="2">
         <x:v>45977</x:v>
@@ -4985,7 +5003,7 @@
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
         <x:v>34</x:v>
@@ -4994,13 +5012,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-2</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G138" s="2">
         <x:v>45977</x:v>
@@ -5008,7 +5026,7 @@
     </x:row>
     <x:row r="139" spans="1:7">
       <x:c r="A139" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
         <x:v>34</x:v>
@@ -5017,13 +5035,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-1</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="G139" s="2">
         <x:v>45977</x:v>
@@ -5031,7 +5049,7 @@
     </x:row>
     <x:row r="140" spans="1:7">
       <x:c r="A140" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
         <x:v>34</x:v>
@@ -5040,39 +5058,39 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="G140" s="2">
-        <x:v>45980</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
       <x:c r="A141" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-800</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G141" s="2">
-        <x:v>40602</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:7">
@@ -5080,10 +5098,10 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
         <x:v>330</x:v>
@@ -5092,10 +5110,10 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G142" s="2">
-        <x:v>37736</x:v>
+        <x:v>45980</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:7">
@@ -5103,10 +5121,10 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
         <x:v>333</x:v>
@@ -5115,10 +5133,10 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="G143" s="2">
-        <x:v>39810</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:7">
@@ -5126,10 +5144,10 @@
         <x:v>335</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
         <x:v>336</x:v>
@@ -5138,10 +5156,10 @@
         <x:v>337</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G144" s="2">
-        <x:v>44767</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:7">
@@ -5149,10 +5167,10 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
         <x:v>339</x:v>
@@ -5161,10 +5179,10 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G145" s="2">
-        <x:v>41010</x:v>
+        <x:v>39810</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:7">
@@ -5172,10 +5190,10 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
         <x:v>342</x:v>
@@ -5184,10 +5202,10 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G146" s="2">
-        <x:v>41840</x:v>
+        <x:v>44767</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:7">
@@ -5195,10 +5213,10 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
         <x:v>345</x:v>
@@ -5207,10 +5225,10 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-100</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G147" s="2">
-        <x:v>40602</x:v>
+        <x:v>41010</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:7">
@@ -5218,10 +5236,10 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
         <x:v>348</x:v>
@@ -5230,10 +5248,10 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-9</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G148" s="2">
-        <x:v>45972</x:v>
+        <x:v>41840</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
@@ -5253,7 +5271,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G149" s="2">
         <x:v>40602</x:v>
@@ -5261,30 +5279,30 @@
     </x:row>
     <x:row r="150" spans="1:7">
       <x:c r="A150" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G150" s="2">
-        <x:v>40602</x:v>
+        <x:v>45972</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
         <x:v>54</x:v>
@@ -5293,13 +5311,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G151" s="2">
         <x:v>40602</x:v>
@@ -5307,7 +5325,7 @@
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
         <x:v>54</x:v>
@@ -5316,13 +5334,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>-50</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G152" s="2">
         <x:v>40602</x:v>
@@ -5330,7 +5348,7 @@
     </x:row>
     <x:row r="153" spans="1:7">
       <x:c r="A153" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
         <x:v>54</x:v>
@@ -5339,13 +5357,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-5</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G153" s="2">
         <x:v>40602</x:v>
@@ -5353,7 +5371,7 @@
     </x:row>
     <x:row r="154" spans="1:7">
       <x:c r="A154" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
         <x:v>54</x:v>
@@ -5362,13 +5380,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>-250</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G154" s="2">
         <x:v>40602</x:v>
@@ -5379,68 +5397,68 @@
         <x:v>356</x:v>
       </x:c>
       <x:c r="B155" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="G155" s="2">
-        <x:v>38075</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:7">
       <x:c r="A156" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F156" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G156" s="2">
-        <x:v>41455</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:7">
       <x:c r="A157" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F157" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G157" s="2">
-        <x:v>45698</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:7">
@@ -5448,10 +5466,10 @@
         <x:v>363</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
         <x:v>364</x:v>
@@ -5460,10 +5478,10 @@
         <x:v>365</x:v>
       </x:c>
       <x:c r="F158" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G158" s="2">
-        <x:v>43646</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:7">
@@ -5471,10 +5489,10 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
         <x:v>367</x:v>
@@ -5483,10 +5501,10 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="F159" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G159" s="2">
-        <x:v>39940</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:7">
@@ -5494,10 +5512,10 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
         <x:v>370</x:v>
@@ -5506,10 +5524,10 @@
         <x:v>371</x:v>
       </x:c>
       <x:c r="F160" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G160" s="2">
-        <x:v>41455</x:v>
+        <x:v>43646</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:7">
@@ -5517,10 +5535,10 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="B161" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
         <x:v>373</x:v>
@@ -5529,10 +5547,10 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="F161" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G161" s="2">
-        <x:v>38322</x:v>
+        <x:v>39940</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:7">
@@ -5540,10 +5558,10 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="B162" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
         <x:v>376</x:v>
@@ -5552,10 +5570,10 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="F162" s="1">
-        <x:v>-250</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G162" s="2">
-        <x:v>38322</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:7">
@@ -5563,10 +5581,10 @@
         <x:v>378</x:v>
       </x:c>
       <x:c r="B163" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
         <x:v>379</x:v>
@@ -5575,56 +5593,56 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="F163" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G163" s="2">
-        <x:v>44377</x:v>
+        <x:v>38322</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:7">
       <x:c r="A164" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B164" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D164" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F164" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G164" s="2">
-        <x:v>44377</x:v>
+        <x:v>38322</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:7">
       <x:c r="A165" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F165" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G165" s="2">
-        <x:v>40682</x:v>
+        <x:v>44377</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:7">
@@ -5632,10 +5650,10 @@
         <x:v>384</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
         <x:v>385</x:v>
@@ -5644,10 +5662,10 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="F166" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G166" s="2">
-        <x:v>39318</x:v>
+        <x:v>44377</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:7">
@@ -5655,10 +5673,10 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
         <x:v>388</x:v>
@@ -5670,7 +5688,7 @@
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G167" s="2">
-        <x:v>45879</x:v>
+        <x:v>40682</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:7">
@@ -5678,96 +5696,96 @@
         <x:v>390</x:v>
       </x:c>
       <x:c r="B168" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="F168" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G168" s="2">
-        <x:v>38075</x:v>
+        <x:v>39318</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:7">
       <x:c r="A169" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B169" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="F169" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G169" s="2">
-        <x:v>38764</x:v>
+        <x:v>45879</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:7">
       <x:c r="A170" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B170" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D170" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F170" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G170" s="2">
-        <x:v>43201</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:7">
       <x:c r="A171" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B171" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D171" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F171" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G171" s="2">
-        <x:v>43201</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:7">
       <x:c r="A172" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B172" s="1" t="s">
         <x:v>54</x:v>
@@ -5776,13 +5794,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F172" s="1">
-        <x:v>-200</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G172" s="2">
         <x:v>43201</x:v>
@@ -5790,7 +5808,7 @@
     </x:row>
     <x:row r="173" spans="1:7">
       <x:c r="A173" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
         <x:v>54</x:v>
@@ -5799,13 +5817,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F173" s="1">
-        <x:v>-100</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G173" s="2">
         <x:v>43201</x:v>
@@ -5813,48 +5831,48 @@
     </x:row>
     <x:row r="174" spans="1:7">
       <x:c r="A174" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C174" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F174" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G174" s="2">
-        <x:v>39777</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:7">
       <x:c r="A175" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B175" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C175" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D175" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F175" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G175" s="2">
-        <x:v>43465</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:7">
@@ -5862,10 +5880,10 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="B176" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
         <x:v>401</x:v>
@@ -5874,10 +5892,10 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="F176" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G176" s="2">
-        <x:v>39010</x:v>
+        <x:v>39777</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:7">
@@ -5885,10 +5903,10 @@
         <x:v>403</x:v>
       </x:c>
       <x:c r="B177" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
         <x:v>404</x:v>
@@ -5897,10 +5915,10 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="F177" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G177" s="2">
-        <x:v>42783</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:7">
@@ -5908,10 +5926,10 @@
         <x:v>406</x:v>
       </x:c>
       <x:c r="B178" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
         <x:v>407</x:v>
@@ -5920,10 +5938,10 @@
         <x:v>408</x:v>
       </x:c>
       <x:c r="F178" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G178" s="2">
-        <x:v>45692</x:v>
+        <x:v>39010</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:7">
@@ -5931,10 +5949,10 @@
         <x:v>409</x:v>
       </x:c>
       <x:c r="B179" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
         <x:v>410</x:v>
@@ -5943,10 +5961,10 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="F179" s="1">
-        <x:v>-300</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G179" s="2">
-        <x:v>43799</x:v>
+        <x:v>42783</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:7">
@@ -5954,68 +5972,68 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B180" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F180" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G180" s="2">
-        <x:v>38075</x:v>
+        <x:v>45692</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:7">
       <x:c r="A181" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B181" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="F181" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G181" s="2">
-        <x:v>45698</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:7">
       <x:c r="A182" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B182" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F182" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G182" s="2">
-        <x:v>45665</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:7">
@@ -6023,10 +6041,10 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="B183" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
         <x:v>420</x:v>
@@ -6035,10 +6053,10 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="F183" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G183" s="2">
-        <x:v>40724</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:7">
@@ -6061,7 +6079,7 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G184" s="2">
-        <x:v>46000</x:v>
+        <x:v>45665</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:7">
@@ -6081,10 +6099,10 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F185" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G185" s="2">
-        <x:v>43465</x:v>
+        <x:v>40724</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:7">
@@ -6107,7 +6125,7 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G186" s="2">
-        <x:v>44845</x:v>
+        <x:v>46000</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:7">
@@ -6115,10 +6133,10 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B187" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
         <x:v>432</x:v>
@@ -6127,10 +6145,10 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="F187" s="1">
-        <x:v>-300</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G187" s="2">
-        <x:v>44645</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:7">
@@ -6138,10 +6156,10 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B188" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
         <x:v>435</x:v>
@@ -6150,56 +6168,56 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="F188" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G188" s="2">
-        <x:v>41900</x:v>
+        <x:v>44845</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:7">
       <x:c r="A189" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B189" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F189" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G189" s="2">
-        <x:v>41813</x:v>
+        <x:v>44645</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
       <x:c r="A190" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B190" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C190" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F190" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G190" s="2">
-        <x:v>43573</x:v>
+        <x:v>41900</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
@@ -6207,10 +6225,10 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
         <x:v>441</x:v>
@@ -6219,15 +6237,15 @@
         <x:v>442</x:v>
       </x:c>
       <x:c r="F191" s="1">
-        <x:v>-100</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G191" s="2">
-        <x:v>42236</x:v>
+        <x:v>41813</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:7">
       <x:c r="A192" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B192" s="1" t="s">
         <x:v>54</x:v>
@@ -6236,39 +6254,39 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F192" s="1">
-        <x:v>-10</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G192" s="2">
-        <x:v>42236</x:v>
+        <x:v>43573</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:7">
       <x:c r="A193" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B193" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C193" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="F193" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G193" s="2">
-        <x:v>44804</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:7">
@@ -6276,10 +6294,10 @@
         <x:v>446</x:v>
       </x:c>
       <x:c r="B194" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C194" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
         <x:v>447</x:v>
@@ -6288,10 +6306,10 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="F194" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G194" s="2">
-        <x:v>37787</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:7">
@@ -6311,10 +6329,10 @@
         <x:v>451</x:v>
       </x:c>
       <x:c r="F195" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G195" s="2">
-        <x:v>45551</x:v>
+        <x:v>44804</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:7">
@@ -6322,10 +6340,10 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="B196" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D196" s="1" t="s">
         <x:v>453</x:v>
@@ -6337,35 +6355,35 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G196" s="2">
-        <x:v>37736</x:v>
+        <x:v>37787</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:7">
       <x:c r="A197" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B197" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C197" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D197" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E197" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F197" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G197" s="2">
-        <x:v>41453</x:v>
+        <x:v>45551</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:7">
       <x:c r="A198" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B198" s="1" t="s">
         <x:v>39</x:v>
@@ -6374,10 +6392,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D198" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E198" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F198" s="1">
         <x:v>-1000</x:v>
@@ -6388,19 +6406,19 @@
     </x:row>
     <x:row r="199" spans="1:7">
       <x:c r="A199" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B199" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C199" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="D199" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E199" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F199" s="1">
         <x:v>-2000</x:v>
@@ -6411,53 +6429,53 @@
     </x:row>
     <x:row r="200" spans="1:7">
       <x:c r="A200" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B200" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E200" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F200" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G200" s="2">
-        <x:v>45077</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
       <x:c r="A201" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B201" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C201" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F201" s="1">
-        <x:v>-950</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G201" s="2">
-        <x:v>45077</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
         <x:v>34</x:v>
@@ -6466,13 +6484,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D202" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E202" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F202" s="1">
-        <x:v>-713</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G202" s="2">
         <x:v>45077</x:v>
@@ -6480,7 +6498,7 @@
     </x:row>
     <x:row r="203" spans="1:7">
       <x:c r="A203" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B203" s="1" t="s">
         <x:v>34</x:v>
@@ -6489,13 +6507,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D203" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F203" s="1">
-        <x:v>-475</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G203" s="2">
         <x:v>45077</x:v>
@@ -6503,7 +6521,7 @@
     </x:row>
     <x:row r="204" spans="1:7">
       <x:c r="A204" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B204" s="1" t="s">
         <x:v>34</x:v>
@@ -6512,13 +6530,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D204" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E204" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F204" s="1">
-        <x:v>-238</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G204" s="2">
         <x:v>45077</x:v>
@@ -6526,25 +6544,25 @@
     </x:row>
     <x:row r="205" spans="1:7">
       <x:c r="A205" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B205" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C205" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D205" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E205" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F205" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G205" s="2">
-        <x:v>40178</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:7">
@@ -6552,10 +6570,10 @@
         <x:v>462</x:v>
       </x:c>
       <x:c r="B206" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
         <x:v>463</x:v>
@@ -6564,32 +6582,78 @@
         <x:v>464</x:v>
       </x:c>
       <x:c r="F206" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G206" s="2">
-        <x:v>39629</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:7">
       <x:c r="A207" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B207" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C207" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D207" s="1" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="E207" s="1" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="F207" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G207" s="2">
+        <x:v>40178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:7">
+      <x:c r="A208" s="1" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B208" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C207" s="1" t="s">
+      <x:c r="C208" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D207" s="1" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="E207" s="1" t="s">
-        <x:v>464</x:v>
-      </x:c>
-      <x:c r="F207" s="1">
+      <x:c r="D208" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="E208" s="1" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="F208" s="1">
         <x:v>-1000</x:v>
       </x:c>
-      <x:c r="G207" s="2">
+      <x:c r="G208" s="2">
+        <x:v>39629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:7">
+      <x:c r="A209" s="1" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B209" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C209" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D209" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="E209" s="1" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="F209" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G209" s="2">
         <x:v>39660</x:v>
       </x:c>
     </x:row>
@@ -6609,7 +6673,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H155"/>
+  <x:dimension ref="A1:H157"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="9" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -6640,13 +6704,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -8396,36 +8460,36 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="C69" s="1" t="s">
+      <x:c r="E69" s="1" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="D69" s="1" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="E69" s="1" t="s">
-        <x:v>233</x:v>
-      </x:c>
       <x:c r="F69" s="1">
-        <x:v>-2800</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>229</x:v>
       </x:c>
       <x:c r="H69" s="1">
-        <x:v>0</x:v>
+        <x:v>249781</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:8">
       <x:c r="A70" s="1" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B70" s="1" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C70" s="1" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="B70" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C70" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
         <x:v>235</x:v>
@@ -8434,13 +8498,13 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2800</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:8">
@@ -8448,10 +8512,10 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
         <x:v>238</x:v>
@@ -8460,13 +8524,13 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>237</x:v>
       </x:c>
       <x:c r="H71" s="1">
-        <x:v>2000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:8">
@@ -8474,10 +8538,10 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
         <x:v>241</x:v>
@@ -8486,13 +8550,13 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>-3400</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>240</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>28982</x:v>
+        <x:v>217522</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:8">
@@ -8500,10 +8564,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
         <x:v>244</x:v>
@@ -8512,13 +8576,13 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>243</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:8">
@@ -8526,10 +8590,10 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
         <x:v>247</x:v>
@@ -8538,13 +8602,13 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3400</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
         <x:v>246</x:v>
       </x:c>
       <x:c r="H74" s="1">
-        <x:v>3000</x:v>
+        <x:v>28982</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:8">
@@ -8552,10 +8616,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
         <x:v>250</x:v>
@@ -8578,10 +8642,10 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
         <x:v>253</x:v>
@@ -8596,7 +8660,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -8604,10 +8668,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
         <x:v>256</x:v>
@@ -8616,13 +8680,13 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>255</x:v>
       </x:c>
       <x:c r="H77" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:8">
@@ -8630,10 +8694,10 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>259</x:v>
@@ -8648,7 +8712,7 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="H78" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:8">
@@ -8656,10 +8720,10 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>262</x:v>
@@ -8668,13 +8732,13 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>-510</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>261</x:v>
       </x:c>
       <x:c r="H79" s="1">
-        <x:v>42500</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:8">
@@ -8682,10 +8746,10 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
         <x:v>265</x:v>
@@ -8694,13 +8758,13 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>264</x:v>
       </x:c>
       <x:c r="H80" s="1">
-        <x:v>2000</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:8">
@@ -8720,13 +8784,13 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>-475</x:v>
+        <x:v>-510</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>267</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>131385</x:v>
+        <x:v>42500</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:8">
@@ -8734,10 +8798,10 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
         <x:v>271</x:v>
@@ -8746,13 +8810,13 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>-250</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
         <x:v>270</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>69371</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:8">
@@ -8760,10 +8824,10 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
         <x:v>274</x:v>
@@ -8772,13 +8836,13 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
         <x:v>273</x:v>
       </x:c>
       <x:c r="H83" s="1">
-        <x:v>500</x:v>
+        <x:v>131385</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:8">
@@ -8786,10 +8850,10 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
         <x:v>277</x:v>
@@ -8798,13 +8862,13 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
         <x:v>276</x:v>
       </x:c>
       <x:c r="H84" s="1">
-        <x:v>111188</x:v>
+        <x:v>69371</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:8">
@@ -8812,10 +8876,10 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
         <x:v>280</x:v>
@@ -8830,7 +8894,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="H85" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:8">
@@ -8838,10 +8902,10 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
         <x:v>283</x:v>
@@ -8856,38 +8920,38 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="H86" s="1">
-        <x:v>10000</x:v>
+        <x:v>111188</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:8">
       <x:c r="A87" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="H87" s="1">
-        <x:v>1150</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:8">
       <x:c r="A88" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
         <x:v>106</x:v>
@@ -8896,16 +8960,16 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F88" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H88" s="1">
         <x:v>10000</x:v>
@@ -8913,7 +8977,7 @@
     </x:row>
     <x:row r="89" spans="1:8">
       <x:c r="A89" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
         <x:v>87</x:v>
@@ -8922,16 +8986,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F89" s="1">
         <x:v>-1350</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H89" s="1">
         <x:v>1150</x:v>
@@ -8939,54 +9003,54 @@
     </x:row>
     <x:row r="90" spans="1:8">
       <x:c r="A90" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="H90" s="1">
-        <x:v>33320</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:8">
       <x:c r="A91" s="1" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B91" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C91" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D91" s="1" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="B91" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C91" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D91" s="1" t="s">
+      <x:c r="E91" s="1" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="E91" s="1" t="s">
+      <x:c r="F91" s="1">
+        <x:v>-1350</x:v>
+      </x:c>
+      <x:c r="G91" s="1" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="F91" s="1">
-        <x:v>-2000</x:v>
-      </x:c>
-      <x:c r="G91" s="1" t="s">
-        <x:v>289</x:v>
-      </x:c>
       <x:c r="H91" s="1">
-        <x:v>0</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:8">
@@ -9006,13 +9070,13 @@
         <x:v>294</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
         <x:v>292</x:v>
       </x:c>
       <x:c r="H92" s="1">
-        <x:v>21095</x:v>
+        <x:v>33320</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:8">
@@ -9020,10 +9084,10 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
         <x:v>296</x:v>
@@ -9046,10 +9110,10 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
         <x:v>299</x:v>
@@ -9058,13 +9122,13 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>-1</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
         <x:v>298</x:v>
       </x:c>
       <x:c r="H94" s="1">
-        <x:v>26650</x:v>
+        <x:v>21095</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:8">
@@ -9072,10 +9136,10 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
         <x:v>302</x:v>
@@ -9084,13 +9148,13 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
         <x:v>301</x:v>
       </x:c>
       <x:c r="H95" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:8">
@@ -9098,140 +9162,140 @@
         <x:v>304</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C96" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D96" s="1" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="C96" s="1" t="s">
+      <x:c r="E96" s="1" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="D96" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="E96" s="1" t="s">
-        <x:v>308</x:v>
-      </x:c>
       <x:c r="F96" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
         <x:v>304</x:v>
       </x:c>
       <x:c r="H96" s="1">
-        <x:v>12000</x:v>
+        <x:v>26650</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:8">
       <x:c r="A97" s="1" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B97" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C97" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D97" s="1" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E97" s="1" t="s">
         <x:v>309</x:v>
-      </x:c>
-      <x:c r="B97" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C97" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D97" s="1" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="E97" s="1" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="F97" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="H97" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:8">
       <x:c r="A98" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="E98" s="1" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F98" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G98" s="1" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="E98" s="1" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="F98" s="1">
-        <x:v>-2500</x:v>
-      </x:c>
-      <x:c r="G98" s="1" t="s">
-        <x:v>309</x:v>
-      </x:c>
       <x:c r="H98" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:8">
       <x:c r="A99" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="E99" s="1" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="F99" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G99" s="1" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="E99" s="1" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="F99" s="1">
-        <x:v>-2000</x:v>
-      </x:c>
-      <x:c r="G99" s="1" t="s">
-        <x:v>312</x:v>
-      </x:c>
       <x:c r="H99" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:8">
       <x:c r="A100" s="1" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B100" s="1" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C100" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D100" s="1" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="E100" s="1" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="B100" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C100" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D100" s="1" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="E100" s="1" t="s">
-        <x:v>319</x:v>
-      </x:c>
       <x:c r="F100" s="1">
-        <x:v>-20</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="H100" s="1">
-        <x:v>14900</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:8">
       <x:c r="A101" s="1" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B101" s="1" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="C101" s="1" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="B101" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C101" s="1" t="s">
-        <x:v>9</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
         <x:v>321</x:v>
@@ -9240,13 +9304,13 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="H101" s="1">
-        <x:v>5000</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:8">
@@ -9254,10 +9318,10 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
         <x:v>324</x:v>
@@ -9266,13 +9330,13 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>-19701</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
         <x:v>323</x:v>
       </x:c>
       <x:c r="H102" s="1">
-        <x:v>49967</x:v>
+        <x:v>14900</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:8">
@@ -9280,10 +9344,10 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
         <x:v>327</x:v>
@@ -9292,13 +9356,13 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>-800</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
         <x:v>326</x:v>
       </x:c>
       <x:c r="H103" s="1">
-        <x:v>58679</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:8">
@@ -9306,10 +9370,10 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
         <x:v>330</x:v>
@@ -9318,13 +9382,13 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-19701</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
         <x:v>329</x:v>
       </x:c>
       <x:c r="H104" s="1">
-        <x:v>0</x:v>
+        <x:v>49967</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:8">
@@ -9332,10 +9396,10 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
         <x:v>333</x:v>
@@ -9344,13 +9408,13 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
         <x:v>332</x:v>
       </x:c>
       <x:c r="H105" s="1">
-        <x:v>5000</x:v>
+        <x:v>58679</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:8">
@@ -9358,10 +9422,10 @@
         <x:v>335</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
         <x:v>336</x:v>
@@ -9370,13 +9434,13 @@
         <x:v>337</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="H106" s="1">
-        <x:v>36900</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:8">
@@ -9384,10 +9448,10 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
         <x:v>339</x:v>
@@ -9396,13 +9460,13 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="H107" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:8">
@@ -9410,10 +9474,10 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
         <x:v>342</x:v>
@@ -9422,13 +9486,13 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="H108" s="1">
-        <x:v>0</x:v>
+        <x:v>36900</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:8">
@@ -9436,10 +9500,10 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
         <x:v>345</x:v>
@@ -9448,13 +9512,13 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-100</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
       <x:c r="H109" s="1">
-        <x:v>58000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:8">
@@ -9462,10 +9526,10 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
         <x:v>348</x:v>
@@ -9474,13 +9538,13 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>-9</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
         <x:v>347</x:v>
       </x:c>
       <x:c r="H110" s="1">
-        <x:v>15349</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:8">
@@ -9500,13 +9564,13 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>-4955</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
         <x:v>350</x:v>
       </x:c>
       <x:c r="H111" s="1">
-        <x:v>64475</x:v>
+        <x:v>58000</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:8">
@@ -9514,10 +9578,10 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
         <x:v>354</x:v>
@@ -9526,13 +9590,13 @@
         <x:v>355</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>-250</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
         <x:v>353</x:v>
       </x:c>
       <x:c r="H112" s="1">
-        <x:v>42061</x:v>
+        <x:v>15349</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:8">
@@ -9540,77 +9604,77 @@
         <x:v>356</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-4955</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
         <x:v>356</x:v>
       </x:c>
       <x:c r="H113" s="1">
-        <x:v>0</x:v>
+        <x:v>64475</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:8">
       <x:c r="A114" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="F114" s="1">
+        <x:v>-250</x:v>
+      </x:c>
+      <x:c r="G114" s="1" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="F114" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G114" s="1" t="s">
-        <x:v>357</x:v>
-      </x:c>
       <x:c r="H114" s="1">
-        <x:v>0</x:v>
+        <x:v>42061</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:8">
       <x:c r="A115" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F115" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G115" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="H115" s="1">
-        <x:v>7380</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:8">
@@ -9618,10 +9682,10 @@
         <x:v>363</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
         <x:v>364</x:v>
@@ -9630,13 +9694,13 @@
         <x:v>365</x:v>
       </x:c>
       <x:c r="F116" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G116" s="1" t="s">
         <x:v>363</x:v>
       </x:c>
       <x:c r="H116" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:8">
@@ -9644,10 +9708,10 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
         <x:v>367</x:v>
@@ -9656,13 +9720,13 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="F117" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G117" s="1" t="s">
         <x:v>366</x:v>
       </x:c>
       <x:c r="H117" s="1">
-        <x:v>0</x:v>
+        <x:v>7380</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:8">
@@ -9670,10 +9734,10 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
         <x:v>370</x:v>
@@ -9682,13 +9746,13 @@
         <x:v>371</x:v>
       </x:c>
       <x:c r="F118" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G118" s="1" t="s">
         <x:v>369</x:v>
       </x:c>
       <x:c r="H118" s="1">
-        <x:v>2400</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:8">
@@ -9696,10 +9760,10 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
         <x:v>373</x:v>
@@ -9708,7 +9772,7 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="F119" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G119" s="1" t="s">
         <x:v>372</x:v>
@@ -9722,10 +9786,10 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
         <x:v>376</x:v>
@@ -9734,13 +9798,13 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-250</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G120" s="1" t="s">
         <x:v>375</x:v>
       </x:c>
       <x:c r="H120" s="1">
-        <x:v>6727</x:v>
+        <x:v>2400</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:8">
@@ -9748,10 +9812,10 @@
         <x:v>378</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
         <x:v>379</x:v>
@@ -9760,13 +9824,13 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="F121" s="1">
-        <x:v>-7500</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G121" s="1" t="s">
         <x:v>378</x:v>
       </x:c>
       <x:c r="H121" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:8">
@@ -9774,10 +9838,10 @@
         <x:v>381</x:v>
       </x:c>
       <x:c r="B122" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
         <x:v>382</x:v>
@@ -9786,13 +9850,13 @@
         <x:v>383</x:v>
       </x:c>
       <x:c r="F122" s="1">
-        <x:v>-500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G122" s="1" t="s">
         <x:v>381</x:v>
       </x:c>
       <x:c r="H122" s="1">
-        <x:v>2500</x:v>
+        <x:v>6727</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:8">
@@ -9800,10 +9864,10 @@
         <x:v>384</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
         <x:v>385</x:v>
@@ -9812,13 +9876,13 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="F123" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-7500</x:v>
       </x:c>
       <x:c r="G123" s="1" t="s">
         <x:v>384</x:v>
       </x:c>
       <x:c r="H123" s="1">
-        <x:v>2000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:8">
@@ -9826,10 +9890,10 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
         <x:v>388</x:v>
@@ -9844,7 +9908,7 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="H124" s="1">
-        <x:v>159727</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:8">
@@ -9852,74 +9916,74 @@
         <x:v>390</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="F125" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G125" s="1" t="s">
         <x:v>390</x:v>
       </x:c>
       <x:c r="H125" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:8">
       <x:c r="A126" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="F126" s="1">
+        <x:v>-500</x:v>
+      </x:c>
+      <x:c r="G126" s="1" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="F126" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G126" s="1" t="s">
-        <x:v>391</x:v>
-      </x:c>
       <x:c r="H126" s="1">
-        <x:v>0</x:v>
+        <x:v>159727</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:8">
       <x:c r="A127" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F127" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G127" s="1" t="s">
         <x:v>396</x:v>
-      </x:c>
-      <x:c r="F127" s="1">
-        <x:v>-2500</x:v>
-      </x:c>
-      <x:c r="G127" s="1" t="s">
-        <x:v>394</x:v>
       </x:c>
       <x:c r="H127" s="1">
         <x:v>0</x:v>
@@ -9927,51 +9991,51 @@
     </x:row>
     <x:row r="128" spans="1:8">
       <x:c r="A128" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F128" s="1">
-        <x:v>-1550</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G128" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="H128" s="1">
-        <x:v>193279</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:8">
       <x:c r="A129" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G129" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="H129" s="1">
         <x:v>0</x:v>
@@ -9982,10 +10046,10 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
         <x:v>401</x:v>
@@ -9994,13 +10058,13 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1550</x:v>
       </x:c>
       <x:c r="G130" s="1" t="s">
         <x:v>400</x:v>
       </x:c>
       <x:c r="H130" s="1">
-        <x:v>0</x:v>
+        <x:v>193279</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:8">
@@ -10008,10 +10072,10 @@
         <x:v>403</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
         <x:v>404</x:v>
@@ -10020,13 +10084,13 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G131" s="1" t="s">
         <x:v>403</x:v>
       </x:c>
       <x:c r="H131" s="1">
-        <x:v>19596</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:8">
@@ -10034,10 +10098,10 @@
         <x:v>406</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
         <x:v>407</x:v>
@@ -10046,13 +10110,13 @@
         <x:v>408</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G132" s="1" t="s">
         <x:v>406</x:v>
       </x:c>
       <x:c r="H132" s="1">
-        <x:v>17260</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:8">
@@ -10060,10 +10124,10 @@
         <x:v>409</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
         <x:v>410</x:v>
@@ -10072,13 +10136,13 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>-300</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G133" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
       <x:c r="H133" s="1">
-        <x:v>6150</x:v>
+        <x:v>19596</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:8">
@@ -10086,77 +10150,77 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G134" s="1" t="s">
         <x:v>412</x:v>
       </x:c>
       <x:c r="H134" s="1">
-        <x:v>0</x:v>
+        <x:v>17260</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:8">
       <x:c r="A135" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="F135" s="1">
+        <x:v>-300</x:v>
+      </x:c>
+      <x:c r="G135" s="1" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="F135" s="1">
-        <x:v>-5000</x:v>
-      </x:c>
-      <x:c r="G135" s="1" t="s">
-        <x:v>413</x:v>
-      </x:c>
       <x:c r="H135" s="1">
-        <x:v>32943</x:v>
+        <x:v>6150</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:8">
       <x:c r="A136" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F136" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G136" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="H136" s="1">
-        <x:v>41676</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:8">
@@ -10164,10 +10228,10 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
         <x:v>420</x:v>
@@ -10176,13 +10240,13 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G137" s="1" t="s">
         <x:v>419</x:v>
       </x:c>
       <x:c r="H137" s="1">
-        <x:v>0</x:v>
+        <x:v>32943</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:8">
@@ -10208,7 +10272,7 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="H138" s="1">
-        <x:v>84497</x:v>
+        <x:v>41676</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:8">
@@ -10228,7 +10292,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G139" s="1" t="s">
         <x:v>425</x:v>
@@ -10260,7 +10324,7 @@
         <x:v>428</x:v>
       </x:c>
       <x:c r="H140" s="1">
-        <x:v>28400</x:v>
+        <x:v>84497</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:8">
@@ -10268,10 +10332,10 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
         <x:v>432</x:v>
@@ -10280,13 +10344,13 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-300</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
         <x:v>431</x:v>
       </x:c>
       <x:c r="H141" s="1">
-        <x:v>22566</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:8">
@@ -10294,10 +10358,10 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
         <x:v>435</x:v>
@@ -10306,65 +10370,65 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
         <x:v>434</x:v>
       </x:c>
       <x:c r="H142" s="1">
-        <x:v>3750</x:v>
+        <x:v>28400</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:8">
       <x:c r="A143" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H143" s="1">
-        <x:v>10000</x:v>
+        <x:v>22566</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:8">
       <x:c r="A144" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H144" s="1">
-        <x:v>18414</x:v>
+        <x:v>3750</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:8">
@@ -10372,10 +10436,10 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
         <x:v>441</x:v>
@@ -10384,13 +10448,13 @@
         <x:v>442</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-110</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G145" s="1" t="s">
         <x:v>440</x:v>
       </x:c>
       <x:c r="H145" s="1">
-        <x:v>5170</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:8">
@@ -10398,10 +10462,10 @@
         <x:v>443</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
         <x:v>444</x:v>
@@ -10410,13 +10474,13 @@
         <x:v>445</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
         <x:v>443</x:v>
       </x:c>
       <x:c r="H146" s="1">
-        <x:v>6000</x:v>
+        <x:v>18414</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:8">
@@ -10424,10 +10488,10 @@
         <x:v>446</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
         <x:v>447</x:v>
@@ -10436,13 +10500,13 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-110</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="H147" s="1">
-        <x:v>10972</x:v>
+        <x:v>5170</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:8">
@@ -10462,13 +10526,13 @@
         <x:v>451</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
         <x:v>449</x:v>
       </x:c>
       <x:c r="H148" s="1">
-        <x:v>57350</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:8">
@@ -10476,10 +10540,10 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
         <x:v>453</x:v>
@@ -10494,38 +10558,38 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="H149" s="1">
-        <x:v>2500</x:v>
+        <x:v>10972</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:8">
       <x:c r="A150" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="H150" s="1">
-        <x:v>0</x:v>
+        <x:v>57350</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:8">
       <x:c r="A151" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
         <x:v>39</x:v>
@@ -10534,16 +10598,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F151" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="H151" s="1">
         <x:v>2500</x:v>
@@ -10551,25 +10615,25 @@
     </x:row>
     <x:row r="152" spans="1:8">
       <x:c r="A152" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F152" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="H152" s="1">
         <x:v>0</x:v>
@@ -10577,54 +10641,54 @@
     </x:row>
     <x:row r="153" spans="1:8">
       <x:c r="A153" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-5131</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="H153" s="1">
-        <x:v>83966</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:8">
       <x:c r="A154" s="1" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B154" s="1" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="C154" s="1" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D154" s="1" t="s">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="B154" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C154" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D154" s="1" t="s">
+      <x:c r="E154" s="1" t="s">
         <x:v>460</x:v>
-      </x:c>
-      <x:c r="E154" s="1" t="s">
-        <x:v>461</x:v>
       </x:c>
       <x:c r="F154" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="H154" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:8">
@@ -10632,10 +10696,10 @@
         <x:v>462</x:v>
       </x:c>
       <x:c r="B155" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
         <x:v>463</x:v>
@@ -10644,12 +10708,64 @@
         <x:v>464</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5131</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
         <x:v>462</x:v>
       </x:c>
       <x:c r="H155" s="1">
+        <x:v>83966</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:8">
+      <x:c r="A156" s="1" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B156" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C156" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D156" s="1" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="E156" s="1" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="F156" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G156" s="1" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="H156" s="1">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:8">
+      <x:c r="A157" s="1" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B157" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C157" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D157" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="E157" s="1" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="F157" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G157" s="1" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="H157" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -8478,7 +8478,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="H69" s="1">
-        <x:v>249781</x:v>
+        <x:v>249782</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:8">
@@ -8556,7 +8556,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>217522</x:v>
+        <x:v>222523</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:8">

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -213,6 +213,15 @@
   </x:si>
   <x:si>
     <x:t>BLUMENTHAL FOR SENATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOOKER, CORY A.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00540500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORY BOOKER FOR SENATE</x:t>
   </x:si>
   <x:si>
     <x:t>BOUSTANY, CHARLES W JR DR</x:t>
@@ -1517,8 +1526,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G209" totalsRowShown="0">
-  <x:autoFilter ref="A1:G209"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G210" totalsRowShown="0">
+  <x:autoFilter ref="A1:G210"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1533,8 +1542,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H157" totalsRowShown="0">
-  <x:autoFilter ref="A1:H157"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H158" totalsRowShown="0">
+  <x:autoFilter ref="A1:H158"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1837,7 +1846,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G209"/>
+  <x:dimension ref="A1:G210"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2269,10 +2278,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>67</x:v>
@@ -2281,15 +2290,15 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>-50</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G19" s="2">
-        <x:v>40602</x:v>
+        <x:v>46057</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>54</x:v>
@@ -2298,13 +2307,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>-1</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G20" s="2">
         <x:v>40602</x:v>
@@ -2321,10 +2330,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F21" s="1">
         <x:v>-1</x:v>
@@ -2335,7 +2344,7 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>54</x:v>
@@ -2344,13 +2353,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>-50</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G22" s="2">
         <x:v>40602</x:v>
@@ -2358,36 +2367,36 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="F23" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G23" s="2">
-        <x:v>44742</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>76</x:v>
@@ -2396,10 +2405,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G24" s="2">
-        <x:v>38807</x:v>
+        <x:v>44742</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
@@ -2407,10 +2416,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>79</x:v>
@@ -2419,10 +2428,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>-500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G25" s="2">
-        <x:v>42236</x:v>
+        <x:v>38807</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
@@ -2430,10 +2439,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>82</x:v>
@@ -2442,33 +2451,33 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G26" s="2">
-        <x:v>38096</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G27" s="2">
-        <x:v>38055</x:v>
+        <x:v>38096</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
@@ -2488,38 +2497,38 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-3500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G28" s="2">
-        <x:v>43342</x:v>
+        <x:v>38055</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-3500</x:v>
       </x:c>
       <x:c r="G29" s="2">
-        <x:v>43190</x:v>
+        <x:v>43342</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>90</x:v>
@@ -2528,27 +2537,27 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G30" s="2">
-        <x:v>39141</x:v>
+        <x:v>43190</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B31" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C31" s="1" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>95</x:v>
@@ -2557,10 +2566,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>-10</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G31" s="2">
-        <x:v>41213</x:v>
+        <x:v>39141</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
@@ -2568,33 +2577,33 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
+      <x:c r="E32" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="F32" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G32" s="2">
-        <x:v>42185</x:v>
+        <x:v>41213</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>103</x:v>
@@ -2603,15 +2612,15 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>-950</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G33" s="2">
-        <x:v>45077</x:v>
+        <x:v>42185</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>34</x:v>
@@ -2620,13 +2629,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>-475</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G34" s="2">
         <x:v>45077</x:v>
@@ -2634,7 +2643,7 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>34</x:v>
@@ -2643,13 +2652,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>-238</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G35" s="2">
         <x:v>45077</x:v>
@@ -2657,7 +2666,7 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>34</x:v>
@@ -2666,13 +2675,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>-95</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G36" s="2">
         <x:v>45077</x:v>
@@ -2680,7 +2689,7 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>34</x:v>
@@ -2689,13 +2698,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>-71</x:v>
+        <x:v>-95</x:v>
       </x:c>
       <x:c r="G37" s="2">
         <x:v>45077</x:v>
@@ -2703,7 +2712,7 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>34</x:v>
@@ -2712,13 +2721,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>-48</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="G38" s="2">
         <x:v>45077</x:v>
@@ -2726,7 +2735,7 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>34</x:v>
@@ -2735,13 +2744,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>-24</x:v>
+        <x:v>-48</x:v>
       </x:c>
       <x:c r="G39" s="2">
         <x:v>45077</x:v>
@@ -2752,33 +2761,33 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="C40" s="1" t="s">
+      <x:c r="E40" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="F40" s="1">
-        <x:v>-250</x:v>
+        <x:v>-24</x:v>
       </x:c>
       <x:c r="G40" s="2">
-        <x:v>39018</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="B41" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>111</x:v>
@@ -2787,10 +2796,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G41" s="2">
-        <x:v>41639</x:v>
+        <x:v>39018</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
@@ -2798,33 +2807,33 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C42" s="1" t="s">
+      <x:c r="E42" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>117</x:v>
-      </x:c>
       <x:c r="F42" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G42" s="2">
-        <x:v>41813</x:v>
+        <x:v>41639</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="B43" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C43" s="1" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>119</x:v>
@@ -2833,15 +2842,15 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G43" s="2">
-        <x:v>43799</x:v>
+        <x:v>41813</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>54</x:v>
@@ -2850,13 +2859,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>-200</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G44" s="2">
         <x:v>43799</x:v>
@@ -2864,7 +2873,7 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>54</x:v>
@@ -2873,13 +2882,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>-100</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G45" s="2">
         <x:v>43799</x:v>
@@ -2887,7 +2896,7 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>54</x:v>
@@ -2896,13 +2905,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>-50</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G46" s="2">
         <x:v>43799</x:v>
@@ -2913,10 +2922,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>122</x:v>
@@ -2925,10 +2934,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G47" s="2">
-        <x:v>40988</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
@@ -2936,10 +2945,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>125</x:v>
@@ -2948,10 +2957,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G48" s="2">
-        <x:v>40724</x:v>
+        <x:v>40988</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
@@ -2959,33 +2968,33 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="C49" s="1" t="s">
+      <x:c r="E49" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>131</x:v>
-      </x:c>
       <x:c r="F49" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G49" s="2">
-        <x:v>43646</x:v>
+        <x:v>40724</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
         <x:v>133</x:v>
@@ -2994,10 +3003,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G50" s="2">
-        <x:v>40420</x:v>
+        <x:v>43646</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
@@ -3017,10 +3026,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G51" s="2">
-        <x:v>38075</x:v>
+        <x:v>40420</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -3028,10 +3037,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
         <x:v>139</x:v>
@@ -3040,10 +3049,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G52" s="2">
-        <x:v>44880</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -3051,10 +3060,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
         <x:v>142</x:v>
@@ -3063,10 +3072,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>-95</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G53" s="2">
-        <x:v>45077</x:v>
+        <x:v>44880</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
@@ -3086,10 +3095,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>-2900</x:v>
+        <x:v>-95</x:v>
       </x:c>
       <x:c r="G54" s="2">
-        <x:v>44712</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
@@ -3097,10 +3106,10 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
         <x:v>148</x:v>
@@ -3109,10 +3118,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2900</x:v>
       </x:c>
       <x:c r="G55" s="2">
-        <x:v>39018</x:v>
+        <x:v>44712</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
@@ -3120,10 +3129,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
         <x:v>151</x:v>
@@ -3135,7 +3144,7 @@
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G56" s="2">
-        <x:v>40178</x:v>
+        <x:v>39018</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
@@ -3143,91 +3152,91 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C57" s="1" t="s">
+      <x:c r="E57" s="1" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="D57" s="1" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="E57" s="1" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="F57" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G57" s="2">
-        <x:v>37855</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="B58" s="1" t="s">
+      <x:c r="D58" s="1" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
+      <x:c r="E58" s="1" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="E58" s="1" t="s">
-        <x:v>162</x:v>
-      </x:c>
       <x:c r="F58" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G58" s="2">
-        <x:v>40543</x:v>
+        <x:v>37855</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C59" s="1" t="s">
+      <x:c r="D59" s="1" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>161</x:v>
-      </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G59" s="2">
-        <x:v>40390</x:v>
+        <x:v>40543</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B60" s="1" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="B60" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C60" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D60" s="1" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="E60" s="1" t="s">
-        <x:v>167</x:v>
-      </x:c>
       <x:c r="F60" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G60" s="2">
-        <x:v>38341</x:v>
+        <x:v>40390</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
@@ -3235,10 +3244,10 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
         <x:v>169</x:v>
@@ -3247,15 +3256,15 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>-10</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G61" s="2">
-        <x:v>42236</x:v>
+        <x:v>38341</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
         <x:v>54</x:v>
@@ -3264,21 +3273,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>-250</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G62" s="2">
-        <x:v>42535</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
         <x:v>54</x:v>
@@ -3287,13 +3296,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>-100</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G63" s="2">
         <x:v>42535</x:v>
@@ -3301,7 +3310,7 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
         <x:v>54</x:v>
@@ -3310,13 +3319,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>-25</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G64" s="2">
         <x:v>42535</x:v>
@@ -3324,13 +3333,13 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
         <x:v>174</x:v>
@@ -3339,10 +3348,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>-500</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G65" s="2">
-        <x:v>39783</x:v>
+        <x:v>42535</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
@@ -3350,56 +3359,56 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C66" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D66" s="1" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="C66" s="1" t="s">
+      <x:c r="E66" s="1" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="D66" s="1" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="E66" s="1" t="s">
-        <x:v>180</x:v>
-      </x:c>
       <x:c r="F66" s="1">
-        <x:v>-100</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G66" s="2">
-        <x:v>44018</x:v>
+        <x:v>39783</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F67" s="1">
         <x:v>-100</x:v>
       </x:c>
       <x:c r="G67" s="2">
-        <x:v>44021</x:v>
+        <x:v>44018</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B68" s="1" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C68" s="1" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="B68" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C68" s="1" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
         <x:v>182</x:v>
@@ -3408,10 +3417,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G68" s="2">
-        <x:v>39729</x:v>
+        <x:v>44021</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
@@ -3419,10 +3428,10 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
         <x:v>185</x:v>
@@ -3431,10 +3440,10 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>-1347</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G69" s="2">
-        <x:v>43535</x:v>
+        <x:v>39729</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
@@ -3442,10 +3451,10 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
         <x:v>188</x:v>
@@ -3454,15 +3463,15 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>-1700</x:v>
+        <x:v>-1347</x:v>
       </x:c>
       <x:c r="G70" s="2">
-        <x:v>45349</x:v>
+        <x:v>43535</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
         <x:v>34</x:v>
@@ -3471,10 +3480,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F71" s="1">
         <x:v>-575</x:v>
@@ -3485,7 +3494,7 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
         <x:v>34</x:v>
@@ -3494,10 +3503,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F72" s="1">
         <x:v>-200</x:v>
@@ -3508,7 +3517,7 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
         <x:v>34</x:v>
@@ -3517,13 +3526,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-1700</x:v>
       </x:c>
       <x:c r="G73" s="2">
         <x:v>45349</x:v>
@@ -3531,7 +3540,7 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
         <x:v>34</x:v>
@@ -3540,21 +3549,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>-3300</x:v>
       </x:c>
       <x:c r="G74" s="2">
-        <x:v>45356</x:v>
+        <x:v>45349</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
         <x:v>34</x:v>
@@ -3563,13 +3572,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G75" s="2">
         <x:v>45356</x:v>
@@ -3577,7 +3586,7 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
         <x:v>34</x:v>
@@ -3586,13 +3595,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>-1667</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G76" s="2">
         <x:v>45356</x:v>
@@ -3603,10 +3612,10 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
         <x:v>191</x:v>
@@ -3615,10 +3624,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>-50</x:v>
+        <x:v>-1667</x:v>
       </x:c>
       <x:c r="G77" s="2">
-        <x:v>42236</x:v>
+        <x:v>45356</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
@@ -3626,10 +3635,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>194</x:v>
@@ -3638,10 +3647,10 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G78" s="2">
-        <x:v>45698</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
@@ -3661,10 +3670,10 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>-2900</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G79" s="2">
-        <x:v>44662</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
@@ -3684,10 +3693,10 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2900</x:v>
       </x:c>
       <x:c r="G80" s="2">
-        <x:v>45980</x:v>
+        <x:v>44662</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
@@ -3695,10 +3704,10 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
         <x:v>203</x:v>
@@ -3707,10 +3716,10 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G81" s="2">
-        <x:v>38184</x:v>
+        <x:v>45980</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
@@ -3718,10 +3727,10 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
         <x:v>206</x:v>
@@ -3730,15 +3739,15 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G82" s="2">
-        <x:v>43410</x:v>
+        <x:v>38184</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
         <x:v>54</x:v>
@@ -3747,13 +3756,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>-20</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G83" s="2">
         <x:v>43410</x:v>
@@ -3764,10 +3773,10 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
         <x:v>209</x:v>
@@ -3776,10 +3785,10 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G84" s="2">
-        <x:v>42017</x:v>
+        <x:v>43410</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
@@ -3787,10 +3796,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
         <x:v>212</x:v>
@@ -3799,10 +3808,10 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G85" s="2">
-        <x:v>38764</x:v>
+        <x:v>42017</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
@@ -3810,10 +3819,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
         <x:v>215</x:v>
@@ -3822,10 +3831,10 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G86" s="2">
-        <x:v>41284</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
@@ -3833,10 +3842,10 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
         <x:v>218</x:v>
@@ -3845,10 +3854,10 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G87" s="2">
-        <x:v>44893</x:v>
+        <x:v>41284</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
@@ -3856,10 +3865,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
         <x:v>221</x:v>
@@ -3868,10 +3877,10 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>-25</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G88" s="2">
-        <x:v>41711</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
@@ -3879,10 +3888,10 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
         <x:v>224</x:v>
@@ -3891,10 +3900,10 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G89" s="2">
-        <x:v>45698</x:v>
+        <x:v>41711</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
@@ -3902,10 +3911,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
         <x:v>227</x:v>
@@ -3914,10 +3923,10 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G90" s="2">
-        <x:v>39813</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
@@ -3925,10 +3934,10 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
         <x:v>230</x:v>
@@ -3937,10 +3946,10 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G91" s="2">
-        <x:v>46044</x:v>
+        <x:v>39813</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
@@ -3948,33 +3957,33 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C92" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D92" s="1" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C92" s="1" t="s">
+      <x:c r="E92" s="1" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="D92" s="1" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="E92" s="1" t="s">
-        <x:v>236</x:v>
-      </x:c>
       <x:c r="F92" s="1">
-        <x:v>-2800</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G92" s="2">
-        <x:v>41893</x:v>
+        <x:v>46044</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B93" s="1" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="C93" s="1" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="B93" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C93" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
         <x:v>238</x:v>
@@ -3983,10 +3992,10 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2800</x:v>
       </x:c>
       <x:c r="G93" s="2">
-        <x:v>38717</x:v>
+        <x:v>41893</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
@@ -3994,10 +4003,10 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
         <x:v>241</x:v>
@@ -4006,10 +4015,10 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G94" s="2">
-        <x:v>46051</x:v>
+        <x:v>38717</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
@@ -4017,10 +4026,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
         <x:v>244</x:v>
@@ -4029,10 +4038,10 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G95" s="2">
-        <x:v>45617</x:v>
+        <x:v>46051</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
@@ -4040,10 +4049,10 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
         <x:v>247</x:v>
@@ -4052,15 +4061,15 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G96" s="2">
-        <x:v>40602</x:v>
+        <x:v>45617</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
         <x:v>54</x:v>
@@ -4069,13 +4078,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G97" s="2">
         <x:v>40602</x:v>
@@ -4086,10 +4095,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
         <x:v>250</x:v>
@@ -4098,10 +4107,10 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G98" s="2">
-        <x:v>44727</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
@@ -4109,10 +4118,10 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
         <x:v>253</x:v>
@@ -4121,10 +4130,10 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G99" s="2">
-        <x:v>38990</x:v>
+        <x:v>44727</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
@@ -4132,10 +4141,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
         <x:v>256</x:v>
@@ -4144,10 +4153,10 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G100" s="2">
-        <x:v>38292</x:v>
+        <x:v>38990</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
@@ -4155,10 +4164,10 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
         <x:v>259</x:v>
@@ -4167,10 +4176,10 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G101" s="2">
-        <x:v>39512</x:v>
+        <x:v>38292</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
@@ -4178,10 +4187,10 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
         <x:v>262</x:v>
@@ -4190,10 +4199,10 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G102" s="2">
-        <x:v>45517</x:v>
+        <x:v>39512</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
@@ -4201,10 +4210,10 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
         <x:v>265</x:v>
@@ -4213,10 +4222,10 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G103" s="2">
-        <x:v>40178</x:v>
+        <x:v>45517</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
@@ -4224,10 +4233,10 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
         <x:v>268</x:v>
@@ -4236,15 +4245,15 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G104" s="2">
-        <x:v>45533</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
         <x:v>34</x:v>
@@ -4253,13 +4262,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>-9</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G105" s="2">
         <x:v>45533</x:v>
@@ -4267,7 +4276,7 @@
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
         <x:v>34</x:v>
@@ -4276,13 +4285,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>-1</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G106" s="2">
         <x:v>45533</x:v>
@@ -4293,10 +4302,10 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
         <x:v>271</x:v>
@@ -4305,10 +4314,10 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G107" s="2">
-        <x:v>44893</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
@@ -4316,10 +4325,10 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
         <x:v>274</x:v>
@@ -4328,10 +4337,10 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-475</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G108" s="2">
-        <x:v>45077</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
@@ -4339,10 +4348,10 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
         <x:v>277</x:v>
@@ -4351,10 +4360,10 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-250</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G109" s="2">
-        <x:v>43799</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
@@ -4362,10 +4371,10 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
         <x:v>280</x:v>
@@ -4374,10 +4383,10 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G110" s="2">
-        <x:v>37855</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
@@ -4385,10 +4394,10 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
         <x:v>283</x:v>
@@ -4397,10 +4406,10 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G111" s="2">
-        <x:v>44716</x:v>
+        <x:v>37855</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
@@ -4408,10 +4417,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
         <x:v>286</x:v>
@@ -4420,10 +4429,10 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G112" s="2">
-        <x:v>42004</x:v>
+        <x:v>44716</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
@@ -4431,10 +4440,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
         <x:v>289</x:v>
@@ -4443,33 +4452,33 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G113" s="2">
-        <x:v>43167</x:v>
+        <x:v>42004</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F114" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G114" s="2">
-        <x:v>44893</x:v>
+        <x:v>43167</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7">
@@ -4477,68 +4486,68 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F115" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G115" s="2">
-        <x:v>43167</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F116" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G116" s="2">
-        <x:v>44893</x:v>
+        <x:v>43167</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="1" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B117" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C117" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D117" s="1" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="B117" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C117" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D117" s="1" t="s">
+      <x:c r="E117" s="1" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="E117" s="1" t="s">
-        <x:v>294</x:v>
-      </x:c>
       <x:c r="F117" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G117" s="2">
-        <x:v>40602</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
@@ -4546,10 +4555,10 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
         <x:v>296</x:v>
@@ -4558,10 +4567,10 @@
         <x:v>297</x:v>
       </x:c>
       <x:c r="F118" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G118" s="2">
-        <x:v>40422</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
@@ -4569,10 +4578,10 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
         <x:v>299</x:v>
@@ -4581,10 +4590,10 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="F119" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G119" s="2">
-        <x:v>42818</x:v>
+        <x:v>40422</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7">
@@ -4592,10 +4601,10 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
         <x:v>302</x:v>
@@ -4604,10 +4613,10 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G120" s="2">
-        <x:v>45107</x:v>
+        <x:v>42818</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
@@ -4615,10 +4624,10 @@
         <x:v>304</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
         <x:v>305</x:v>
@@ -4627,10 +4636,10 @@
         <x:v>306</x:v>
       </x:c>
       <x:c r="F121" s="1">
-        <x:v>-1</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G121" s="2">
-        <x:v>45408</x:v>
+        <x:v>45107</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7">
@@ -4638,10 +4647,10 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="B122" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
         <x:v>308</x:v>
@@ -4650,10 +4659,10 @@
         <x:v>309</x:v>
       </x:c>
       <x:c r="F122" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G122" s="2">
-        <x:v>43390</x:v>
+        <x:v>45408</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:7">
@@ -4661,33 +4670,33 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C123" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D123" s="1" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="C123" s="1" t="s">
+      <x:c r="E123" s="1" t="s">
         <x:v>312</x:v>
-      </x:c>
-      <x:c r="D123" s="1" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="E123" s="1" t="s">
-        <x:v>314</x:v>
       </x:c>
       <x:c r="F123" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G123" s="2">
-        <x:v>43282</x:v>
+        <x:v>43390</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="1" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B124" s="1" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="C124" s="1" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="B124" s="1" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C124" s="1" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
         <x:v>316</x:v>
@@ -4696,33 +4705,33 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="F124" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G124" s="2">
-        <x:v>44013</x:v>
+        <x:v>43282</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F125" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G125" s="2">
-        <x:v>44022</x:v>
+        <x:v>44013</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:7">
@@ -4730,33 +4739,33 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C126" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D126" s="1" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="C126" s="1" t="s">
+      <x:c r="E126" s="1" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="D126" s="1" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="E126" s="1" t="s">
-        <x:v>322</x:v>
-      </x:c>
       <x:c r="F126" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G126" s="2">
-        <x:v>41926</x:v>
+        <x:v>44022</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7">
       <x:c r="A127" s="1" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B127" s="1" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="C127" s="1" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="B127" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C127" s="1" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
         <x:v>324</x:v>
@@ -4765,10 +4774,10 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="F127" s="1">
-        <x:v>-20</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G127" s="2">
-        <x:v>41698</x:v>
+        <x:v>41926</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7">
@@ -4776,10 +4785,10 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
         <x:v>327</x:v>
@@ -4788,10 +4797,10 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="F128" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G128" s="2">
-        <x:v>45484</x:v>
+        <x:v>41698</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
@@ -4799,10 +4808,10 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
         <x:v>330</x:v>
@@ -4811,15 +4820,15 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G129" s="2">
-        <x:v>45957</x:v>
+        <x:v>45484</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
         <x:v>34</x:v>
@@ -4828,21 +4837,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>-1650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G130" s="2">
-        <x:v>45959</x:v>
+        <x:v>45957</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
         <x:v>34</x:v>
@@ -4851,21 +4860,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F131" s="1">
         <x:v>-1650</x:v>
       </x:c>
       <x:c r="G131" s="2">
-        <x:v>45977</x:v>
+        <x:v>45959</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
         <x:v>34</x:v>
@@ -4874,13 +4883,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="G132" s="2">
         <x:v>45977</x:v>
@@ -4888,7 +4897,7 @@
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
         <x:v>34</x:v>
@@ -4897,13 +4906,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G133" s="2">
         <x:v>45977</x:v>
@@ -4911,7 +4920,7 @@
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
         <x:v>34</x:v>
@@ -4920,13 +4929,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-1800</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G134" s="2">
         <x:v>45977</x:v>
@@ -4934,7 +4943,7 @@
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
         <x:v>34</x:v>
@@ -4943,13 +4952,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F135" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-36</x:v>
       </x:c>
       <x:c r="G135" s="2">
         <x:v>45977</x:v>
@@ -4957,7 +4966,7 @@
     </x:row>
     <x:row r="136" spans="1:7">
       <x:c r="A136" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
         <x:v>34</x:v>
@@ -4966,13 +4975,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F136" s="1">
-        <x:v>-750</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G136" s="2">
         <x:v>45977</x:v>
@@ -4980,7 +4989,7 @@
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
         <x:v>34</x:v>
@@ -4989,13 +4998,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-36</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="G137" s="2">
         <x:v>45977</x:v>
@@ -5003,7 +5012,7 @@
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
         <x:v>34</x:v>
@@ -5012,13 +5021,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-9</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="G138" s="2">
         <x:v>45977</x:v>
@@ -5026,7 +5035,7 @@
     </x:row>
     <x:row r="139" spans="1:7">
       <x:c r="A139" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
         <x:v>34</x:v>
@@ -5035,13 +5044,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-3</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G139" s="2">
         <x:v>45977</x:v>
@@ -5049,7 +5058,7 @@
     </x:row>
     <x:row r="140" spans="1:7">
       <x:c r="A140" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
         <x:v>34</x:v>
@@ -5058,13 +5067,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-2</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G140" s="2">
         <x:v>45977</x:v>
@@ -5072,7 +5081,7 @@
     </x:row>
     <x:row r="141" spans="1:7">
       <x:c r="A141" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
         <x:v>34</x:v>
@@ -5081,13 +5090,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-1</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G141" s="2">
         <x:v>45977</x:v>
@@ -5095,7 +5104,7 @@
     </x:row>
     <x:row r="142" spans="1:7">
       <x:c r="A142" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
         <x:v>34</x:v>
@@ -5104,16 +5113,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-1800</x:v>
       </x:c>
       <x:c r="G142" s="2">
-        <x:v>45980</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:7">
@@ -5121,10 +5130,10 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
         <x:v>333</x:v>
@@ -5133,10 +5142,10 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-800</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G143" s="2">
-        <x:v>40602</x:v>
+        <x:v>45980</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:7">
@@ -5144,10 +5153,10 @@
         <x:v>335</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
         <x:v>336</x:v>
@@ -5156,10 +5165,10 @@
         <x:v>337</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="G144" s="2">
-        <x:v>37736</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:7">
@@ -5167,10 +5176,10 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
         <x:v>339</x:v>
@@ -5179,10 +5188,10 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G145" s="2">
-        <x:v>39810</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:7">
@@ -5190,10 +5199,10 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
         <x:v>342</x:v>
@@ -5202,10 +5211,10 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-300</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G146" s="2">
-        <x:v>44767</x:v>
+        <x:v>39810</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:7">
@@ -5213,10 +5222,10 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
         <x:v>345</x:v>
@@ -5225,10 +5234,10 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G147" s="2">
-        <x:v>41010</x:v>
+        <x:v>44767</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:7">
@@ -5236,10 +5245,10 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
         <x:v>348</x:v>
@@ -5251,7 +5260,7 @@
         <x:v>-2500</x:v>
       </x:c>
       <x:c r="G148" s="2">
-        <x:v>41840</x:v>
+        <x:v>41010</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
@@ -5259,10 +5268,10 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
         <x:v>351</x:v>
@@ -5271,10 +5280,10 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-100</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G149" s="2">
-        <x:v>40602</x:v>
+        <x:v>41840</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:7">
@@ -5282,10 +5291,10 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
         <x:v>354</x:v>
@@ -5294,10 +5303,10 @@
         <x:v>355</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-9</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G150" s="2">
-        <x:v>45972</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
@@ -5305,10 +5314,10 @@
         <x:v>356</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
         <x:v>357</x:v>
@@ -5317,15 +5326,15 @@
         <x:v>358</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G151" s="2">
-        <x:v>40602</x:v>
+        <x:v>45972</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
         <x:v>54</x:v>
@@ -5334,13 +5343,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G152" s="2">
         <x:v>40602</x:v>
@@ -5348,7 +5357,7 @@
     </x:row>
     <x:row r="153" spans="1:7">
       <x:c r="A153" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
         <x:v>54</x:v>
@@ -5357,13 +5366,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G153" s="2">
         <x:v>40602</x:v>
@@ -5371,7 +5380,7 @@
     </x:row>
     <x:row r="154" spans="1:7">
       <x:c r="A154" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
         <x:v>54</x:v>
@@ -5380,13 +5389,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>-50</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G154" s="2">
         <x:v>40602</x:v>
@@ -5394,7 +5403,7 @@
     </x:row>
     <x:row r="155" spans="1:7">
       <x:c r="A155" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B155" s="1" t="s">
         <x:v>54</x:v>
@@ -5403,13 +5412,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>-5</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G155" s="2">
         <x:v>40602</x:v>
@@ -5432,7 +5441,7 @@
         <x:v>361</x:v>
       </x:c>
       <x:c r="F156" s="1">
-        <x:v>-250</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="G156" s="2">
         <x:v>40602</x:v>
@@ -5443,45 +5452,45 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="F157" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G157" s="2">
-        <x:v>38075</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:7">
       <x:c r="A158" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F158" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G158" s="2">
-        <x:v>41455</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:7">
@@ -5489,10 +5498,10 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
         <x:v>367</x:v>
@@ -5501,10 +5510,10 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="F159" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G159" s="2">
-        <x:v>45698</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:7">
@@ -5512,10 +5521,10 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
         <x:v>370</x:v>
@@ -5527,7 +5536,7 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G160" s="2">
-        <x:v>43646</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:7">
@@ -5535,10 +5544,10 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="B161" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
         <x:v>373</x:v>
@@ -5547,10 +5556,10 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="F161" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G161" s="2">
-        <x:v>39940</x:v>
+        <x:v>43646</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:7">
@@ -5558,10 +5567,10 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="B162" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
         <x:v>376</x:v>
@@ -5570,10 +5579,10 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="F162" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G162" s="2">
-        <x:v>41455</x:v>
+        <x:v>39940</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:7">
@@ -5581,10 +5590,10 @@
         <x:v>378</x:v>
       </x:c>
       <x:c r="B163" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
         <x:v>379</x:v>
@@ -5593,10 +5602,10 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="F163" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G163" s="2">
-        <x:v>38322</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:7">
@@ -5616,7 +5625,7 @@
         <x:v>383</x:v>
       </x:c>
       <x:c r="F164" s="1">
-        <x:v>-250</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G164" s="2">
         <x:v>38322</x:v>
@@ -5627,10 +5636,10 @@
         <x:v>384</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
         <x:v>385</x:v>
@@ -5639,30 +5648,30 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="F165" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G165" s="2">
-        <x:v>44377</x:v>
+        <x:v>38322</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:7">
       <x:c r="A166" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="F166" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G166" s="2">
         <x:v>44377</x:v>
@@ -5673,10 +5682,10 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
         <x:v>388</x:v>
@@ -5685,10 +5694,10 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="F167" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G167" s="2">
-        <x:v>40682</x:v>
+        <x:v>44377</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:7">
@@ -5696,10 +5705,10 @@
         <x:v>390</x:v>
       </x:c>
       <x:c r="B168" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
         <x:v>391</x:v>
@@ -5708,10 +5717,10 @@
         <x:v>392</x:v>
       </x:c>
       <x:c r="F168" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G168" s="2">
-        <x:v>39318</x:v>
+        <x:v>40682</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:7">
@@ -5719,10 +5728,10 @@
         <x:v>393</x:v>
       </x:c>
       <x:c r="B169" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
         <x:v>394</x:v>
@@ -5731,10 +5740,10 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="F169" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G169" s="2">
-        <x:v>45879</x:v>
+        <x:v>39318</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:7">
@@ -5742,27 +5751,27 @@
         <x:v>396</x:v>
       </x:c>
       <x:c r="B170" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D170" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="F170" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G170" s="2">
-        <x:v>38075</x:v>
+        <x:v>45879</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:7">
       <x:c r="A171" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B171" s="1" t="s">
         <x:v>39</x:v>
@@ -5771,16 +5780,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D171" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F171" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G171" s="2">
-        <x:v>38764</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:7">
@@ -5788,10 +5797,10 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="B172" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
         <x:v>401</x:v>
@@ -5803,12 +5812,12 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G172" s="2">
-        <x:v>43201</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:7">
       <x:c r="A173" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
         <x:v>54</x:v>
@@ -5817,13 +5826,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F173" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G173" s="2">
         <x:v>43201</x:v>
@@ -5831,7 +5840,7 @@
     </x:row>
     <x:row r="174" spans="1:7">
       <x:c r="A174" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
         <x:v>54</x:v>
@@ -5840,13 +5849,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F174" s="1">
-        <x:v>-200</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G174" s="2">
         <x:v>43201</x:v>
@@ -5854,7 +5863,7 @@
     </x:row>
     <x:row r="175" spans="1:7">
       <x:c r="A175" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B175" s="1" t="s">
         <x:v>54</x:v>
@@ -5863,13 +5872,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D175" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F175" s="1">
-        <x:v>-100</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G175" s="2">
         <x:v>43201</x:v>
@@ -5877,25 +5886,25 @@
     </x:row>
     <x:row r="176" spans="1:7">
       <x:c r="A176" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B176" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F176" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G176" s="2">
-        <x:v>39777</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:7">
@@ -5903,10 +5912,10 @@
         <x:v>403</x:v>
       </x:c>
       <x:c r="B177" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
         <x:v>404</x:v>
@@ -5915,10 +5924,10 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="F177" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G177" s="2">
-        <x:v>43465</x:v>
+        <x:v>39777</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:7">
@@ -5926,10 +5935,10 @@
         <x:v>406</x:v>
       </x:c>
       <x:c r="B178" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
         <x:v>407</x:v>
@@ -5941,7 +5950,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G178" s="2">
-        <x:v>39010</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:7">
@@ -5949,10 +5958,10 @@
         <x:v>409</x:v>
       </x:c>
       <x:c r="B179" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
         <x:v>410</x:v>
@@ -5961,10 +5970,10 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="F179" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G179" s="2">
-        <x:v>42783</x:v>
+        <x:v>39010</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:7">
@@ -5984,10 +5993,10 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="F180" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G180" s="2">
-        <x:v>45692</x:v>
+        <x:v>42783</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:7">
@@ -5995,10 +6004,10 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B181" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
         <x:v>416</x:v>
@@ -6007,10 +6016,10 @@
         <x:v>417</x:v>
       </x:c>
       <x:c r="F181" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G181" s="2">
-        <x:v>43799</x:v>
+        <x:v>45692</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:7">
@@ -6018,45 +6027,45 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B182" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="F182" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G182" s="2">
-        <x:v>38075</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:7">
       <x:c r="A183" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B183" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F183" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G183" s="2">
-        <x:v>45698</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:7">
@@ -6079,7 +6088,7 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G184" s="2">
-        <x:v>45665</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:7">
@@ -6087,10 +6096,10 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B185" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
         <x:v>426</x:v>
@@ -6099,10 +6108,10 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F185" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G185" s="2">
-        <x:v>40724</x:v>
+        <x:v>45665</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:7">
@@ -6110,10 +6119,10 @@
         <x:v>428</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
         <x:v>429</x:v>
@@ -6122,10 +6131,10 @@
         <x:v>430</x:v>
       </x:c>
       <x:c r="F186" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G186" s="2">
-        <x:v>46000</x:v>
+        <x:v>40724</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:7">
@@ -6133,10 +6142,10 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B187" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
         <x:v>432</x:v>
@@ -6145,10 +6154,10 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="F187" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G187" s="2">
-        <x:v>43465</x:v>
+        <x:v>46000</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:7">
@@ -6156,10 +6165,10 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B188" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
         <x:v>435</x:v>
@@ -6168,10 +6177,10 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="F188" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G188" s="2">
-        <x:v>44845</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:7">
@@ -6179,10 +6188,10 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="B189" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
         <x:v>438</x:v>
@@ -6191,10 +6200,10 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="F189" s="1">
-        <x:v>-300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G189" s="2">
-        <x:v>44645</x:v>
+        <x:v>44845</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
@@ -6202,10 +6211,10 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B190" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C190" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
         <x:v>441</x:v>
@@ -6214,33 +6223,33 @@
         <x:v>442</x:v>
       </x:c>
       <x:c r="F190" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G190" s="2">
-        <x:v>41900</x:v>
+        <x:v>44645</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
       <x:c r="A191" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F191" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G191" s="2">
-        <x:v>41813</x:v>
+        <x:v>41900</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:7">
@@ -6248,10 +6257,10 @@
         <x:v>443</x:v>
       </x:c>
       <x:c r="B192" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
         <x:v>444</x:v>
@@ -6260,10 +6269,10 @@
         <x:v>445</x:v>
       </x:c>
       <x:c r="F192" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G192" s="2">
-        <x:v>43573</x:v>
+        <x:v>41813</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:7">
@@ -6283,15 +6292,15 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="F193" s="1">
-        <x:v>-100</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G193" s="2">
-        <x:v>42236</x:v>
+        <x:v>43573</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:7">
       <x:c r="A194" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B194" s="1" t="s">
         <x:v>54</x:v>
@@ -6300,13 +6309,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="F194" s="1">
-        <x:v>-10</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G194" s="2">
         <x:v>42236</x:v>
@@ -6317,10 +6326,10 @@
         <x:v>449</x:v>
       </x:c>
       <x:c r="B195" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C195" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
         <x:v>450</x:v>
@@ -6329,10 +6338,10 @@
         <x:v>451</x:v>
       </x:c>
       <x:c r="F195" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G195" s="2">
-        <x:v>44804</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:7">
@@ -6340,10 +6349,10 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="B196" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D196" s="1" t="s">
         <x:v>453</x:v>
@@ -6355,7 +6364,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G196" s="2">
-        <x:v>37787</x:v>
+        <x:v>44804</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:7">
@@ -6363,10 +6372,10 @@
         <x:v>455</x:v>
       </x:c>
       <x:c r="B197" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C197" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D197" s="1" t="s">
         <x:v>456</x:v>
@@ -6375,10 +6384,10 @@
         <x:v>457</x:v>
       </x:c>
       <x:c r="F197" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G197" s="2">
-        <x:v>45551</x:v>
+        <x:v>37787</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:7">
@@ -6386,10 +6395,10 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="B198" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C198" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D198" s="1" t="s">
         <x:v>459</x:v>
@@ -6398,33 +6407,33 @@
         <x:v>460</x:v>
       </x:c>
       <x:c r="F198" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G198" s="2">
-        <x:v>37736</x:v>
+        <x:v>45551</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:7">
       <x:c r="A199" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B199" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C199" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D199" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E199" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F199" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G199" s="2">
-        <x:v>41453</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
@@ -6432,73 +6441,73 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="B200" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E200" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F200" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G200" s="2">
-        <x:v>37736</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
       <x:c r="A201" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B201" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C201" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F201" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G201" s="2">
-        <x:v>41453</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="1" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B202" s="1" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="C202" s="1" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="D202" s="1" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="B202" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C202" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D202" s="1" t="s">
+      <x:c r="E202" s="1" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="E202" s="1" t="s">
-        <x:v>464</x:v>
-      </x:c>
       <x:c r="F202" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G202" s="2">
-        <x:v>45077</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
       <x:c r="A203" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B203" s="1" t="s">
         <x:v>34</x:v>
@@ -6507,13 +6516,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D203" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F203" s="1">
-        <x:v>-950</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G203" s="2">
         <x:v>45077</x:v>
@@ -6521,7 +6530,7 @@
     </x:row>
     <x:row r="204" spans="1:7">
       <x:c r="A204" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B204" s="1" t="s">
         <x:v>34</x:v>
@@ -6530,13 +6539,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D204" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E204" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F204" s="1">
-        <x:v>-713</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G204" s="2">
         <x:v>45077</x:v>
@@ -6544,7 +6553,7 @@
     </x:row>
     <x:row r="205" spans="1:7">
       <x:c r="A205" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B205" s="1" t="s">
         <x:v>34</x:v>
@@ -6553,13 +6562,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D205" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E205" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F205" s="1">
-        <x:v>-475</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G205" s="2">
         <x:v>45077</x:v>
@@ -6567,7 +6576,7 @@
     </x:row>
     <x:row r="206" spans="1:7">
       <x:c r="A206" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B206" s="1" t="s">
         <x:v>34</x:v>
@@ -6576,13 +6585,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F206" s="1">
-        <x:v>-238</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G206" s="2">
         <x:v>45077</x:v>
@@ -6593,10 +6602,10 @@
         <x:v>465</x:v>
       </x:c>
       <x:c r="B207" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
         <x:v>466</x:v>
@@ -6605,10 +6614,10 @@
         <x:v>467</x:v>
       </x:c>
       <x:c r="F207" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G207" s="2">
-        <x:v>40178</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:7">
@@ -6616,10 +6625,10 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B208" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D208" s="1" t="s">
         <x:v>469</x:v>
@@ -6628,32 +6637,55 @@
         <x:v>470</x:v>
       </x:c>
       <x:c r="F208" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G208" s="2">
-        <x:v>39629</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:7">
       <x:c r="A209" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B209" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C209" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D209" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="E209" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="F209" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G209" s="2">
+        <x:v>39629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:7">
+      <x:c r="A210" s="1" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B210" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C210" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D210" s="1" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="E210" s="1" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="F210" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G210" s="2">
         <x:v>39660</x:v>
       </x:c>
     </x:row>
@@ -6673,7 +6705,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H157"/>
+  <x:dimension ref="A1:H158"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="9" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -6704,13 +6736,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>476</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -7134,10 +7166,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>67</x:v>
@@ -7146,13 +7178,13 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>-51</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>8339</x:v>
+        <x:v>702091</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8">
@@ -7166,10 +7198,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F19" s="1">
         <x:v>-51</x:v>
@@ -7183,39 +7215,39 @@
     </x:row>
     <x:row r="20" spans="1:8">
       <x:c r="A20" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
+      <x:c r="F20" s="1">
+        <x:v>-51</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F20" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="H20" s="1">
-        <x:v>0</x:v>
+        <x:v>8339</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8">
       <x:c r="A21" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>76</x:v>
@@ -7224,13 +7256,13 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>9075</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8">
@@ -7238,10 +7270,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>79</x:v>
@@ -7250,13 +7282,13 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>-500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>51183</x:v>
+        <x:v>9075</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8">
@@ -7264,10 +7296,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>82</x:v>
@@ -7276,36 +7308,36 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>0</x:v>
+        <x:v>51183</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8">
       <x:c r="A24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H24" s="1">
         <x:v>0</x:v>
@@ -7316,10 +7348,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>85</x:v>
@@ -7328,7 +7360,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>-3500</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>84</x:v>
@@ -7339,25 +7371,25 @@
     </x:row>
     <x:row r="26" spans="1:8">
       <x:c r="A26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F26" s="1">
+        <x:v>-3500</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F26" s="1">
-        <x:v>-5000</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="H26" s="1">
         <x:v>0</x:v>
@@ -7365,7 +7397,7 @@
     </x:row>
     <x:row r="27" spans="1:8">
       <x:c r="A27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>90</x:v>
@@ -7374,16 +7406,16 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H27" s="1">
         <x:v>0</x:v>
@@ -7391,13 +7423,13 @@
     </x:row>
     <x:row r="28" spans="1:8">
       <x:c r="A28" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>95</x:v>
@@ -7406,13 +7438,13 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-10</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:8">
@@ -7420,36 +7452,36 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
+      <x:c r="E29" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="F29" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>5032</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:8">
       <x:c r="A30" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>103</x:v>
@@ -7458,13 +7490,13 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-1901</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>21265</x:v>
+        <x:v>5032</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:8">
@@ -7472,36 +7504,36 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="E31" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="F31" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1901</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>0</x:v>
+        <x:v>21265</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:8">
       <x:c r="A32" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>111</x:v>
@@ -7510,10 +7542,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>0</x:v>
@@ -7524,19 +7556,19 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>117</x:v>
-      </x:c>
       <x:c r="F33" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>113</x:v>
@@ -7547,13 +7579,13 @@
     </x:row>
     <x:row r="34" spans="1:8">
       <x:c r="A34" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C34" s="1" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>119</x:v>
@@ -7562,13 +7594,13 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>-850</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>26114</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:8">
@@ -7576,10 +7608,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>122</x:v>
@@ -7588,13 +7620,13 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-850</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>2400</x:v>
+        <x:v>26114</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:8">
@@ -7602,10 +7634,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>125</x:v>
@@ -7614,13 +7646,13 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>0</x:v>
+        <x:v>2400</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:8">
@@ -7628,36 +7660,36 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="C37" s="1" t="s">
+      <x:c r="E37" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>131</x:v>
-      </x:c>
       <x:c r="F37" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:8">
       <x:c r="A38" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="B38" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C38" s="1" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>133</x:v>
@@ -7666,13 +7698,13 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>1500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:8">
@@ -7692,13 +7724,13 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:8">
@@ -7706,10 +7738,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>139</x:v>
@@ -7718,13 +7750,13 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:8">
@@ -7732,10 +7764,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>142</x:v>
@@ -7744,13 +7776,13 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>-95</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>42275</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:8">
@@ -7770,13 +7802,13 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>-2900</x:v>
+        <x:v>-95</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>500</x:v>
+        <x:v>42275</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:8">
@@ -7784,10 +7816,10 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>148</x:v>
@@ -7796,13 +7828,13 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2900</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>1500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:8">
@@ -7810,10 +7842,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>151</x:v>
@@ -7828,7 +7860,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:8">
@@ -7836,16 +7868,16 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C45" s="1" t="s">
+      <x:c r="E45" s="1" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="F45" s="1">
         <x:v>-500</x:v>
@@ -7859,25 +7891,25 @@
     </x:row>
     <x:row r="46" spans="1:8">
       <x:c r="A46" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
+      <x:c r="D46" s="1" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="s">
+      <x:c r="E46" s="1" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>162</x:v>
-      </x:c>
       <x:c r="F46" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H46" s="1">
         <x:v>0</x:v>
@@ -7885,54 +7917,54 @@
     </x:row>
     <x:row r="47" spans="1:8">
       <x:c r="A47" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C47" s="1" t="s">
+      <x:c r="D47" s="1" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="D47" s="1" t="s">
+      <x:c r="E47" s="1" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F47" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F47" s="1">
-        <x:v>-5000</x:v>
-      </x:c>
-      <x:c r="G47" s="1" t="s">
-        <x:v>158</x:v>
-      </x:c>
       <x:c r="H47" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:8">
       <x:c r="A48" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>167</x:v>
-      </x:c>
       <x:c r="F48" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>0</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:8">
@@ -7940,10 +7972,10 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
         <x:v>169</x:v>
@@ -7952,18 +7984,18 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>-10</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>168</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>90014</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:8">
       <x:c r="A50" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
         <x:v>54</x:v>
@@ -7972,30 +8004,30 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F50" s="1">
+        <x:v>-10</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F50" s="1">
-        <x:v>-375</x:v>
-      </x:c>
-      <x:c r="G50" s="1" t="s">
-        <x:v>168</x:v>
-      </x:c>
       <x:c r="H50" s="1">
-        <x:v>42958</x:v>
+        <x:v>90014</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:8">
       <x:c r="A51" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
         <x:v>174</x:v>
@@ -8004,13 +8036,13 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>-500</x:v>
+        <x:v>-375</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>1500</x:v>
+        <x:v>42958</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:8">
@@ -8018,36 +8050,36 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="C52" s="1" t="s">
+      <x:c r="E52" s="1" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="D52" s="1" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>180</x:v>
-      </x:c>
       <x:c r="F52" s="1">
-        <x:v>-200</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>176</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>251266</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:8">
       <x:c r="A53" s="1" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="B53" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C53" s="1" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
         <x:v>182</x:v>
@@ -8056,13 +8088,13 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H53" s="1">
-        <x:v>10000</x:v>
+        <x:v>251266</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:8">
@@ -8070,10 +8102,10 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
         <x:v>185</x:v>
@@ -8082,13 +8114,13 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>-1347</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>184</x:v>
       </x:c>
       <x:c r="H54" s="1">
-        <x:v>35205</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:8">
@@ -8096,10 +8128,10 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
         <x:v>188</x:v>
@@ -8108,13 +8140,13 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>-13242</x:v>
+        <x:v>-1347</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>187</x:v>
       </x:c>
       <x:c r="H55" s="1">
-        <x:v>158894</x:v>
+        <x:v>35205</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:8">
@@ -8122,10 +8154,10 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
         <x:v>191</x:v>
@@ -8134,13 +8166,13 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>-50</x:v>
+        <x:v>-13242</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>190</x:v>
       </x:c>
       <x:c r="H56" s="1">
-        <x:v>35388</x:v>
+        <x:v>158894</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:8">
@@ -8148,10 +8180,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
         <x:v>194</x:v>
@@ -8160,13 +8192,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>193</x:v>
       </x:c>
       <x:c r="H57" s="1">
-        <x:v>71916</x:v>
+        <x:v>35388</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:8">
@@ -8186,13 +8218,13 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>-2900</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>196</x:v>
       </x:c>
       <x:c r="H58" s="1">
-        <x:v>25700</x:v>
+        <x:v>71916</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:8">
@@ -8212,13 +8244,13 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2900</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>199</x:v>
       </x:c>
       <x:c r="H59" s="1">
-        <x:v>622244</x:v>
+        <x:v>25700</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:8">
@@ -8226,10 +8258,10 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
         <x:v>203</x:v>
@@ -8238,13 +8270,13 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>202</x:v>
       </x:c>
       <x:c r="H60" s="1">
-        <x:v>3000</x:v>
+        <x:v>622244</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:8">
@@ -8252,10 +8284,10 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
         <x:v>206</x:v>
@@ -8264,13 +8296,13 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>-270</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="H61" s="1">
-        <x:v>13265</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:8">
@@ -8278,10 +8310,10 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
         <x:v>209</x:v>
@@ -8290,13 +8322,13 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-270</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>208</x:v>
       </x:c>
       <x:c r="H62" s="1">
-        <x:v>5000</x:v>
+        <x:v>13265</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:8">
@@ -8304,10 +8336,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
         <x:v>212</x:v>
@@ -8316,13 +8348,13 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>211</x:v>
       </x:c>
       <x:c r="H63" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:8">
@@ -8330,10 +8362,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
         <x:v>215</x:v>
@@ -8342,13 +8374,13 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>214</x:v>
       </x:c>
       <x:c r="H64" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:8">
@@ -8356,10 +8388,10 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
         <x:v>218</x:v>
@@ -8368,13 +8400,13 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>217</x:v>
       </x:c>
       <x:c r="H65" s="1">
-        <x:v>3461</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:8">
@@ -8382,10 +8414,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
         <x:v>221</x:v>
@@ -8394,13 +8426,13 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>-25</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>220</x:v>
       </x:c>
       <x:c r="H66" s="1">
-        <x:v>38904</x:v>
+        <x:v>3461</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:8">
@@ -8408,10 +8440,10 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
         <x:v>224</x:v>
@@ -8420,13 +8452,13 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>223</x:v>
       </x:c>
       <x:c r="H67" s="1">
-        <x:v>51848</x:v>
+        <x:v>38904</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:8">
@@ -8434,10 +8466,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
         <x:v>227</x:v>
@@ -8446,13 +8478,13 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="H68" s="1">
-        <x:v>0</x:v>
+        <x:v>51848</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:8">
@@ -8460,10 +8492,10 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
         <x:v>230</x:v>
@@ -8472,13 +8504,13 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>229</x:v>
       </x:c>
       <x:c r="H69" s="1">
-        <x:v>249782</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:8">
@@ -8486,36 +8518,36 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C70" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D70" s="1" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C70" s="1" t="s">
+      <x:c r="E70" s="1" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="D70" s="1" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="E70" s="1" t="s">
-        <x:v>236</x:v>
-      </x:c>
       <x:c r="F70" s="1">
-        <x:v>-2800</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>232</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>0</x:v>
+        <x:v>249782</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:8">
       <x:c r="A71" s="1" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B71" s="1" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="C71" s="1" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="B71" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C71" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
         <x:v>238</x:v>
@@ -8524,13 +8556,13 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2800</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H71" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:8">
@@ -8538,10 +8570,10 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
         <x:v>241</x:v>
@@ -8550,13 +8582,13 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>240</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>222523</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:8">
@@ -8564,10 +8596,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
         <x:v>244</x:v>
@@ -8576,13 +8608,13 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>243</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>2000</x:v>
+        <x:v>222523</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:8">
@@ -8590,10 +8622,10 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
         <x:v>247</x:v>
@@ -8602,13 +8634,13 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>-3400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
         <x:v>246</x:v>
       </x:c>
       <x:c r="H74" s="1">
-        <x:v>28982</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:8">
@@ -8616,10 +8648,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
         <x:v>250</x:v>
@@ -8628,13 +8660,13 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-3400</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>249</x:v>
       </x:c>
       <x:c r="H75" s="1">
-        <x:v>0</x:v>
+        <x:v>28982</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:8">
@@ -8642,10 +8674,10 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
         <x:v>253</x:v>
@@ -8654,13 +8686,13 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>252</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -8668,10 +8700,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
         <x:v>256</x:v>
@@ -8680,13 +8712,13 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>255</x:v>
       </x:c>
       <x:c r="H77" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:8">
@@ -8694,10 +8726,10 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>259</x:v>
@@ -8706,7 +8738,7 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>258</x:v>
@@ -8720,10 +8752,10 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>262</x:v>
@@ -8732,13 +8764,13 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>261</x:v>
       </x:c>
       <x:c r="H79" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:8">
@@ -8746,10 +8778,10 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
         <x:v>265</x:v>
@@ -8758,13 +8790,13 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>264</x:v>
       </x:c>
       <x:c r="H80" s="1">
-        <x:v>4000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:8">
@@ -8772,10 +8804,10 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
         <x:v>268</x:v>
@@ -8784,13 +8816,13 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>-510</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>267</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>42500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:8">
@@ -8798,10 +8830,10 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
         <x:v>271</x:v>
@@ -8810,13 +8842,13 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-510</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
         <x:v>270</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>2000</x:v>
+        <x:v>42500</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:8">
@@ -8824,10 +8856,10 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
         <x:v>274</x:v>
@@ -8836,13 +8868,13 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>-475</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
         <x:v>273</x:v>
       </x:c>
       <x:c r="H83" s="1">
-        <x:v>131385</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:8">
@@ -8850,10 +8882,10 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
         <x:v>277</x:v>
@@ -8862,13 +8894,13 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>-250</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
         <x:v>276</x:v>
       </x:c>
       <x:c r="H84" s="1">
-        <x:v>69371</x:v>
+        <x:v>131385</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:8">
@@ -8876,10 +8908,10 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
         <x:v>280</x:v>
@@ -8888,13 +8920,13 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>279</x:v>
       </x:c>
       <x:c r="H85" s="1">
-        <x:v>500</x:v>
+        <x:v>69371</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:8">
@@ -8902,10 +8934,10 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
         <x:v>283</x:v>
@@ -8914,13 +8946,13 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
         <x:v>282</x:v>
       </x:c>
       <x:c r="H86" s="1">
-        <x:v>111188</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:8">
@@ -8928,10 +8960,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
         <x:v>286</x:v>
@@ -8940,13 +8972,13 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
         <x:v>285</x:v>
       </x:c>
       <x:c r="H87" s="1">
-        <x:v>1000</x:v>
+        <x:v>111188</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:8">
@@ -8954,10 +8986,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
         <x:v>289</x:v>
@@ -8966,39 +8998,39 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
         <x:v>288</x:v>
       </x:c>
       <x:c r="H88" s="1">
-        <x:v>10000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:8">
       <x:c r="A89" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="H89" s="1">
-        <x:v>1150</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:8">
@@ -9006,77 +9038,77 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
         <x:v>291</x:v>
       </x:c>
       <x:c r="H90" s="1">
-        <x:v>10000</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:8">
       <x:c r="A91" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="H91" s="1">
-        <x:v>1150</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:8">
       <x:c r="A92" s="1" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B92" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C92" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D92" s="1" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="B92" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C92" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D92" s="1" t="s">
+      <x:c r="E92" s="1" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="E92" s="1" t="s">
+      <x:c r="F92" s="1">
+        <x:v>-1350</x:v>
+      </x:c>
+      <x:c r="G92" s="1" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="F92" s="1">
-        <x:v>-500</x:v>
-      </x:c>
-      <x:c r="G92" s="1" t="s">
-        <x:v>292</x:v>
-      </x:c>
       <x:c r="H92" s="1">
-        <x:v>33320</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:8">
@@ -9084,10 +9116,10 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
         <x:v>296</x:v>
@@ -9096,13 +9128,13 @@
         <x:v>297</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
         <x:v>295</x:v>
       </x:c>
       <x:c r="H93" s="1">
-        <x:v>0</x:v>
+        <x:v>33320</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:8">
@@ -9110,10 +9142,10 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
         <x:v>299</x:v>
@@ -9122,13 +9154,13 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
         <x:v>298</x:v>
       </x:c>
       <x:c r="H94" s="1">
-        <x:v>21095</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:8">
@@ -9136,10 +9168,10 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
         <x:v>302</x:v>
@@ -9148,13 +9180,13 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
         <x:v>301</x:v>
       </x:c>
       <x:c r="H95" s="1">
-        <x:v>0</x:v>
+        <x:v>21095</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:8">
@@ -9162,10 +9194,10 @@
         <x:v>304</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
         <x:v>305</x:v>
@@ -9174,13 +9206,13 @@
         <x:v>306</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>-1</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
         <x:v>304</x:v>
       </x:c>
       <x:c r="H96" s="1">
-        <x:v>26650</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:8">
@@ -9188,10 +9220,10 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
         <x:v>308</x:v>
@@ -9200,13 +9232,13 @@
         <x:v>309</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
         <x:v>307</x:v>
       </x:c>
       <x:c r="H97" s="1">
-        <x:v>5000</x:v>
+        <x:v>26650</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:8">
@@ -9214,16 +9246,16 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C98" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D98" s="1" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="C98" s="1" t="s">
+      <x:c r="E98" s="1" t="s">
         <x:v>312</x:v>
-      </x:c>
-      <x:c r="D98" s="1" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="E98" s="1" t="s">
-        <x:v>314</x:v>
       </x:c>
       <x:c r="F98" s="1">
         <x:v>-5000</x:v>
@@ -9232,18 +9264,18 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="H98" s="1">
-        <x:v>12000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:8">
       <x:c r="A99" s="1" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B99" s="1" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="C99" s="1" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="B99" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C99" s="1" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
         <x:v>316</x:v>
@@ -9255,33 +9287,33 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="H99" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:8">
       <x:c r="A100" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="H100" s="1">
         <x:v>0</x:v>
@@ -9292,36 +9324,36 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C101" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D101" s="1" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="C101" s="1" t="s">
+      <x:c r="E101" s="1" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="D101" s="1" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="E101" s="1" t="s">
-        <x:v>322</x:v>
-      </x:c>
       <x:c r="F101" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
         <x:v>318</x:v>
       </x:c>
       <x:c r="H101" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:8">
       <x:c r="A102" s="1" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B102" s="1" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="C102" s="1" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="B102" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C102" s="1" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
         <x:v>324</x:v>
@@ -9330,13 +9362,13 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>-20</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="H102" s="1">
-        <x:v>14900</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:8">
@@ -9344,10 +9376,10 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
         <x:v>327</x:v>
@@ -9356,13 +9388,13 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
         <x:v>326</x:v>
       </x:c>
       <x:c r="H103" s="1">
-        <x:v>5000</x:v>
+        <x:v>14900</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:8">
@@ -9370,10 +9402,10 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
         <x:v>330</x:v>
@@ -9382,13 +9414,13 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>-19701</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
         <x:v>329</x:v>
       </x:c>
       <x:c r="H104" s="1">
-        <x:v>49967</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:8">
@@ -9396,10 +9428,10 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
         <x:v>333</x:v>
@@ -9408,13 +9440,13 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>-800</x:v>
+        <x:v>-19701</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
         <x:v>332</x:v>
       </x:c>
       <x:c r="H105" s="1">
-        <x:v>58679</x:v>
+        <x:v>49967</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:8">
@@ -9422,10 +9454,10 @@
         <x:v>335</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
         <x:v>336</x:v>
@@ -9434,13 +9466,13 @@
         <x:v>337</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="H106" s="1">
-        <x:v>0</x:v>
+        <x:v>58679</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:8">
@@ -9448,10 +9480,10 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
         <x:v>339</x:v>
@@ -9460,13 +9492,13 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="H107" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:8">
@@ -9474,10 +9506,10 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
         <x:v>342</x:v>
@@ -9486,13 +9518,13 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-300</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="H108" s="1">
-        <x:v>36900</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:8">
@@ -9500,10 +9532,10 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
         <x:v>345</x:v>
@@ -9512,13 +9544,13 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
       <x:c r="H109" s="1">
-        <x:v>0</x:v>
+        <x:v>36900</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:8">
@@ -9526,10 +9558,10 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
         <x:v>348</x:v>
@@ -9552,10 +9584,10 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
         <x:v>351</x:v>
@@ -9564,13 +9596,13 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>-100</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
         <x:v>350</x:v>
       </x:c>
       <x:c r="H111" s="1">
-        <x:v>58000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:8">
@@ -9578,10 +9610,10 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
         <x:v>354</x:v>
@@ -9590,13 +9622,13 @@
         <x:v>355</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>-9</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
         <x:v>353</x:v>
       </x:c>
       <x:c r="H112" s="1">
-        <x:v>15349</x:v>
+        <x:v>58000</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:8">
@@ -9604,10 +9636,10 @@
         <x:v>356</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
         <x:v>357</x:v>
@@ -9616,13 +9648,13 @@
         <x:v>358</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>-4955</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
         <x:v>356</x:v>
       </x:c>
       <x:c r="H113" s="1">
-        <x:v>64475</x:v>
+        <x:v>15349</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:8">
@@ -9642,13 +9674,13 @@
         <x:v>361</x:v>
       </x:c>
       <x:c r="F114" s="1">
-        <x:v>-250</x:v>
+        <x:v>-4955</x:v>
       </x:c>
       <x:c r="G114" s="1" t="s">
         <x:v>359</x:v>
       </x:c>
       <x:c r="H114" s="1">
-        <x:v>42061</x:v>
+        <x:v>64475</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:8">
@@ -9656,48 +9688,48 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="F115" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G115" s="1" t="s">
         <x:v>362</x:v>
       </x:c>
       <x:c r="H115" s="1">
-        <x:v>0</x:v>
+        <x:v>42061</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:8">
       <x:c r="A116" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F116" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G116" s="1" t="s">
         <x:v>365</x:v>
-      </x:c>
-      <x:c r="F116" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G116" s="1" t="s">
-        <x:v>363</x:v>
       </x:c>
       <x:c r="H116" s="1">
         <x:v>0</x:v>
@@ -9708,10 +9740,10 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
         <x:v>367</x:v>
@@ -9720,13 +9752,13 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="F117" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G117" s="1" t="s">
         <x:v>366</x:v>
       </x:c>
       <x:c r="H117" s="1">
-        <x:v>7380</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:8">
@@ -9734,10 +9766,10 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
         <x:v>370</x:v>
@@ -9752,7 +9784,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H118" s="1">
-        <x:v>3000</x:v>
+        <x:v>7380</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:8">
@@ -9760,10 +9792,10 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
         <x:v>373</x:v>
@@ -9772,13 +9804,13 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="F119" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G119" s="1" t="s">
         <x:v>372</x:v>
       </x:c>
       <x:c r="H119" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:8">
@@ -9786,10 +9818,10 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
         <x:v>376</x:v>
@@ -9798,13 +9830,13 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G120" s="1" t="s">
         <x:v>375</x:v>
       </x:c>
       <x:c r="H120" s="1">
-        <x:v>2400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:8">
@@ -9812,10 +9844,10 @@
         <x:v>378</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
         <x:v>379</x:v>
@@ -9824,13 +9856,13 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="F121" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G121" s="1" t="s">
         <x:v>378</x:v>
       </x:c>
       <x:c r="H121" s="1">
-        <x:v>0</x:v>
+        <x:v>2400</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:8">
@@ -9850,13 +9882,13 @@
         <x:v>383</x:v>
       </x:c>
       <x:c r="F122" s="1">
-        <x:v>-250</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G122" s="1" t="s">
         <x:v>381</x:v>
       </x:c>
       <x:c r="H122" s="1">
-        <x:v>6727</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:8">
@@ -9864,10 +9896,10 @@
         <x:v>384</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
         <x:v>385</x:v>
@@ -9876,13 +9908,13 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="F123" s="1">
-        <x:v>-7500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G123" s="1" t="s">
         <x:v>384</x:v>
       </x:c>
       <x:c r="H123" s="1">
-        <x:v>5000</x:v>
+        <x:v>6727</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:8">
@@ -9890,10 +9922,10 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
         <x:v>388</x:v>
@@ -9902,13 +9934,13 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="F124" s="1">
-        <x:v>-500</x:v>
+        <x:v>-7500</x:v>
       </x:c>
       <x:c r="G124" s="1" t="s">
         <x:v>387</x:v>
       </x:c>
       <x:c r="H124" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:8">
@@ -9916,10 +9948,10 @@
         <x:v>390</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
         <x:v>391</x:v>
@@ -9928,13 +9960,13 @@
         <x:v>392</x:v>
       </x:c>
       <x:c r="F125" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G125" s="1" t="s">
         <x:v>390</x:v>
       </x:c>
       <x:c r="H125" s="1">
-        <x:v>2000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:8">
@@ -9942,10 +9974,10 @@
         <x:v>393</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
         <x:v>394</x:v>
@@ -9954,13 +9986,13 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="F126" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G126" s="1" t="s">
         <x:v>393</x:v>
       </x:c>
       <x:c r="H126" s="1">
-        <x:v>159727</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:8">
@@ -9968,30 +10000,30 @@
         <x:v>396</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="F127" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G127" s="1" t="s">
         <x:v>396</x:v>
       </x:c>
       <x:c r="H127" s="1">
-        <x:v>0</x:v>
+        <x:v>159727</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:8">
       <x:c r="A128" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
         <x:v>39</x:v>
@@ -10000,16 +10032,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F128" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G128" s="1" t="s">
         <x:v>399</x:v>
-      </x:c>
-      <x:c r="F128" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G128" s="1" t="s">
-        <x:v>397</x:v>
       </x:c>
       <x:c r="H128" s="1">
         <x:v>0</x:v>
@@ -10020,10 +10052,10 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
         <x:v>401</x:v>
@@ -10032,7 +10064,7 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G129" s="1" t="s">
         <x:v>400</x:v>
@@ -10043,28 +10075,28 @@
     </x:row>
     <x:row r="130" spans="1:8">
       <x:c r="A130" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>-1550</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G130" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="H130" s="1">
-        <x:v>193279</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:8">
@@ -10072,10 +10104,10 @@
         <x:v>403</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
         <x:v>404</x:v>
@@ -10084,13 +10116,13 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1550</x:v>
       </x:c>
       <x:c r="G131" s="1" t="s">
         <x:v>403</x:v>
       </x:c>
       <x:c r="H131" s="1">
-        <x:v>0</x:v>
+        <x:v>193279</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:8">
@@ -10098,10 +10130,10 @@
         <x:v>406</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
         <x:v>407</x:v>
@@ -10124,10 +10156,10 @@
         <x:v>409</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
         <x:v>410</x:v>
@@ -10136,13 +10168,13 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G133" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
       <x:c r="H133" s="1">
-        <x:v>19596</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:8">
@@ -10162,13 +10194,13 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G134" s="1" t="s">
         <x:v>412</x:v>
       </x:c>
       <x:c r="H134" s="1">
-        <x:v>17260</x:v>
+        <x:v>19596</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:8">
@@ -10176,10 +10208,10 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
         <x:v>416</x:v>
@@ -10188,13 +10220,13 @@
         <x:v>417</x:v>
       </x:c>
       <x:c r="F135" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G135" s="1" t="s">
         <x:v>415</x:v>
       </x:c>
       <x:c r="H135" s="1">
-        <x:v>6150</x:v>
+        <x:v>17260</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:8">
@@ -10202,51 +10234,51 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="F136" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G136" s="1" t="s">
         <x:v>418</x:v>
       </x:c>
       <x:c r="H136" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:8">
       <x:c r="A137" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F137" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G137" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="H137" s="1">
-        <x:v>32943</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:8">
@@ -10272,7 +10304,7 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="H138" s="1">
-        <x:v>41676</x:v>
+        <x:v>32943</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:8">
@@ -10280,10 +10312,10 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
         <x:v>426</x:v>
@@ -10292,13 +10324,13 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G139" s="1" t="s">
         <x:v>425</x:v>
       </x:c>
       <x:c r="H139" s="1">
-        <x:v>0</x:v>
+        <x:v>41676</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:8">
@@ -10306,10 +10338,10 @@
         <x:v>428</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
         <x:v>429</x:v>
@@ -10318,13 +10350,13 @@
         <x:v>430</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G140" s="1" t="s">
         <x:v>428</x:v>
       </x:c>
       <x:c r="H140" s="1">
-        <x:v>84497</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:8">
@@ -10332,10 +10364,10 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
         <x:v>432</x:v>
@@ -10344,13 +10376,13 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
         <x:v>431</x:v>
       </x:c>
       <x:c r="H141" s="1">
-        <x:v>0</x:v>
+        <x:v>84497</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:8">
@@ -10358,10 +10390,10 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
         <x:v>435</x:v>
@@ -10370,13 +10402,13 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
         <x:v>434</x:v>
       </x:c>
       <x:c r="H142" s="1">
-        <x:v>28400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:8">
@@ -10384,10 +10416,10 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
         <x:v>438</x:v>
@@ -10396,13 +10428,13 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
         <x:v>437</x:v>
       </x:c>
       <x:c r="H143" s="1">
-        <x:v>22566</x:v>
+        <x:v>28400</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:8">
@@ -10410,10 +10442,10 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
         <x:v>441</x:v>
@@ -10422,39 +10454,39 @@
         <x:v>442</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
         <x:v>440</x:v>
       </x:c>
       <x:c r="H144" s="1">
-        <x:v>3750</x:v>
+        <x:v>22566</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:8">
       <x:c r="A145" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G145" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="H145" s="1">
-        <x:v>10000</x:v>
+        <x:v>3750</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:8">
@@ -10462,10 +10494,10 @@
         <x:v>443</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
         <x:v>444</x:v>
@@ -10474,13 +10506,13 @@
         <x:v>445</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
         <x:v>443</x:v>
       </x:c>
       <x:c r="H146" s="1">
-        <x:v>18414</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:8">
@@ -10500,13 +10532,13 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-110</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="H147" s="1">
-        <x:v>5170</x:v>
+        <x:v>18414</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:8">
@@ -10514,10 +10546,10 @@
         <x:v>449</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
         <x:v>450</x:v>
@@ -10526,13 +10558,13 @@
         <x:v>451</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-110</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
         <x:v>449</x:v>
       </x:c>
       <x:c r="H148" s="1">
-        <x:v>6000</x:v>
+        <x:v>5170</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:8">
@@ -10540,10 +10572,10 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
         <x:v>453</x:v>
@@ -10558,7 +10590,7 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="H149" s="1">
-        <x:v>10972</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:8">
@@ -10566,10 +10598,10 @@
         <x:v>455</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
         <x:v>456</x:v>
@@ -10578,13 +10610,13 @@
         <x:v>457</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
         <x:v>455</x:v>
       </x:c>
       <x:c r="H150" s="1">
-        <x:v>57350</x:v>
+        <x:v>10972</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:8">
@@ -10592,10 +10624,10 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
         <x:v>459</x:v>
@@ -10604,39 +10636,39 @@
         <x:v>460</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
         <x:v>458</x:v>
       </x:c>
       <x:c r="H151" s="1">
-        <x:v>2500</x:v>
+        <x:v>57350</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:8">
       <x:c r="A152" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="H152" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:8">
@@ -10644,77 +10676,77 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
         <x:v>461</x:v>
       </x:c>
       <x:c r="H153" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:8">
       <x:c r="A154" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="H154" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:8">
       <x:c r="A155" s="1" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B155" s="1" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="C155" s="1" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="D155" s="1" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="B155" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C155" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D155" s="1" t="s">
+      <x:c r="E155" s="1" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="E155" s="1" t="s">
+      <x:c r="F155" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G155" s="1" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="F155" s="1">
-        <x:v>-5131</x:v>
-      </x:c>
-      <x:c r="G155" s="1" t="s">
-        <x:v>462</x:v>
-      </x:c>
       <x:c r="H155" s="1">
-        <x:v>83966</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:8">
@@ -10722,10 +10754,10 @@
         <x:v>465</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
         <x:v>466</x:v>
@@ -10734,13 +10766,13 @@
         <x:v>467</x:v>
       </x:c>
       <x:c r="F156" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5131</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
         <x:v>465</x:v>
       </x:c>
       <x:c r="H156" s="1">
-        <x:v>6000</x:v>
+        <x:v>83966</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:8">
@@ -10748,10 +10780,10 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
         <x:v>469</x:v>
@@ -10766,6 +10798,32 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="H157" s="1">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:8">
+      <x:c r="A158" s="1" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B158" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C158" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D158" s="1" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="E158" s="1" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="F158" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G158" s="1" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="H158" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -389,6 +389,15 @@
     <x:t>LESLIE COCKBURN FOR CONGRESS</x:t>
   </x:si>
   <x:si>
+    <x:t>COLE, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00379735</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLE FOR CONGRESS</x:t>
+  </x:si>
+  <x:si>
     <x:t>CORZINE, JON S</x:t>
   </x:si>
   <x:si>
@@ -704,6 +713,15 @@
     <x:t>CHRISSY HOULAHAN FOR CONGRESS</x:t>
   </x:si>
   <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00459297</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA FOR CONGRESS</x:t>
+  </x:si>
+  <x:si>
     <x:t>INHOFE, JAMES M. SEN.</x:t>
   </x:si>
   <x:si>
@@ -800,6 +818,15 @@
     <x:t>KERRY VICTORY 2004</x:t>
   </x:si>
   <x:si>
+    <x:t>KIGGANS, JENNIFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00776120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIGGANS FOR CONGRESS</x:t>
+  </x:si>
+  <x:si>
     <x:t>KILPATRICK, CAROLYN MS.</x:t>
   </x:si>
   <x:si>
@@ -872,6 +899,15 @@
     <x:t>LUCAS FOR CONGRESS 2000</x:t>
   </x:si>
   <x:si>
+    <x:t>MALLIOTAKIS, NICOLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00694778</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICOLE FOR NEW YORK</x:t>
+  </x:si>
+  <x:si>
     <x:t>MALONEY, CAROLYN B.</x:t>
   </x:si>
   <x:si>
@@ -1020,6 +1056,18 @@
   </x:si>
   <x:si>
     <x:t>SETH FOR MASSACHUSETTS, INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MULLIN, MARKWAYNE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00498345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MULLIN FOR AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MULLIN, MARKWAYNE MR.</x:t>
   </x:si>
   <x:si>
     <x:t>MURPHY, SCOTT M</x:t>
@@ -1526,8 +1574,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G210" totalsRowShown="0">
-  <x:autoFilter ref="A1:G210"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G228" totalsRowShown="0">
+  <x:autoFilter ref="A1:G228"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1542,8 +1590,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H158" totalsRowShown="0">
-  <x:autoFilter ref="A1:H158"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H163" totalsRowShown="0">
+  <x:autoFilter ref="A1:H163"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1846,7 +1894,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G210"/>
+  <x:dimension ref="A1:G228"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2945,10 +2993,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>125</x:v>
@@ -2957,10 +3005,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G48" s="2">
-        <x:v>40988</x:v>
+        <x:v>45630</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
@@ -2968,10 +3016,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
         <x:v>128</x:v>
@@ -2980,10 +3028,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G49" s="2">
-        <x:v>40724</x:v>
+        <x:v>40988</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
@@ -2991,33 +3039,33 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="C50" s="1" t="s">
+      <x:c r="E50" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="F50" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G50" s="2">
-        <x:v>43646</x:v>
+        <x:v>40724</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="B51" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C51" s="1" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
         <x:v>136</x:v>
@@ -3026,10 +3074,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G51" s="2">
-        <x:v>40420</x:v>
+        <x:v>43646</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -3049,10 +3097,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G52" s="2">
-        <x:v>38075</x:v>
+        <x:v>40420</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -3060,10 +3108,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
         <x:v>142</x:v>
@@ -3072,10 +3120,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G53" s="2">
-        <x:v>44880</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
@@ -3083,10 +3131,10 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
         <x:v>145</x:v>
@@ -3095,10 +3143,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>-95</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G54" s="2">
-        <x:v>45077</x:v>
+        <x:v>44880</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
@@ -3118,10 +3166,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>-2900</x:v>
+        <x:v>-95</x:v>
       </x:c>
       <x:c r="G55" s="2">
-        <x:v>44712</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
@@ -3129,10 +3177,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
         <x:v>151</x:v>
@@ -3141,10 +3189,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2900</x:v>
       </x:c>
       <x:c r="G56" s="2">
-        <x:v>39018</x:v>
+        <x:v>44712</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
@@ -3152,10 +3200,10 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
         <x:v>154</x:v>
@@ -3167,7 +3215,7 @@
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G57" s="2">
-        <x:v>40178</x:v>
+        <x:v>39018</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
@@ -3175,91 +3223,91 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
+      <x:c r="E58" s="1" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="E58" s="1" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="F58" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G58" s="2">
-        <x:v>37855</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B59" s="1" t="s">
+      <x:c r="D59" s="1" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="C59" s="1" t="s">
+      <x:c r="E59" s="1" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="E59" s="1" t="s">
-        <x:v>165</x:v>
-      </x:c>
       <x:c r="F59" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G59" s="2">
-        <x:v>40543</x:v>
+        <x:v>37855</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C60" s="1" t="s">
+      <x:c r="D60" s="1" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D60" s="1" t="s">
-        <x:v>164</x:v>
-      </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G60" s="2">
-        <x:v>40390</x:v>
+        <x:v>40543</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="B61" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C61" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D61" s="1" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="E61" s="1" t="s">
-        <x:v>170</x:v>
-      </x:c>
       <x:c r="F61" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G61" s="2">
-        <x:v>38341</x:v>
+        <x:v>40390</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
@@ -3267,10 +3315,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
         <x:v>172</x:v>
@@ -3279,15 +3327,15 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>-10</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G62" s="2">
-        <x:v>42236</x:v>
+        <x:v>38341</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
         <x:v>54</x:v>
@@ -3296,21 +3344,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>-250</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G63" s="2">
-        <x:v>42535</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
         <x:v>54</x:v>
@@ -3319,13 +3367,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>-100</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G64" s="2">
         <x:v>42535</x:v>
@@ -3333,7 +3381,7 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
         <x:v>54</x:v>
@@ -3342,13 +3390,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>-25</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G65" s="2">
         <x:v>42535</x:v>
@@ -3356,13 +3404,13 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
         <x:v>177</x:v>
@@ -3371,10 +3419,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>-500</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G66" s="2">
-        <x:v>39783</x:v>
+        <x:v>42535</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
@@ -3382,56 +3430,56 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="C67" s="1" t="s">
+      <x:c r="E67" s="1" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="D67" s="1" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="E67" s="1" t="s">
-        <x:v>183</x:v>
-      </x:c>
       <x:c r="F67" s="1">
-        <x:v>-100</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G67" s="2">
-        <x:v>44018</x:v>
+        <x:v>39783</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="F68" s="1">
         <x:v>-100</x:v>
       </x:c>
       <x:c r="G68" s="2">
-        <x:v>44021</x:v>
+        <x:v>44018</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B69" s="1" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="B69" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C69" s="1" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
         <x:v>185</x:v>
@@ -3440,10 +3488,10 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G69" s="2">
-        <x:v>39729</x:v>
+        <x:v>44021</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
@@ -3451,10 +3499,10 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
         <x:v>188</x:v>
@@ -3463,10 +3511,10 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>-1347</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G70" s="2">
-        <x:v>43535</x:v>
+        <x:v>39729</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
@@ -3474,10 +3522,10 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
         <x:v>191</x:v>
@@ -3486,15 +3534,15 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>-575</x:v>
+        <x:v>-1347</x:v>
       </x:c>
       <x:c r="G71" s="2">
-        <x:v>45349</x:v>
+        <x:v>43535</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
         <x:v>34</x:v>
@@ -3503,13 +3551,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>-200</x:v>
+        <x:v>-1700</x:v>
       </x:c>
       <x:c r="G72" s="2">
         <x:v>45349</x:v>
@@ -3517,7 +3565,7 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
         <x:v>34</x:v>
@@ -3526,13 +3574,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>-1700</x:v>
+        <x:v>-575</x:v>
       </x:c>
       <x:c r="G73" s="2">
         <x:v>45349</x:v>
@@ -3540,7 +3588,7 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
         <x:v>34</x:v>
@@ -3549,13 +3597,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G74" s="2">
         <x:v>45349</x:v>
@@ -3563,7 +3611,7 @@
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
         <x:v>34</x:v>
@@ -3572,21 +3620,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F75" s="1">
         <x:v>-3300</x:v>
       </x:c>
       <x:c r="G75" s="2">
-        <x:v>45356</x:v>
+        <x:v>45349</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
         <x:v>34</x:v>
@@ -3595,13 +3643,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G76" s="2">
         <x:v>45356</x:v>
@@ -3609,7 +3657,7 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
         <x:v>34</x:v>
@@ -3618,13 +3666,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>-1667</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G77" s="2">
         <x:v>45356</x:v>
@@ -3635,10 +3683,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>194</x:v>
@@ -3647,10 +3695,10 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>-50</x:v>
+        <x:v>-1667</x:v>
       </x:c>
       <x:c r="G78" s="2">
-        <x:v>42236</x:v>
+        <x:v>45356</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
@@ -3658,10 +3706,10 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>197</x:v>
@@ -3670,10 +3718,10 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G79" s="2">
-        <x:v>45698</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
@@ -3693,10 +3741,10 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>-2900</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G80" s="2">
-        <x:v>44662</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
@@ -3716,10 +3764,10 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2900</x:v>
       </x:c>
       <x:c r="G81" s="2">
-        <x:v>45980</x:v>
+        <x:v>44662</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
@@ -3727,10 +3775,10 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
         <x:v>206</x:v>
@@ -3739,10 +3787,10 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G82" s="2">
-        <x:v>38184</x:v>
+        <x:v>45980</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
@@ -3750,10 +3798,10 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
         <x:v>209</x:v>
@@ -3762,15 +3810,15 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G83" s="2">
-        <x:v>43410</x:v>
+        <x:v>38184</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
         <x:v>54</x:v>
@@ -3779,13 +3827,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>-20</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G84" s="2">
         <x:v>43410</x:v>
@@ -3796,10 +3844,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
         <x:v>212</x:v>
@@ -3808,10 +3856,10 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G85" s="2">
-        <x:v>42017</x:v>
+        <x:v>43410</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
@@ -3819,10 +3867,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
         <x:v>215</x:v>
@@ -3831,10 +3879,10 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G86" s="2">
-        <x:v>38764</x:v>
+        <x:v>42017</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
@@ -3842,10 +3890,10 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
         <x:v>218</x:v>
@@ -3854,10 +3902,10 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G87" s="2">
-        <x:v>41284</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
@@ -3865,10 +3913,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
         <x:v>221</x:v>
@@ -3877,10 +3925,10 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G88" s="2">
-        <x:v>44893</x:v>
+        <x:v>41284</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
@@ -3888,10 +3936,10 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
         <x:v>224</x:v>
@@ -3900,10 +3948,10 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>-25</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G89" s="2">
-        <x:v>41711</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
@@ -3911,10 +3959,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
         <x:v>227</x:v>
@@ -3923,10 +3971,10 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G90" s="2">
-        <x:v>45698</x:v>
+        <x:v>41711</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
@@ -3934,10 +3982,10 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
         <x:v>230</x:v>
@@ -3946,10 +3994,10 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G91" s="2">
-        <x:v>39813</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
@@ -3972,7 +4020,7 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G92" s="2">
-        <x:v>46044</x:v>
+        <x:v>45629</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
@@ -3980,56 +4028,56 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C93" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D93" s="1" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="C93" s="1" t="s">
+      <x:c r="E93" s="1" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="D93" s="1" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="E93" s="1" t="s">
-        <x:v>239</x:v>
-      </x:c>
       <x:c r="F93" s="1">
-        <x:v>-2800</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G93" s="2">
-        <x:v>41893</x:v>
+        <x:v>39813</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B94" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C94" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D94" s="1" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="E94" s="1" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="B94" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C94" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D94" s="1" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="E94" s="1" t="s">
-        <x:v>242</x:v>
-      </x:c>
       <x:c r="F94" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G94" s="2">
-        <x:v>38717</x:v>
+        <x:v>46044</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B95" s="1" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="C95" s="1" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="B95" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C95" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
         <x:v>244</x:v>
@@ -4038,10 +4086,10 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2800</x:v>
       </x:c>
       <x:c r="G95" s="2">
-        <x:v>46051</x:v>
+        <x:v>41893</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
@@ -4049,10 +4097,10 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
         <x:v>247</x:v>
@@ -4061,10 +4109,10 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G96" s="2">
-        <x:v>45617</x:v>
+        <x:v>38717</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
@@ -4072,10 +4120,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
         <x:v>250</x:v>
@@ -4084,56 +4132,56 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G97" s="2">
-        <x:v>40602</x:v>
+        <x:v>46051</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F98" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G98" s="2">
-        <x:v>40602</x:v>
+        <x:v>45617</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G99" s="2">
-        <x:v>44727</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
@@ -4141,10 +4189,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
         <x:v>256</x:v>
@@ -4156,7 +4204,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G100" s="2">
-        <x:v>38990</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
@@ -4164,10 +4212,10 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
         <x:v>259</x:v>
@@ -4179,7 +4227,7 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G101" s="2">
-        <x:v>38292</x:v>
+        <x:v>44727</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
@@ -4187,10 +4235,10 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
         <x:v>262</x:v>
@@ -4202,7 +4250,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G102" s="2">
-        <x:v>39512</x:v>
+        <x:v>38990</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
@@ -4210,10 +4258,10 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
         <x:v>265</x:v>
@@ -4222,10 +4270,10 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G103" s="2">
-        <x:v>45517</x:v>
+        <x:v>38292</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
@@ -4233,10 +4281,10 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
         <x:v>268</x:v>
@@ -4245,10 +4293,10 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G104" s="2">
-        <x:v>40178</x:v>
+        <x:v>45638</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -4256,10 +4304,10 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
         <x:v>271</x:v>
@@ -4268,84 +4316,84 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G105" s="2">
-        <x:v>45533</x:v>
+        <x:v>39512</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>-9</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G106" s="2">
-        <x:v>45533</x:v>
+        <x:v>45517</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-1</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G107" s="2">
-        <x:v>45533</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G108" s="2">
-        <x:v>44893</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
         <x:v>34</x:v>
@@ -4354,16 +4402,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-475</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G109" s="2">
-        <x:v>45077</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
@@ -4371,10 +4419,10 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
         <x:v>280</x:v>
@@ -4383,10 +4431,10 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G110" s="2">
-        <x:v>43799</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
@@ -4394,10 +4442,10 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
         <x:v>283</x:v>
@@ -4406,10 +4454,10 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G111" s="2">
-        <x:v>37855</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
@@ -4429,10 +4477,10 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G112" s="2">
-        <x:v>44716</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
@@ -4440,10 +4488,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
         <x:v>289</x:v>
@@ -4452,10 +4500,10 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G113" s="2">
-        <x:v>42004</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7">
@@ -4463,10 +4511,10 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
         <x:v>292</x:v>
@@ -4475,171 +4523,171 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="F114" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G114" s="2">
-        <x:v>43167</x:v>
+        <x:v>37855</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F115" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G115" s="2">
-        <x:v>44893</x:v>
+        <x:v>45638</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F116" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G116" s="2">
-        <x:v>43167</x:v>
+        <x:v>44716</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F117" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G117" s="2">
-        <x:v>44893</x:v>
+        <x:v>42004</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
       <x:c r="A118" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F118" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G118" s="2">
-        <x:v>40602</x:v>
+        <x:v>43167</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
       <x:c r="A119" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F119" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G119" s="2">
-        <x:v>40422</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7">
       <x:c r="A120" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G120" s="2">
-        <x:v>42818</x:v>
+        <x:v>43167</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
       <x:c r="A121" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B121" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C121" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D121" s="1" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="B121" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C121" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D121" s="1" t="s">
+      <x:c r="E121" s="1" t="s">
         <x:v>305</x:v>
-      </x:c>
-      <x:c r="E121" s="1" t="s">
-        <x:v>306</x:v>
       </x:c>
       <x:c r="F121" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G121" s="2">
-        <x:v>45107</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7">
@@ -4647,10 +4695,10 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="B122" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
         <x:v>308</x:v>
@@ -4659,10 +4707,10 @@
         <x:v>309</x:v>
       </x:c>
       <x:c r="F122" s="1">
-        <x:v>-1</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G122" s="2">
-        <x:v>45408</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:7">
@@ -4670,10 +4718,10 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
         <x:v>311</x:v>
@@ -4682,10 +4730,10 @@
         <x:v>312</x:v>
       </x:c>
       <x:c r="F123" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G123" s="2">
-        <x:v>43390</x:v>
+        <x:v>40422</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:7">
@@ -4693,234 +4741,234 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C124" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D124" s="1" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="C124" s="1" t="s">
+      <x:c r="E124" s="1" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="D124" s="1" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="E124" s="1" t="s">
-        <x:v>317</x:v>
-      </x:c>
       <x:c r="F124" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G124" s="2">
-        <x:v>43282</x:v>
+        <x:v>42818</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="1" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B125" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C125" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D125" s="1" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="E125" s="1" t="s">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="B125" s="1" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="C125" s="1" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D125" s="1" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="E125" s="1" t="s">
-        <x:v>320</x:v>
-      </x:c>
       <x:c r="F125" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G125" s="2">
-        <x:v>44013</x:v>
+        <x:v>45107</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:7">
       <x:c r="A126" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F126" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G126" s="2">
-        <x:v>44022</x:v>
+        <x:v>45408</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7">
       <x:c r="A127" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D127" s="1" t="s">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="D127" s="1" t="s">
+      <x:c r="E127" s="1" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="E127" s="1" t="s">
-        <x:v>325</x:v>
-      </x:c>
       <x:c r="F127" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G127" s="2">
-        <x:v>41926</x:v>
+        <x:v>43390</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7">
       <x:c r="A128" s="1" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B128" s="1" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B128" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F128" s="1">
-        <x:v>-20</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G128" s="2">
-        <x:v>41698</x:v>
+        <x:v>43282</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
       <x:c r="A129" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G129" s="2">
-        <x:v>45484</x:v>
+        <x:v>44013</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="1" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B130" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C130" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D130" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="E130" s="1" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="B130" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C130" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D130" s="1" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="E130" s="1" t="s">
-        <x:v>334</x:v>
-      </x:c>
       <x:c r="F130" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G130" s="2">
-        <x:v>45957</x:v>
+        <x:v>44022</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>-1650</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G131" s="2">
-        <x:v>45959</x:v>
+        <x:v>41926</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>-1650</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G132" s="2">
-        <x:v>45977</x:v>
+        <x:v>41698</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G133" s="2">
-        <x:v>45977</x:v>
+        <x:v>45484</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
         <x:v>34</x:v>
@@ -4929,21 +4977,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G134" s="2">
-        <x:v>45977</x:v>
+        <x:v>45957</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
         <x:v>34</x:v>
@@ -4952,21 +5000,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F135" s="1">
-        <x:v>-36</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="G135" s="2">
-        <x:v>45977</x:v>
+        <x:v>45959</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:7">
       <x:c r="A136" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
         <x:v>34</x:v>
@@ -4975,13 +5023,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F136" s="1">
-        <x:v>-9</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="G136" s="2">
         <x:v>45977</x:v>
@@ -4989,7 +5037,7 @@
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
         <x:v>34</x:v>
@@ -4998,13 +5046,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-3</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G137" s="2">
         <x:v>45977</x:v>
@@ -5012,7 +5060,7 @@
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
         <x:v>34</x:v>
@@ -5021,13 +5069,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-2</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G138" s="2">
         <x:v>45977</x:v>
@@ -5035,7 +5083,7 @@
     </x:row>
     <x:row r="139" spans="1:7">
       <x:c r="A139" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
         <x:v>34</x:v>
@@ -5044,13 +5092,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-1</x:v>
+        <x:v>-1800</x:v>
       </x:c>
       <x:c r="G139" s="2">
         <x:v>45977</x:v>
@@ -5058,7 +5106,7 @@
     </x:row>
     <x:row r="140" spans="1:7">
       <x:c r="A140" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
         <x:v>34</x:v>
@@ -5067,13 +5115,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G140" s="2">
         <x:v>45977</x:v>
@@ -5081,7 +5129,7 @@
     </x:row>
     <x:row r="141" spans="1:7">
       <x:c r="A141" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
         <x:v>34</x:v>
@@ -5090,13 +5138,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G141" s="2">
         <x:v>45977</x:v>
@@ -5104,7 +5152,7 @@
     </x:row>
     <x:row r="142" spans="1:7">
       <x:c r="A142" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
         <x:v>34</x:v>
@@ -5113,13 +5161,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-1800</x:v>
+        <x:v>-36</x:v>
       </x:c>
       <x:c r="G142" s="2">
         <x:v>45977</x:v>
@@ -5127,7 +5175,7 @@
     </x:row>
     <x:row r="143" spans="1:7">
       <x:c r="A143" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
         <x:v>34</x:v>
@@ -5136,85 +5184,85 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G143" s="2">
-        <x:v>45980</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:7">
       <x:c r="A144" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-800</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="G144" s="2">
-        <x:v>40602</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:7">
       <x:c r="A145" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="G145" s="2">
-        <x:v>37736</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:7">
       <x:c r="A146" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G146" s="2">
-        <x:v>39810</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:7">
@@ -5234,10 +5282,10 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G147" s="2">
-        <x:v>44767</x:v>
+        <x:v>45980</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:7">
@@ -5245,10 +5293,10 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
         <x:v>348</x:v>
@@ -5257,61 +5305,61 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G148" s="2">
-        <x:v>41010</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
       <x:c r="A149" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1425</x:v>
       </x:c>
       <x:c r="G149" s="2">
-        <x:v>41840</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:7">
       <x:c r="A150" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-100</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G150" s="2">
-        <x:v>40602</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
         <x:v>34</x:v>
@@ -5320,205 +5368,205 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-9</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G151" s="2">
-        <x:v>45972</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G152" s="2">
-        <x:v>40602</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:7">
       <x:c r="A153" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G153" s="2">
-        <x:v>40602</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:7">
       <x:c r="A154" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1900</x:v>
       </x:c>
       <x:c r="G154" s="2">
-        <x:v>40602</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:7">
       <x:c r="A155" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B155" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>-50</x:v>
+        <x:v>-1900</x:v>
       </x:c>
       <x:c r="G155" s="2">
-        <x:v>40602</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:7">
       <x:c r="A156" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F156" s="1">
-        <x:v>-5</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G156" s="2">
-        <x:v>40602</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:7">
       <x:c r="A157" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F157" s="1">
-        <x:v>-250</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G157" s="2">
-        <x:v>40602</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:7">
       <x:c r="A158" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F158" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G158" s="2">
-        <x:v>38075</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:7">
       <x:c r="A159" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F159" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G159" s="2">
-        <x:v>41455</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:7">
       <x:c r="A160" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
         <x:v>34</x:v>
@@ -5527,297 +5575,297 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F160" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1425</x:v>
       </x:c>
       <x:c r="G160" s="2">
-        <x:v>45698</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:7">
       <x:c r="A161" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B161" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F161" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G161" s="2">
-        <x:v>43646</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:7">
       <x:c r="A162" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B162" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F162" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="G162" s="2">
-        <x:v>39940</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:7">
       <x:c r="A163" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B163" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="F163" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G163" s="2">
-        <x:v>41455</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:7">
       <x:c r="A164" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B164" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D164" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F164" s="1">
-        <x:v>-500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G164" s="2">
-        <x:v>38322</x:v>
+        <x:v>39810</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:7">
       <x:c r="A165" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F165" s="1">
-        <x:v>-250</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G165" s="2">
-        <x:v>38322</x:v>
+        <x:v>44767</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:7">
       <x:c r="A166" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F166" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G166" s="2">
-        <x:v>44377</x:v>
+        <x:v>41010</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:7">
       <x:c r="A167" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F167" s="1">
         <x:v>-2500</x:v>
       </x:c>
       <x:c r="G167" s="2">
-        <x:v>44377</x:v>
+        <x:v>41840</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:7">
       <x:c r="A168" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B168" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F168" s="1">
-        <x:v>-500</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G168" s="2">
-        <x:v>40682</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:7">
       <x:c r="A169" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B169" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F169" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G169" s="2">
-        <x:v>39318</x:v>
+        <x:v>45972</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:7">
       <x:c r="A170" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B170" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D170" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F170" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G170" s="2">
-        <x:v>45879</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:7">
       <x:c r="A171" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B171" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D171" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F171" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G171" s="2">
-        <x:v>38075</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:7">
       <x:c r="A172" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B172" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F172" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G172" s="2">
-        <x:v>38764</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:7">
       <x:c r="A173" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
         <x:v>54</x:v>
@@ -5826,21 +5874,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F173" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G173" s="2">
-        <x:v>43201</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:7">
       <x:c r="A174" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
         <x:v>54</x:v>
@@ -5849,21 +5897,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F174" s="1">
-        <x:v>-250</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="G174" s="2">
-        <x:v>43201</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:7">
       <x:c r="A175" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B175" s="1" t="s">
         <x:v>54</x:v>
@@ -5872,44 +5920,44 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D175" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F175" s="1">
-        <x:v>-200</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G175" s="2">
-        <x:v>43201</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:7">
       <x:c r="A176" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B176" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F176" s="1">
-        <x:v>-100</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G176" s="2">
-        <x:v>43201</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:7">
       <x:c r="A177" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B177" s="1" t="s">
         <x:v>74</x:v>
@@ -5918,366 +5966,366 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="F177" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G177" s="2">
-        <x:v>39777</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:7">
       <x:c r="A178" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B178" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F178" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G178" s="2">
-        <x:v>43465</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:7">
       <x:c r="A179" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B179" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F179" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G179" s="2">
-        <x:v>39010</x:v>
+        <x:v>43646</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:7">
       <x:c r="A180" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B180" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F180" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G180" s="2">
-        <x:v>42783</x:v>
+        <x:v>39940</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:7">
       <x:c r="A181" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B181" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F181" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G181" s="2">
-        <x:v>45692</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:7">
       <x:c r="A182" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B182" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F182" s="1">
-        <x:v>-300</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G182" s="2">
-        <x:v>43799</x:v>
+        <x:v>38322</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:7">
       <x:c r="A183" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B183" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F183" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G183" s="2">
-        <x:v>38075</x:v>
+        <x:v>38322</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:7">
       <x:c r="A184" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B184" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F184" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G184" s="2">
-        <x:v>45698</x:v>
+        <x:v>44377</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:7">
       <x:c r="A185" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B185" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F185" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G185" s="2">
-        <x:v>45665</x:v>
+        <x:v>44377</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:7">
       <x:c r="A186" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E186" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F186" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G186" s="2">
-        <x:v>40724</x:v>
+        <x:v>40682</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:7">
       <x:c r="A187" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B187" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E187" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F187" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G187" s="2">
-        <x:v>46000</x:v>
+        <x:v>39318</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:7">
       <x:c r="A188" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B188" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F188" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G188" s="2">
-        <x:v>43465</x:v>
+        <x:v>45879</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:7">
       <x:c r="A189" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B189" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F189" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G189" s="2">
-        <x:v>44845</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
       <x:c r="A190" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B190" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C190" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F190" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G190" s="2">
-        <x:v>44645</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
       <x:c r="A191" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F191" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G191" s="2">
-        <x:v>41900</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:7">
       <x:c r="A192" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B192" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F192" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G192" s="2">
-        <x:v>41813</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:7">
       <x:c r="A193" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B193" s="1" t="s">
         <x:v>54</x:v>
@@ -6286,21 +6334,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F193" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G193" s="2">
-        <x:v>43573</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:7">
       <x:c r="A194" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B194" s="1" t="s">
         <x:v>54</x:v>
@@ -6309,159 +6357,159 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F194" s="1">
         <x:v>-100</x:v>
       </x:c>
       <x:c r="G194" s="2">
-        <x:v>42236</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:7">
       <x:c r="A195" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B195" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C195" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E195" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F195" s="1">
-        <x:v>-10</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G195" s="2">
-        <x:v>42236</x:v>
+        <x:v>39777</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:7">
       <x:c r="A196" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B196" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D196" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F196" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G196" s="2">
-        <x:v>44804</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:7">
       <x:c r="A197" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B197" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C197" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D197" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E197" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F197" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G197" s="2">
-        <x:v>37787</x:v>
+        <x:v>39010</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:7">
       <x:c r="A198" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B198" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C198" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D198" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="E198" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F198" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G198" s="2">
-        <x:v>45551</x:v>
+        <x:v>42783</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:7">
       <x:c r="A199" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B199" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C199" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D199" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E199" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F199" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G199" s="2">
-        <x:v>37736</x:v>
+        <x:v>45692</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
       <x:c r="A200" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B200" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E200" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F200" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G200" s="2">
-        <x:v>41453</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
       <x:c r="A201" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B201" s="1" t="s">
         <x:v>39</x:v>
@@ -6470,44 +6518,44 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F201" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G201" s="2">
-        <x:v>37736</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C202" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D202" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="E202" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F202" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G202" s="2">
-        <x:v>41453</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
       <x:c r="A203" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B203" s="1" t="s">
         <x:v>34</x:v>
@@ -6516,44 +6564,44 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D203" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="F203" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G203" s="2">
-        <x:v>45077</x:v>
+        <x:v>45665</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
       <x:c r="A204" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B204" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C204" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D204" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E204" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F204" s="1">
-        <x:v>-950</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G204" s="2">
-        <x:v>45077</x:v>
+        <x:v>40724</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:7">
       <x:c r="A205" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B205" s="1" t="s">
         <x:v>34</x:v>
@@ -6562,44 +6610,44 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D205" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="E205" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F205" s="1">
-        <x:v>-713</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G205" s="2">
-        <x:v>45077</x:v>
+        <x:v>46000</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:7">
       <x:c r="A206" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B206" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F206" s="1">
-        <x:v>-475</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G206" s="2">
-        <x:v>45077</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:7">
       <x:c r="A207" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B207" s="1" t="s">
         <x:v>34</x:v>
@@ -6608,84 +6656,498 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F207" s="1">
-        <x:v>-238</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G207" s="2">
-        <x:v>45077</x:v>
+        <x:v>44845</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:7">
       <x:c r="A208" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B208" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D208" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E208" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F208" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G208" s="2">
-        <x:v>40178</x:v>
+        <x:v>44645</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:7">
       <x:c r="A209" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B209" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C209" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D209" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="E209" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F209" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G209" s="2">
-        <x:v>39629</x:v>
+        <x:v>41900</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:7">
       <x:c r="A210" s="1" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B210" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C210" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D210" s="1" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="E210" s="1" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="F210" s="1">
+        <x:v>-2500</x:v>
+      </x:c>
+      <x:c r="G210" s="2">
+        <x:v>41813</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:7">
+      <x:c r="A211" s="1" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B211" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C211" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D211" s="1" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="E211" s="1" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="F211" s="1">
+        <x:v>-6250</x:v>
+      </x:c>
+      <x:c r="G211" s="2">
+        <x:v>43573</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:7">
+      <x:c r="A212" s="1" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B212" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C212" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D212" s="1" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="E212" s="1" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="F212" s="1">
+        <x:v>-100</x:v>
+      </x:c>
+      <x:c r="G212" s="2">
+        <x:v>42236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:7">
+      <x:c r="A213" s="1" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B213" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C213" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D213" s="1" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="E213" s="1" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="F213" s="1">
+        <x:v>-10</x:v>
+      </x:c>
+      <x:c r="G213" s="2">
+        <x:v>42236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:7">
+      <x:c r="A214" s="1" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B214" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C214" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D214" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="E214" s="1" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="F214" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G214" s="2">
+        <x:v>44804</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:7">
+      <x:c r="A215" s="1" t="s">
         <x:v>471</x:v>
       </x:c>
-      <x:c r="B210" s="1" t="s">
+      <x:c r="B215" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C215" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D215" s="1" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="E215" s="1" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="F215" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G215" s="2">
+        <x:v>37787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:7">
+      <x:c r="A216" s="1" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="B216" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C216" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D216" s="1" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="E216" s="1" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="F216" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G216" s="2">
+        <x:v>45551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:7">
+      <x:c r="A217" s="1" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B217" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C217" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D217" s="1" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="E217" s="1" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="F217" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G217" s="2">
+        <x:v>37736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:7">
+      <x:c r="A218" s="1" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B218" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C218" s="1" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="D218" s="1" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="E218" s="1" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="F218" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G218" s="2">
+        <x:v>41453</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:7">
+      <x:c r="A219" s="1" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B219" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C219" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D219" s="1" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="E219" s="1" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="F219" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G219" s="2">
+        <x:v>37736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:7">
+      <x:c r="A220" s="1" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B220" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C220" s="1" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="D220" s="1" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="E220" s="1" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="F220" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G220" s="2">
+        <x:v>41453</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:7">
+      <x:c r="A221" s="1" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B221" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C221" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D221" s="1" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="E221" s="1" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="F221" s="1">
+        <x:v>-2755</x:v>
+      </x:c>
+      <x:c r="G221" s="2">
+        <x:v>45077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:7">
+      <x:c r="A222" s="1" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B222" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C222" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D222" s="1" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="E222" s="1" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="F222" s="1">
+        <x:v>-950</x:v>
+      </x:c>
+      <x:c r="G222" s="2">
+        <x:v>45077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:7">
+      <x:c r="A223" s="1" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B223" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C223" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D223" s="1" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="E223" s="1" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="F223" s="1">
+        <x:v>-713</x:v>
+      </x:c>
+      <x:c r="G223" s="2">
+        <x:v>45077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:7">
+      <x:c r="A224" s="1" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B224" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C224" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D224" s="1" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="E224" s="1" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="F224" s="1">
+        <x:v>-475</x:v>
+      </x:c>
+      <x:c r="G224" s="2">
+        <x:v>45077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:7">
+      <x:c r="A225" s="1" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B225" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C225" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D225" s="1" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="E225" s="1" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="F225" s="1">
+        <x:v>-238</x:v>
+      </x:c>
+      <x:c r="G225" s="2">
+        <x:v>45077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:7">
+      <x:c r="A226" s="1" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B226" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C226" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D226" s="1" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="E226" s="1" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="F226" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G226" s="2">
+        <x:v>40178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:7">
+      <x:c r="A227" s="1" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B227" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C210" s="1" t="s">
+      <x:c r="C227" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D210" s="1" t="s">
-        <x:v>472</x:v>
-      </x:c>
-      <x:c r="E210" s="1" t="s">
-        <x:v>473</x:v>
-      </x:c>
-      <x:c r="F210" s="1">
+      <x:c r="D227" s="1" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="E227" s="1" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="F227" s="1">
         <x:v>-1000</x:v>
       </x:c>
-      <x:c r="G210" s="2">
+      <x:c r="G227" s="2">
+        <x:v>39629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:7">
+      <x:c r="A228" s="1" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B228" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C228" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D228" s="1" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="E228" s="1" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="F228" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G228" s="2">
         <x:v>39660</x:v>
       </x:c>
     </x:row>
@@ -6705,7 +7167,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H158"/>
+  <x:dimension ref="A1:H163"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="9" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -6736,13 +7198,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -6950,7 +7412,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>99682</x:v>
+        <x:v>67592</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
@@ -7163,33 +7625,33 @@
     </x:row>
     <x:row r="18" spans="1:8">
       <x:c r="A18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>-10</x:v>
+        <x:v>-51</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>702091</x:v>
+        <x:v>8339</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8">
       <x:c r="A19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>54</x:v>
@@ -7207,7 +7669,7 @@
         <x:v>-51</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="1">
         <x:v>8339</x:v>
@@ -7215,106 +7677,106 @@
     </x:row>
     <x:row r="20" spans="1:8">
       <x:c r="A20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>-51</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>8339</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8">
       <x:c r="A21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>0</x:v>
+        <x:v>9075</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8">
       <x:c r="A22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>9075</x:v>
+        <x:v>51183</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8">
       <x:c r="A23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>51183</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8">
@@ -7322,10 +7784,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>85</x:v>
@@ -7334,7 +7796,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>84</x:v>
@@ -7345,25 +7807,25 @@
     </x:row>
     <x:row r="25" spans="1:8">
       <x:c r="A25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-3500</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H25" s="1">
         <x:v>0</x:v>
@@ -7374,10 +7836,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>88</x:v>
@@ -7386,7 +7848,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>-3500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>87</x:v>
@@ -7397,25 +7859,25 @@
     </x:row>
     <x:row r="27" spans="1:8">
       <x:c r="A27" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H27" s="1">
         <x:v>0</x:v>
@@ -7423,129 +7885,129 @@
     </x:row>
     <x:row r="28" spans="1:8">
       <x:c r="A28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:8">
       <x:c r="A29" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>-10</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>150</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:8">
       <x:c r="A30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1901</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>5032</x:v>
+        <x:v>21265</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:8">
       <x:c r="A31" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>-1901</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>21265</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:8">
       <x:c r="A32" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>0</x:v>
@@ -7553,25 +8015,25 @@
     </x:row>
     <x:row r="33" spans="1:8">
       <x:c r="A33" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>0</x:v>
@@ -7579,59 +8041,59 @@
     </x:row>
     <x:row r="34" spans="1:8">
       <x:c r="A34" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-850</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>0</x:v>
+        <x:v>26114</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:8">
       <x:c r="A35" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>-850</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>26114</x:v>
+        <x:v>330449</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:8">
       <x:c r="A36" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>46</x:v>
@@ -7640,16 +8102,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F36" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H36" s="1">
         <x:v>2400</x:v>
@@ -7657,7 +8119,7 @@
     </x:row>
     <x:row r="37" spans="1:8">
       <x:c r="A37" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>109</x:v>
@@ -7666,16 +8128,16 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F37" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H37" s="1">
         <x:v>0</x:v>
@@ -7683,25 +8145,25 @@
     </x:row>
     <x:row r="38" spans="1:8">
       <x:c r="A38" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F38" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H38" s="1">
         <x:v>1000</x:v>
@@ -7709,7 +8171,7 @@
     </x:row>
     <x:row r="39" spans="1:8">
       <x:c r="A39" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>39</x:v>
@@ -7718,16 +8180,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F39" s="1">
         <x:v>-1500</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H39" s="1">
         <x:v>1500</x:v>
@@ -7735,7 +8197,7 @@
     </x:row>
     <x:row r="40" spans="1:8">
       <x:c r="A40" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>39</x:v>
@@ -7744,16 +8206,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F40" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H40" s="1">
         <x:v>0</x:v>
@@ -7761,7 +8223,7 @@
     </x:row>
     <x:row r="41" spans="1:8">
       <x:c r="A41" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>109</x:v>
@@ -7770,16 +8232,16 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F41" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H41" s="1">
         <x:v>1000</x:v>
@@ -7787,7 +8249,7 @@
     </x:row>
     <x:row r="42" spans="1:8">
       <x:c r="A42" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>34</x:v>
@@ -7796,16 +8258,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F42" s="1">
         <x:v>-95</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H42" s="1">
         <x:v>42275</x:v>
@@ -7813,7 +8275,7 @@
     </x:row>
     <x:row r="43" spans="1:8">
       <x:c r="A43" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>34</x:v>
@@ -7822,16 +8284,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="F43" s="1">
         <x:v>-2900</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H43" s="1">
         <x:v>500</x:v>
@@ -7839,7 +8301,7 @@
     </x:row>
     <x:row r="44" spans="1:8">
       <x:c r="A44" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>109</x:v>
@@ -7848,16 +8310,16 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F44" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H44" s="1">
         <x:v>1500</x:v>
@@ -7865,7 +8327,7 @@
     </x:row>
     <x:row r="45" spans="1:8">
       <x:c r="A45" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>18</x:v>
@@ -7874,16 +8336,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F45" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H45" s="1">
         <x:v>0</x:v>
@@ -7891,25 +8353,25 @@
     </x:row>
     <x:row r="46" spans="1:8">
       <x:c r="A46" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F46" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H46" s="1">
         <x:v>0</x:v>
@@ -7917,25 +8379,25 @@
     </x:row>
     <x:row r="47" spans="1:8">
       <x:c r="A47" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F47" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H47" s="1">
         <x:v>0</x:v>
@@ -7943,25 +8405,25 @@
     </x:row>
     <x:row r="48" spans="1:8">
       <x:c r="A48" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>164</x:v>
-      </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F48" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H48" s="1">
         <x:v>30000</x:v>
@@ -7969,7 +8431,7 @@
     </x:row>
     <x:row r="49" spans="1:8">
       <x:c r="A49" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
         <x:v>46</x:v>
@@ -7978,16 +8440,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F49" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H49" s="1">
         <x:v>0</x:v>
@@ -7995,7 +8457,7 @@
     </x:row>
     <x:row r="50" spans="1:8">
       <x:c r="A50" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
         <x:v>54</x:v>
@@ -8004,16 +8466,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F50" s="1">
         <x:v>-10</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H50" s="1">
         <x:v>90014</x:v>
@@ -8021,7 +8483,7 @@
     </x:row>
     <x:row r="51" spans="1:8">
       <x:c r="A51" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
         <x:v>54</x:v>
@@ -8030,16 +8492,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F51" s="1">
         <x:v>-375</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H51" s="1">
         <x:v>42958</x:v>
@@ -8047,7 +8509,7 @@
     </x:row>
     <x:row r="52" spans="1:8">
       <x:c r="A52" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
         <x:v>109</x:v>
@@ -8056,16 +8518,16 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F52" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H52" s="1">
         <x:v>1500</x:v>
@@ -8073,25 +8535,25 @@
     </x:row>
     <x:row r="53" spans="1:8">
       <x:c r="A53" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="F53" s="1">
         <x:v>-200</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H53" s="1">
         <x:v>251266</x:v>
@@ -8099,7 +8561,7 @@
     </x:row>
     <x:row r="54" spans="1:8">
       <x:c r="A54" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
         <x:v>74</x:v>
@@ -8108,16 +8570,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F54" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H54" s="1">
         <x:v>10000</x:v>
@@ -8125,7 +8587,7 @@
     </x:row>
     <x:row r="55" spans="1:8">
       <x:c r="A55" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
         <x:v>101</x:v>
@@ -8134,16 +8596,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F55" s="1">
         <x:v>-1347</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H55" s="1">
         <x:v>35205</x:v>
@@ -8151,7 +8613,7 @@
     </x:row>
     <x:row r="56" spans="1:8">
       <x:c r="A56" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
         <x:v>34</x:v>
@@ -8160,16 +8622,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F56" s="1">
         <x:v>-13242</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H56" s="1">
         <x:v>158894</x:v>
@@ -8177,7 +8639,7 @@
     </x:row>
     <x:row r="57" spans="1:8">
       <x:c r="A57" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
         <x:v>54</x:v>
@@ -8186,16 +8648,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="F57" s="1">
         <x:v>-50</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H57" s="1">
         <x:v>35388</x:v>
@@ -8203,7 +8665,7 @@
     </x:row>
     <x:row r="58" spans="1:8">
       <x:c r="A58" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
         <x:v>34</x:v>
@@ -8212,24 +8674,24 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F58" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H58" s="1">
-        <x:v>71916</x:v>
+        <x:v>76916</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:8">
       <x:c r="A59" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
         <x:v>34</x:v>
@@ -8238,16 +8700,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F59" s="1">
         <x:v>-2900</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H59" s="1">
         <x:v>25700</x:v>
@@ -8255,7 +8717,7 @@
     </x:row>
     <x:row r="60" spans="1:8">
       <x:c r="A60" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
         <x:v>34</x:v>
@@ -8264,24 +8726,24 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F60" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H60" s="1">
-        <x:v>622244</x:v>
+        <x:v>355947</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:8">
       <x:c r="A61" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
         <x:v>18</x:v>
@@ -8290,16 +8752,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F61" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H61" s="1">
         <x:v>3000</x:v>
@@ -8307,7 +8769,7 @@
     </x:row>
     <x:row r="62" spans="1:8">
       <x:c r="A62" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
         <x:v>54</x:v>
@@ -8316,16 +8778,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F62" s="1">
         <x:v>-270</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H62" s="1">
         <x:v>13265</x:v>
@@ -8333,7 +8795,7 @@
     </x:row>
     <x:row r="63" spans="1:8">
       <x:c r="A63" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
         <x:v>117</x:v>
@@ -8342,16 +8804,16 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F63" s="1">
         <x:v>-2500</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H63" s="1">
         <x:v>5000</x:v>
@@ -8359,7 +8821,7 @@
     </x:row>
     <x:row r="64" spans="1:8">
       <x:c r="A64" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
         <x:v>39</x:v>
@@ -8368,16 +8830,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F64" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H64" s="1">
         <x:v>2500</x:v>
@@ -8385,7 +8847,7 @@
     </x:row>
     <x:row r="65" spans="1:8">
       <x:c r="A65" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
         <x:v>46</x:v>
@@ -8394,16 +8856,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F65" s="1">
         <x:v>-7000</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H65" s="1">
         <x:v>0</x:v>
@@ -8411,7 +8873,7 @@
     </x:row>
     <x:row r="66" spans="1:8">
       <x:c r="A66" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
         <x:v>101</x:v>
@@ -8420,16 +8882,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F66" s="1">
         <x:v>-2500</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H66" s="1">
         <x:v>3461</x:v>
@@ -8437,7 +8899,7 @@
     </x:row>
     <x:row r="67" spans="1:8">
       <x:c r="A67" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
         <x:v>54</x:v>
@@ -8446,16 +8908,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F67" s="1">
         <x:v>-25</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="H67" s="1">
         <x:v>38904</x:v>
@@ -8463,7 +8925,7 @@
     </x:row>
     <x:row r="68" spans="1:8">
       <x:c r="A68" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
         <x:v>34</x:v>
@@ -8472,284 +8934,284 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F68" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H68" s="1">
-        <x:v>51848</x:v>
+        <x:v>56848</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:8">
       <x:c r="A69" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H69" s="1">
-        <x:v>0</x:v>
+        <x:v>30766</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:8">
       <x:c r="A70" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>249782</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:8">
       <x:c r="A71" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="E71" s="1" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F71" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G71" s="1" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="E71" s="1" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="F71" s="1">
-        <x:v>-2800</x:v>
-      </x:c>
-      <x:c r="G71" s="1" t="s">
-        <x:v>235</x:v>
-      </x:c>
       <x:c r="H71" s="1">
-        <x:v>0</x:v>
+        <x:v>94803</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:8">
       <x:c r="A72" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="E72" s="1" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F72" s="1">
+        <x:v>-2800</x:v>
+      </x:c>
+      <x:c r="G72" s="1" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="E72" s="1" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F72" s="1">
-        <x:v>-500</x:v>
-      </x:c>
-      <x:c r="G72" s="1" t="s">
-        <x:v>240</x:v>
-      </x:c>
       <x:c r="H72" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:8">
       <x:c r="A73" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>222523</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:8">
       <x:c r="A74" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="H74" s="1">
-        <x:v>2000</x:v>
+        <x:v>114262</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:8">
       <x:c r="A75" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>-3400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H75" s="1">
-        <x:v>28982</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:8">
       <x:c r="A76" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-3400</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>0</x:v>
+        <x:v>28982</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
       <x:c r="A77" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H77" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:8">
       <x:c r="A78" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="H78" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:8">
       <x:c r="A79" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
         <x:v>74</x:v>
@@ -8758,16 +9220,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H79" s="1">
         <x:v>0</x:v>
@@ -8775,111 +9237,111 @@
     </x:row>
     <x:row r="80" spans="1:8">
       <x:c r="A80" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="H80" s="1">
-        <x:v>5000</x:v>
+        <x:v>52742</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:8">
       <x:c r="A81" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F81" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:8">
       <x:c r="A82" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>-510</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>42500</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:8">
       <x:c r="A83" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="H83" s="1">
-        <x:v>2000</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:8">
       <x:c r="A84" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
         <x:v>34</x:v>
@@ -8888,570 +9350,570 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>-475</x:v>
+        <x:v>-510</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H84" s="1">
-        <x:v>131385</x:v>
+        <x:v>42500</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:8">
       <x:c r="A85" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>-250</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="H85" s="1">
-        <x:v>69371</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:8">
       <x:c r="A86" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="H86" s="1">
-        <x:v>500</x:v>
+        <x:v>131385</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:8">
       <x:c r="A87" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H87" s="1">
-        <x:v>111188</x:v>
+        <x:v>69371</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:8">
       <x:c r="A88" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F88" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="H88" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:8">
       <x:c r="A89" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="H89" s="1">
-        <x:v>10000</x:v>
+        <x:v>135047</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:8">
       <x:c r="A90" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="H90" s="1">
-        <x:v>1150</x:v>
+        <x:v>111188</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:8">
       <x:c r="A91" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="H91" s="1">
-        <x:v>10000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:8">
       <x:c r="A92" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="H92" s="1">
-        <x:v>1150</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:8">
       <x:c r="A93" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="H93" s="1">
-        <x:v>33320</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:8">
       <x:c r="A94" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F94" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H94" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:8">
       <x:c r="A95" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H95" s="1">
-        <x:v>21095</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:8">
       <x:c r="A96" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="H96" s="1">
-        <x:v>0</x:v>
+        <x:v>33320</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:8">
       <x:c r="A97" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>-1</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="H97" s="1">
-        <x:v>26650</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:8">
       <x:c r="A98" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="H98" s="1">
-        <x:v>5000</x:v>
+        <x:v>21095</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:8">
       <x:c r="A99" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="E99" s="1" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="F99" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G99" s="1" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="E99" s="1" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="F99" s="1">
-        <x:v>-5000</x:v>
-      </x:c>
-      <x:c r="G99" s="1" t="s">
-        <x:v>313</x:v>
-      </x:c>
       <x:c r="H99" s="1">
-        <x:v>12000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:8">
       <x:c r="A100" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="E100" s="1" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="F100" s="1">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="G100" s="1" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="E100" s="1" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="F100" s="1">
-        <x:v>-5000</x:v>
-      </x:c>
-      <x:c r="G100" s="1" t="s">
-        <x:v>318</x:v>
-      </x:c>
       <x:c r="H100" s="1">
-        <x:v>0</x:v>
+        <x:v>26650</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:8">
       <x:c r="A101" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="H101" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:8">
       <x:c r="A102" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F102" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G102" s="1" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="F102" s="1">
-        <x:v>-2000</x:v>
-      </x:c>
-      <x:c r="G102" s="1" t="s">
-        <x:v>321</x:v>
-      </x:c>
       <x:c r="H102" s="1">
-        <x:v>2000</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:8">
       <x:c r="A103" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>-20</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="H103" s="1">
-        <x:v>14900</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:8">
       <x:c r="A104" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="E104" s="1" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="F104" s="1">
+        <x:v>-2500</x:v>
+      </x:c>
+      <x:c r="G104" s="1" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="E104" s="1" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="F104" s="1">
-        <x:v>-3000</x:v>
-      </x:c>
-      <x:c r="G104" s="1" t="s">
-        <x:v>329</x:v>
-      </x:c>
       <x:c r="H104" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:8">
       <x:c r="A105" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="E105" s="1" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="F105" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G105" s="1" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="E105" s="1" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="F105" s="1">
-        <x:v>-19701</x:v>
-      </x:c>
-      <x:c r="G105" s="1" t="s">
-        <x:v>332</x:v>
-      </x:c>
       <x:c r="H105" s="1">
-        <x:v>49967</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:8">
       <x:c r="A106" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
         <x:v>54</x:v>
@@ -9460,76 +9922,76 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>-800</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="H106" s="1">
-        <x:v>58679</x:v>
+        <x:v>14900</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:8">
       <x:c r="A107" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="H107" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:8">
       <x:c r="A108" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-19701</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="H108" s="1">
-        <x:v>5000</x:v>
+        <x:v>49867</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:8">
       <x:c r="A109" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
         <x:v>34</x:v>
@@ -9538,30 +10000,30 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-300</x:v>
+        <x:v>-8456</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="H109" s="1">
-        <x:v>36900</x:v>
+        <x:v>95962</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:8">
       <x:c r="A110" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
         <x:v>348</x:v>
@@ -9570,166 +10032,166 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-8456</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="H110" s="1">
-        <x:v>0</x:v>
+        <x:v>95962</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:8">
       <x:c r="A111" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="E111" s="1" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="F111" s="1">
+        <x:v>-800</x:v>
+      </x:c>
+      <x:c r="G111" s="1" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="E111" s="1" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="F111" s="1">
-        <x:v>-2500</x:v>
-      </x:c>
-      <x:c r="G111" s="1" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="H111" s="1">
-        <x:v>0</x:v>
+        <x:v>58679</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:8">
       <x:c r="A112" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="E112" s="1" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="F112" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G112" s="1" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="E112" s="1" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="F112" s="1">
-        <x:v>-100</x:v>
-      </x:c>
-      <x:c r="G112" s="1" t="s">
-        <x:v>353</x:v>
-      </x:c>
       <x:c r="H112" s="1">
-        <x:v>58000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:8">
       <x:c r="A113" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="E113" s="1" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="F113" s="1">
+        <x:v>-3000</x:v>
+      </x:c>
+      <x:c r="G113" s="1" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="E113" s="1" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="F113" s="1">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="G113" s="1" t="s">
-        <x:v>356</x:v>
-      </x:c>
       <x:c r="H113" s="1">
-        <x:v>15349</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:8">
       <x:c r="A114" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="E114" s="1" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="F114" s="1">
+        <x:v>-300</x:v>
+      </x:c>
+      <x:c r="G114" s="1" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="E114" s="1" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="F114" s="1">
-        <x:v>-4955</x:v>
-      </x:c>
-      <x:c r="G114" s="1" t="s">
-        <x:v>359</x:v>
-      </x:c>
       <x:c r="H114" s="1">
-        <x:v>64475</x:v>
+        <x:v>36900</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:8">
       <x:c r="A115" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="E115" s="1" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="F115" s="1">
+        <x:v>-2500</x:v>
+      </x:c>
+      <x:c r="G115" s="1" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="E115" s="1" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="F115" s="1">
-        <x:v>-250</x:v>
-      </x:c>
-      <x:c r="G115" s="1" t="s">
-        <x:v>362</x:v>
-      </x:c>
       <x:c r="H115" s="1">
-        <x:v>42061</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:8">
       <x:c r="A116" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F116" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G116" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="H116" s="1">
         <x:v>0</x:v>
@@ -9737,33 +10199,33 @@
     </x:row>
     <x:row r="117" spans="1:8">
       <x:c r="A117" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F117" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G117" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="H117" s="1">
-        <x:v>0</x:v>
+        <x:v>58000</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:8">
       <x:c r="A118" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
         <x:v>34</x:v>
@@ -9772,120 +10234,120 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F118" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G118" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="H118" s="1">
-        <x:v>7380</x:v>
+        <x:v>15328</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:8">
       <x:c r="A119" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F119" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-4955</x:v>
       </x:c>
       <x:c r="G119" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="H119" s="1">
-        <x:v>3000</x:v>
+        <x:v>64475</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:8">
       <x:c r="A120" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G120" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="H120" s="1">
-        <x:v>0</x:v>
+        <x:v>42061</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:8">
       <x:c r="A121" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F121" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G121" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H121" s="1">
-        <x:v>2400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:8">
       <x:c r="A122" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B122" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="E122" s="1" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="F122" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G122" s="1" t="s">
         <x:v>382</x:v>
-      </x:c>
-      <x:c r="E122" s="1" t="s">
-        <x:v>383</x:v>
-      </x:c>
-      <x:c r="F122" s="1">
-        <x:v>-500</x:v>
-      </x:c>
-      <x:c r="G122" s="1" t="s">
-        <x:v>381</x:v>
       </x:c>
       <x:c r="H122" s="1">
         <x:v>0</x:v>
@@ -9893,285 +10355,285 @@
     </x:row>
     <x:row r="123" spans="1:8">
       <x:c r="A123" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="E123" s="1" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="F123" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G123" s="1" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="E123" s="1" t="s">
-        <x:v>386</x:v>
-      </x:c>
-      <x:c r="F123" s="1">
-        <x:v>-250</x:v>
-      </x:c>
-      <x:c r="G123" s="1" t="s">
-        <x:v>384</x:v>
-      </x:c>
       <x:c r="H123" s="1">
-        <x:v>6727</x:v>
+        <x:v>12380</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:8">
       <x:c r="A124" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="E124" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="F124" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G124" s="1" t="s">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="E124" s="1" t="s">
-        <x:v>389</x:v>
-      </x:c>
-      <x:c r="F124" s="1">
-        <x:v>-7500</x:v>
-      </x:c>
-      <x:c r="G124" s="1" t="s">
-        <x:v>387</x:v>
-      </x:c>
       <x:c r="H124" s="1">
-        <x:v>5000</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:8">
       <x:c r="A125" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="E125" s="1" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="F125" s="1">
+        <x:v>-1500</x:v>
+      </x:c>
+      <x:c r="G125" s="1" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="E125" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F125" s="1">
-        <x:v>-500</x:v>
-      </x:c>
-      <x:c r="G125" s="1" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="H125" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:8">
       <x:c r="A126" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="E126" s="1" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="F126" s="1">
+        <x:v>-2400</x:v>
+      </x:c>
+      <x:c r="G126" s="1" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="E126" s="1" t="s">
-        <x:v>395</x:v>
-      </x:c>
-      <x:c r="F126" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G126" s="1" t="s">
-        <x:v>393</x:v>
-      </x:c>
       <x:c r="H126" s="1">
-        <x:v>2000</x:v>
+        <x:v>2400</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:8">
       <x:c r="A127" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F127" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G127" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="H127" s="1">
-        <x:v>159727</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:8">
       <x:c r="A128" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F128" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G128" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="H128" s="1">
-        <x:v>0</x:v>
+        <x:v>6727</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:8">
       <x:c r="A129" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-7500</x:v>
       </x:c>
       <x:c r="G129" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="H129" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:8">
       <x:c r="A130" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G130" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="H130" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:8">
       <x:c r="A131" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>-1550</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G131" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="H131" s="1">
-        <x:v>193279</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:8">
       <x:c r="A132" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G132" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="H132" s="1">
-        <x:v>0</x:v>
+        <x:v>131464</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:8">
       <x:c r="A133" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G133" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="H133" s="1">
         <x:v>0</x:v>
@@ -10179,59 +10641,59 @@
     </x:row>
     <x:row r="134" spans="1:8">
       <x:c r="A134" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G134" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="H134" s="1">
-        <x:v>19596</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:8">
       <x:c r="A135" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F135" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G135" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="H135" s="1">
-        <x:v>17260</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:8">
       <x:c r="A136" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
         <x:v>54</x:v>
@@ -10240,42 +10702,42 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="E136" s="1" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="F136" s="1">
+        <x:v>-1550</x:v>
+      </x:c>
+      <x:c r="G136" s="1" t="s">
         <x:v>419</x:v>
       </x:c>
-      <x:c r="E136" s="1" t="s">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="F136" s="1">
-        <x:v>-300</x:v>
-      </x:c>
-      <x:c r="G136" s="1" t="s">
-        <x:v>418</x:v>
-      </x:c>
       <x:c r="H136" s="1">
-        <x:v>6150</x:v>
+        <x:v>193279</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:8">
       <x:c r="A137" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G137" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="H137" s="1">
         <x:v>0</x:v>
@@ -10283,129 +10745,129 @@
     </x:row>
     <x:row r="138" spans="1:8">
       <x:c r="A138" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G138" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H138" s="1">
-        <x:v>32943</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:8">
       <x:c r="A139" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G139" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H139" s="1">
-        <x:v>41676</x:v>
+        <x:v>19596</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:8">
       <x:c r="A140" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G140" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="H140" s="1">
-        <x:v>0</x:v>
+        <x:v>18660</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:8">
       <x:c r="A141" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="H141" s="1">
-        <x:v>84497</x:v>
+        <x:v>6150</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:8">
       <x:c r="A142" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H142" s="1">
         <x:v>0</x:v>
@@ -10413,7 +10875,7 @@
     </x:row>
     <x:row r="143" spans="1:8">
       <x:c r="A143" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
         <x:v>34</x:v>
@@ -10422,336 +10884,336 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F143" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="H143" s="1">
-        <x:v>28400</x:v>
+        <x:v>37943</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:8">
       <x:c r="A144" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="E144" s="1" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="F144" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G144" s="1" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="E144" s="1" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="F144" s="1">
-        <x:v>-300</x:v>
-      </x:c>
-      <x:c r="G144" s="1" t="s">
-        <x:v>440</x:v>
-      </x:c>
       <x:c r="H144" s="1">
-        <x:v>22566</x:v>
+        <x:v>46676</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:8">
       <x:c r="A145" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E145" s="1" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="F145" s="1">
+        <x:v>-500</x:v>
+      </x:c>
+      <x:c r="G145" s="1" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="E145" s="1" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="F145" s="1">
-        <x:v>-3000</x:v>
-      </x:c>
-      <x:c r="G145" s="1" t="s">
-        <x:v>443</x:v>
-      </x:c>
       <x:c r="H145" s="1">
-        <x:v>3750</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:8">
       <x:c r="A146" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="H146" s="1">
-        <x:v>10000</x:v>
+        <x:v>75893</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:8">
       <x:c r="A147" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="H147" s="1">
-        <x:v>18414</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:8">
       <x:c r="A148" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-110</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="H148" s="1">
-        <x:v>5170</x:v>
+        <x:v>28400</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:8">
       <x:c r="A149" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="H149" s="1">
-        <x:v>6000</x:v>
+        <x:v>22566</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:8">
       <x:c r="A150" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="H150" s="1">
-        <x:v>10972</x:v>
+        <x:v>3750</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:8">
       <x:c r="A151" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="E151" s="1" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="F151" s="1">
+        <x:v>-2500</x:v>
+      </x:c>
+      <x:c r="G151" s="1" t="s">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="E151" s="1" t="s">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="F151" s="1">
-        <x:v>-5000</x:v>
-      </x:c>
-      <x:c r="G151" s="1" t="s">
-        <x:v>458</x:v>
-      </x:c>
       <x:c r="H151" s="1">
-        <x:v>57350</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:8">
       <x:c r="A152" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="E152" s="1" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="F152" s="1">
+        <x:v>-6250</x:v>
+      </x:c>
+      <x:c r="G152" s="1" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="E152" s="1" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="F152" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G152" s="1" t="s">
-        <x:v>461</x:v>
-      </x:c>
       <x:c r="H152" s="1">
-        <x:v>2500</x:v>
+        <x:v>18414</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:8">
       <x:c r="A153" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-110</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="H153" s="1">
-        <x:v>0</x:v>
+        <x:v>5170</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:8">
       <x:c r="A154" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F154" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="H154" s="1">
-        <x:v>2500</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:8">
       <x:c r="A155" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B155" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="H155" s="1">
-        <x:v>0</x:v>
+        <x:v>10972</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:8">
       <x:c r="A156" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
         <x:v>34</x:v>
@@ -10760,70 +11222,200 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="F156" s="1">
-        <x:v>-5131</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="H156" s="1">
-        <x:v>83966</x:v>
+        <x:v>57350</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:8">
       <x:c r="A157" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="F157" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="H157" s="1">
-        <x:v>6000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:8">
       <x:c r="A158" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="F158" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="H158" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:8">
+      <x:c r="A159" s="1" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B159" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C159" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D159" s="1" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="E159" s="1" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="F159" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G159" s="1" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="H159" s="1">
+        <x:v>2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:8">
+      <x:c r="A160" s="1" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B160" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C160" s="1" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="D160" s="1" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="E160" s="1" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="F160" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G160" s="1" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="H160" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:8">
+      <x:c r="A161" s="1" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B161" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C161" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D161" s="1" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="E161" s="1" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="F161" s="1">
+        <x:v>-5131</x:v>
+      </x:c>
+      <x:c r="G161" s="1" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="H161" s="1">
+        <x:v>83966</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:8">
+      <x:c r="A162" s="1" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B162" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C162" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D162" s="1" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="E162" s="1" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="F162" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G162" s="1" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="H162" s="1">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:8">
+      <x:c r="A163" s="1" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B163" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C163" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D163" s="1" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="E163" s="1" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="F163" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G163" s="1" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="H163" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -1590,8 +1590,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H163" totalsRowShown="0">
-  <x:autoFilter ref="A1:H163"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H164" totalsRowShown="0">
+  <x:autoFilter ref="A1:H164"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -7167,7 +7167,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H163"/>
+  <x:dimension ref="A1:H164"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="9" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -7412,7 +7412,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>67592</x:v>
+        <x:v>99682</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
@@ -7625,33 +7625,33 @@
     </x:row>
     <x:row r="18" spans="1:8">
       <x:c r="A18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>-51</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>8339</x:v>
+        <x:v>702091</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8">
       <x:c r="A19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>54</x:v>
@@ -7669,7 +7669,7 @@
         <x:v>-51</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H19" s="1">
         <x:v>8339</x:v>
@@ -7677,106 +7677,106 @@
     </x:row>
     <x:row r="20" spans="1:8">
       <x:c r="A20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-51</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>0</x:v>
+        <x:v>8339</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8">
       <x:c r="A21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>9075</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8">
       <x:c r="A22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>-500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>51183</x:v>
+        <x:v>9075</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8">
       <x:c r="A23" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>0</x:v>
+        <x:v>51183</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8">
@@ -7784,10 +7784,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>85</x:v>
@@ -7796,7 +7796,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>84</x:v>
@@ -7807,25 +7807,25 @@
     </x:row>
     <x:row r="25" spans="1:8">
       <x:c r="A25" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>-3500</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H25" s="1">
         <x:v>0</x:v>
@@ -7836,10 +7836,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>88</x:v>
@@ -7848,7 +7848,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-3500</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>87</x:v>
@@ -7859,25 +7859,25 @@
     </x:row>
     <x:row r="27" spans="1:8">
       <x:c r="A27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H27" s="1">
         <x:v>0</x:v>
@@ -7885,129 +7885,129 @@
     </x:row>
     <x:row r="28" spans="1:8">
       <x:c r="A28" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-10</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:8">
       <x:c r="A29" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>5000</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:8">
       <x:c r="A30" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-1901</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>21265</x:v>
+        <x:v>5133</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:8">
       <x:c r="A31" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1901</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>0</x:v>
+        <x:v>21265</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:8">
       <x:c r="A32" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>0</x:v>
@@ -8015,25 +8015,25 @@
     </x:row>
     <x:row r="33" spans="1:8">
       <x:c r="A33" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>0</x:v>
@@ -8041,163 +8041,163 @@
     </x:row>
     <x:row r="34" spans="1:8">
       <x:c r="A34" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>-850</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>26114</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:8">
       <x:c r="A35" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-850</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>330449</x:v>
+        <x:v>26114</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:8">
       <x:c r="A36" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>2400</x:v>
+        <x:v>526047</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:8">
       <x:c r="A37" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>0</x:v>
+        <x:v>2400</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:8">
       <x:c r="A38" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:8">
       <x:c r="A39" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>1500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:8">
       <x:c r="A40" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>39</x:v>
@@ -8206,76 +8206,76 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:8">
       <x:c r="A41" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:8">
       <x:c r="A42" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>-95</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>42275</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:8">
       <x:c r="A43" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>34</x:v>
@@ -8284,94 +8284,94 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>-2900</x:v>
+        <x:v>-95</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>500</x:v>
+        <x:v>42275</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:8">
       <x:c r="A44" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2900</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>1500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:8">
       <x:c r="A45" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F45" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:8">
       <x:c r="A46" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F46" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H46" s="1">
         <x:v>0</x:v>
@@ -8379,25 +8379,25 @@
     </x:row>
     <x:row r="47" spans="1:8">
       <x:c r="A47" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H47" s="1">
         <x:v>0</x:v>
@@ -8408,10 +8408,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>167</x:v>
@@ -8420,65 +8420,65 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>164</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:8">
       <x:c r="A49" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>0</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:8">
       <x:c r="A50" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>-10</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>90014</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:8">
@@ -8492,206 +8492,206 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>-375</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>174</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>42958</x:v>
+        <x:v>90014</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:8">
       <x:c r="A52" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>-500</x:v>
+        <x:v>-375</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>1500</x:v>
+        <x:v>42958</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:8">
       <x:c r="A53" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>-200</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H53" s="1">
-        <x:v>251266</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:8">
       <x:c r="A54" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H54" s="1">
-        <x:v>10000</x:v>
+        <x:v>251266</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:8">
       <x:c r="A55" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>-1347</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H55" s="1">
-        <x:v>35205</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:8">
       <x:c r="A56" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>-13242</x:v>
+        <x:v>-1347</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H56" s="1">
-        <x:v>158894</x:v>
+        <x:v>35205</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:8">
       <x:c r="A57" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>-50</x:v>
+        <x:v>-13242</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H57" s="1">
-        <x:v>35388</x:v>
+        <x:v>158894</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:8">
       <x:c r="A58" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H58" s="1">
-        <x:v>76916</x:v>
+        <x:v>35388</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:8">
       <x:c r="A59" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
         <x:v>34</x:v>
@@ -8700,24 +8700,24 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>-2900</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H59" s="1">
-        <x:v>25700</x:v>
+        <x:v>71916</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:8">
       <x:c r="A60" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
         <x:v>34</x:v>
@@ -8726,232 +8726,232 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2900</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H60" s="1">
-        <x:v>355947</x:v>
+        <x:v>25700</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:8">
       <x:c r="A61" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H61" s="1">
-        <x:v>3000</x:v>
+        <x:v>622244</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:8">
       <x:c r="A62" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>-270</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H62" s="1">
-        <x:v>13265</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:8">
       <x:c r="A63" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-270</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H63" s="1">
-        <x:v>5000</x:v>
+        <x:v>13265</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:8">
       <x:c r="A64" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H64" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:8">
       <x:c r="A65" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H65" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:8">
       <x:c r="A66" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H66" s="1">
-        <x:v>3461</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:8">
       <x:c r="A67" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>-25</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H67" s="1">
-        <x:v>38904</x:v>
+        <x:v>3461</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:8">
       <x:c r="A68" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="H68" s="1">
-        <x:v>56848</x:v>
+        <x:v>38904</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:8">
       <x:c r="A69" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
         <x:v>34</x:v>
@@ -8960,544 +8960,544 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F69" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H69" s="1">
-        <x:v>30766</x:v>
+        <x:v>51848</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:8">
       <x:c r="A70" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>0</x:v>
+        <x:v>31807</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:8">
       <x:c r="A71" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H71" s="1">
-        <x:v>94803</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:8">
       <x:c r="A72" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>-2800</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>0</x:v>
+        <x:v>249782</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:8">
       <x:c r="A73" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2800</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:8">
       <x:c r="A74" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H74" s="1">
-        <x:v>114262</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:8">
       <x:c r="A75" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="H75" s="1">
-        <x:v>2000</x:v>
+        <x:v>222523</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:8">
       <x:c r="A76" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>-3400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>28982</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
       <x:c r="A77" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-3400</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="H77" s="1">
-        <x:v>0</x:v>
+        <x:v>28982</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:8">
       <x:c r="A78" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H78" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:8">
       <x:c r="A79" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="H79" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:8">
       <x:c r="A80" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F80" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H80" s="1">
-        <x:v>52742</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:8">
       <x:c r="A81" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>0</x:v>
+        <x:v>58803</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:8">
       <x:c r="A82" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:8">
       <x:c r="A83" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H83" s="1">
-        <x:v>4000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:8">
       <x:c r="A84" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>-510</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="H84" s="1">
-        <x:v>42500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:8">
       <x:c r="A85" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-510</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H85" s="1">
-        <x:v>2000</x:v>
+        <x:v>42500</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:8">
       <x:c r="A86" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>-475</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="H86" s="1">
-        <x:v>131385</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:8">
       <x:c r="A87" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>-250</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="H87" s="1">
-        <x:v>69371</x:v>
+        <x:v>131385</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:8">
       <x:c r="A88" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H88" s="1">
-        <x:v>500</x:v>
+        <x:v>69371</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:8">
       <x:c r="A89" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="H89" s="1">
-        <x:v>135047</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:8">
       <x:c r="A90" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
         <x:v>34</x:v>
@@ -9506,71 +9506,71 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="H90" s="1">
-        <x:v>111188</x:v>
+        <x:v>183604</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:8">
       <x:c r="A91" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="H91" s="1">
-        <x:v>1000</x:v>
+        <x:v>111188</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:8">
       <x:c r="A92" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="H92" s="1">
-        <x:v>10000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:8">
@@ -9578,10 +9578,10 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
         <x:v>304</x:v>
@@ -9590,24 +9590,24 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
         <x:v>303</x:v>
       </x:c>
       <x:c r="H93" s="1">
-        <x:v>1150</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:8">
       <x:c r="A94" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
         <x:v>304</x:v>
@@ -9616,13 +9616,13 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="H94" s="1">
-        <x:v>10000</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:8">
@@ -9630,10 +9630,10 @@
         <x:v>306</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
         <x:v>304</x:v>
@@ -9642,221 +9642,221 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
         <x:v>306</x:v>
       </x:c>
       <x:c r="H95" s="1">
-        <x:v>1150</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:8">
       <x:c r="A96" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H96" s="1">
-        <x:v>33320</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:8">
       <x:c r="A97" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="H97" s="1">
-        <x:v>0</x:v>
+        <x:v>33320</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:8">
       <x:c r="A98" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="H98" s="1">
-        <x:v>21095</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:8">
       <x:c r="A99" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="H99" s="1">
-        <x:v>0</x:v>
+        <x:v>21095</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:8">
       <x:c r="A100" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>-1</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="H100" s="1">
-        <x:v>26650</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:8">
       <x:c r="A101" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="H101" s="1">
-        <x:v>5000</x:v>
+        <x:v>26650</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:8">
       <x:c r="A102" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F102" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="H102" s="1">
-        <x:v>12000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:8">
       <x:c r="A103" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F103" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="H103" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:8">
@@ -9864,10 +9864,10 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
         <x:v>331</x:v>
@@ -9876,7 +9876,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
         <x:v>330</x:v>
@@ -9887,111 +9887,111 @@
     </x:row>
     <x:row r="105" spans="1:8">
       <x:c r="A105" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="H105" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:8">
       <x:c r="A106" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>-20</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="H106" s="1">
-        <x:v>14900</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:8">
       <x:c r="A107" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="H107" s="1">
-        <x:v>5000</x:v>
+        <x:v>14900</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:8">
       <x:c r="A108" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-19701</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="H108" s="1">
-        <x:v>49867</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:8">
       <x:c r="A109" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
         <x:v>34</x:v>
@@ -10000,24 +10000,24 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-8456</x:v>
+        <x:v>-19701</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="H109" s="1">
-        <x:v>95962</x:v>
+        <x:v>49967</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:8">
       <x:c r="A110" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
         <x:v>34</x:v>
@@ -10035,163 +10035,163 @@
         <x:v>-8456</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="H110" s="1">
-        <x:v>95962</x:v>
+        <x:v>162020</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:8">
       <x:c r="A111" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>-800</x:v>
+        <x:v>-8456</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="H111" s="1">
-        <x:v>58679</x:v>
+        <x:v>162020</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:8">
       <x:c r="A112" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="H112" s="1">
-        <x:v>0</x:v>
+        <x:v>58679</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:8">
       <x:c r="A113" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="H113" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:8">
       <x:c r="A114" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F114" s="1">
-        <x:v>-300</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G114" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="H114" s="1">
-        <x:v>36900</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:8">
       <x:c r="A115" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F115" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G115" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="H115" s="1">
-        <x:v>0</x:v>
+        <x:v>36900</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:8">
       <x:c r="A116" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F116" s="1">
         <x:v>-2500</x:v>
       </x:c>
       <x:c r="G116" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="H116" s="1">
         <x:v>0</x:v>
@@ -10199,85 +10199,85 @@
     </x:row>
     <x:row r="117" spans="1:8">
       <x:c r="A117" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F117" s="1">
-        <x:v>-100</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G117" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="H117" s="1">
-        <x:v>58000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:8">
       <x:c r="A118" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F118" s="1">
-        <x:v>-9</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G118" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="H118" s="1">
-        <x:v>15328</x:v>
+        <x:v>58000</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:8">
       <x:c r="A119" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F119" s="1">
-        <x:v>-4955</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G119" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="H119" s="1">
-        <x:v>64475</x:v>
+        <x:v>15349</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:8">
       <x:c r="A120" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
         <x:v>54</x:v>
@@ -10286,68 +10286,68 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-250</x:v>
+        <x:v>-4955</x:v>
       </x:c>
       <x:c r="G120" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="H120" s="1">
-        <x:v>42061</x:v>
+        <x:v>64475</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:8">
       <x:c r="A121" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F121" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G121" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="H121" s="1">
-        <x:v>0</x:v>
+        <x:v>42061</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:8">
       <x:c r="A122" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B122" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E122" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F122" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G122" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H122" s="1">
         <x:v>0</x:v>
@@ -10355,85 +10355,85 @@
     </x:row>
     <x:row r="123" spans="1:8">
       <x:c r="A123" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="F123" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G123" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="H123" s="1">
-        <x:v>12380</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:8">
       <x:c r="A124" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="E124" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F124" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G124" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="H124" s="1">
-        <x:v>3000</x:v>
+        <x:v>7380</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:8">
       <x:c r="A125" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F125" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G125" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="H125" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:8">
       <x:c r="A126" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
         <x:v>74</x:v>
@@ -10442,50 +10442,50 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F126" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G126" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="H126" s="1">
-        <x:v>2400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:8">
       <x:c r="A127" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F127" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G127" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="H127" s="1">
-        <x:v>0</x:v>
+        <x:v>2400</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:8">
       <x:c r="A128" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
         <x:v>46</x:v>
@@ -10494,154 +10494,154 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F128" s="1">
-        <x:v>-250</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G128" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="H128" s="1">
-        <x:v>6727</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:8">
       <x:c r="A129" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-7500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G129" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="H129" s="1">
-        <x:v>5000</x:v>
+        <x:v>6727</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:8">
       <x:c r="A130" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>-500</x:v>
+        <x:v>-7500</x:v>
       </x:c>
       <x:c r="G130" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="H130" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:8">
       <x:c r="A131" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G131" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="H131" s="1">
-        <x:v>2000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:8">
       <x:c r="A132" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G132" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="H132" s="1">
-        <x:v>131464</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:8">
       <x:c r="A133" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G133" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="H133" s="1">
-        <x:v>0</x:v>
+        <x:v>159727</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:8">
       <x:c r="A134" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
         <x:v>39</x:v>
@@ -10650,16 +10650,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G134" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="H134" s="1">
         <x:v>0</x:v>
@@ -10667,25 +10667,25 @@
     </x:row>
     <x:row r="135" spans="1:8">
       <x:c r="A135" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F135" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G135" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="H135" s="1">
         <x:v>0</x:v>
@@ -10696,10 +10696,10 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
         <x:v>420</x:v>
@@ -10708,62 +10708,62 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="F136" s="1">
-        <x:v>-1550</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G136" s="1" t="s">
         <x:v>419</x:v>
       </x:c>
       <x:c r="H136" s="1">
-        <x:v>193279</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:8">
       <x:c r="A137" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1550</x:v>
       </x:c>
       <x:c r="G137" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="H137" s="1">
-        <x:v>0</x:v>
+        <x:v>193279</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:8">
       <x:c r="A138" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F138" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G138" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="H138" s="1">
         <x:v>0</x:v>
@@ -10771,33 +10771,33 @@
     </x:row>
     <x:row r="139" spans="1:8">
       <x:c r="A139" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G139" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H139" s="1">
-        <x:v>19596</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:8">
       <x:c r="A140" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
         <x:v>46</x:v>
@@ -10806,102 +10806,102 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G140" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H140" s="1">
-        <x:v>18660</x:v>
+        <x:v>19596</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:8">
       <x:c r="A141" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="H141" s="1">
-        <x:v>6150</x:v>
+        <x:v>17260</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:8">
       <x:c r="A142" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="H142" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:8">
       <x:c r="A143" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F143" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H143" s="1">
-        <x:v>37943</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:8">
       <x:c r="A144" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
         <x:v>34</x:v>
@@ -10910,175 +10910,175 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F144" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="H144" s="1">
-        <x:v>46676</x:v>
+        <x:v>32943</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:8">
       <x:c r="A145" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G145" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="H145" s="1">
-        <x:v>0</x:v>
+        <x:v>41676</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:8">
       <x:c r="A146" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="H146" s="1">
-        <x:v>75893</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:8">
       <x:c r="A147" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="H147" s="1">
-        <x:v>0</x:v>
+        <x:v>84497</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:8">
       <x:c r="A148" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="H148" s="1">
-        <x:v>28400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:8">
       <x:c r="A149" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="H149" s="1">
-        <x:v>22566</x:v>
+        <x:v>28400</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:8">
       <x:c r="A150" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="H150" s="1">
-        <x:v>3750</x:v>
+        <x:v>22566</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:8">
@@ -11086,10 +11086,10 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
         <x:v>460</x:v>
@@ -11098,44 +11098,44 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
         <x:v>459</x:v>
       </x:c>
       <x:c r="H151" s="1">
-        <x:v>10000</x:v>
+        <x:v>3750</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:8">
       <x:c r="A152" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="H152" s="1">
-        <x:v>18414</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:8">
       <x:c r="A153" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
         <x:v>54</x:v>
@@ -11144,123 +11144,123 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-110</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="H153" s="1">
-        <x:v>5170</x:v>
+        <x:v>18414</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:8">
       <x:c r="A154" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-110</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="H154" s="1">
-        <x:v>6000</x:v>
+        <x:v>5170</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:8">
       <x:c r="A155" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B155" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F155" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="H155" s="1">
-        <x:v>10972</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:8">
       <x:c r="A156" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="F156" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="H156" s="1">
-        <x:v>57350</x:v>
+        <x:v>10972</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:8">
       <x:c r="A157" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="F157" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="H157" s="1">
-        <x:v>2500</x:v>
+        <x:v>57350</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:8">
@@ -11268,10 +11268,10 @@
         <x:v>477</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
         <x:v>478</x:v>
@@ -11280,24 +11280,24 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="F158" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
         <x:v>477</x:v>
       </x:c>
       <x:c r="H158" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:8">
       <x:c r="A159" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
         <x:v>478</x:v>
@@ -11306,13 +11306,13 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="F159" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="H159" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:8">
@@ -11320,10 +11320,10 @@
         <x:v>480</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
         <x:v>478</x:v>
@@ -11332,90 +11332,116 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="F160" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
         <x:v>480</x:v>
       </x:c>
       <x:c r="H160" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:8">
       <x:c r="A161" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B161" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="F161" s="1">
-        <x:v>-5131</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="H161" s="1">
-        <x:v>83966</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:8">
       <x:c r="A162" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B162" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="F162" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5131</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="H162" s="1">
-        <x:v>6000</x:v>
+        <x:v>83966</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:8">
       <x:c r="A163" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B163" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F163" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G163" s="1" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="H163" s="1">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:8">
+      <x:c r="A164" s="1" t="s">
         <x:v>487</x:v>
       </x:c>
-      <x:c r="H163" s="1">
+      <x:c r="B164" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C164" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D164" s="1" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="E164" s="1" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="F164" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G164" s="1" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="H164" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -1260,6 +1260,15 @@
   </x:si>
   <x:si>
     <x:t>FRIENDS OF DAVID SCHWEIKERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, JAMES AUSTIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00482737</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUSTIN SCOTT FOR CONGRESS INC</x:t>
   </x:si>
   <x:si>
     <x:t>SHAHEEN, JEANNE</x:t>
@@ -1574,8 +1583,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G228" totalsRowShown="0">
-  <x:autoFilter ref="A1:G228"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G229" totalsRowShown="0">
+  <x:autoFilter ref="A1:G229"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1590,8 +1599,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H164" totalsRowShown="0">
-  <x:autoFilter ref="A1:H164"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H165" totalsRowShown="0">
+  <x:autoFilter ref="A1:H165"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1894,7 +1903,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G228"/>
+  <x:dimension ref="A1:G229"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3557,7 +3566,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>-1700</x:v>
+        <x:v>-575</x:v>
       </x:c>
       <x:c r="G72" s="2">
         <x:v>45349</x:v>
@@ -3580,7 +3589,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>-575</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G73" s="2">
         <x:v>45349</x:v>
@@ -3603,7 +3612,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>-200</x:v>
+        <x:v>-1700</x:v>
       </x:c>
       <x:c r="G74" s="2">
         <x:v>45349</x:v>
@@ -5052,7 +5061,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G137" s="2">
         <x:v>45977</x:v>
@@ -5075,7 +5084,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G138" s="2">
         <x:v>45977</x:v>
@@ -5098,7 +5107,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-1800</x:v>
+        <x:v>-36</x:v>
       </x:c>
       <x:c r="G139" s="2">
         <x:v>45977</x:v>
@@ -5121,7 +5130,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G140" s="2">
         <x:v>45977</x:v>
@@ -5144,7 +5153,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-750</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="G141" s="2">
         <x:v>45977</x:v>
@@ -5167,7 +5176,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-36</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="G142" s="2">
         <x:v>45977</x:v>
@@ -5190,7 +5199,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-9</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G143" s="2">
         <x:v>45977</x:v>
@@ -5213,7 +5222,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-3</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G144" s="2">
         <x:v>45977</x:v>
@@ -5236,7 +5245,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-2</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G145" s="2">
         <x:v>45977</x:v>
@@ -5259,7 +5268,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-1</x:v>
+        <x:v>-1800</x:v>
       </x:c>
       <x:c r="G146" s="2">
         <x:v>45977</x:v>
@@ -6236,27 +6245,27 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B189" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="F189" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G189" s="2">
-        <x:v>38075</x:v>
+        <x:v>46112</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
       <x:c r="A190" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B190" s="1" t="s">
         <x:v>39</x:v>
@@ -6265,16 +6274,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F190" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G190" s="2">
-        <x:v>38764</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
@@ -6282,10 +6291,10 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
         <x:v>420</x:v>
@@ -6297,12 +6306,12 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G191" s="2">
-        <x:v>43201</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:7">
       <x:c r="A192" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B192" s="1" t="s">
         <x:v>54</x:v>
@@ -6311,13 +6320,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F192" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G192" s="2">
         <x:v>43201</x:v>
@@ -6325,7 +6334,7 @@
     </x:row>
     <x:row r="193" spans="1:7">
       <x:c r="A193" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B193" s="1" t="s">
         <x:v>54</x:v>
@@ -6334,13 +6343,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F193" s="1">
-        <x:v>-200</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G193" s="2">
         <x:v>43201</x:v>
@@ -6348,7 +6357,7 @@
     </x:row>
     <x:row r="194" spans="1:7">
       <x:c r="A194" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B194" s="1" t="s">
         <x:v>54</x:v>
@@ -6357,13 +6366,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F194" s="1">
-        <x:v>-100</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G194" s="2">
         <x:v>43201</x:v>
@@ -6371,25 +6380,25 @@
     </x:row>
     <x:row r="195" spans="1:7">
       <x:c r="A195" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B195" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C195" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E195" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F195" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G195" s="2">
-        <x:v>39777</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:7">
@@ -6397,10 +6406,10 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="B196" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D196" s="1" t="s">
         <x:v>423</x:v>
@@ -6409,10 +6418,10 @@
         <x:v>424</x:v>
       </x:c>
       <x:c r="F196" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G196" s="2">
-        <x:v>43465</x:v>
+        <x:v>39777</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:7">
@@ -6420,10 +6429,10 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B197" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C197" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D197" s="1" t="s">
         <x:v>426</x:v>
@@ -6435,7 +6444,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G197" s="2">
-        <x:v>39010</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:7">
@@ -6443,10 +6452,10 @@
         <x:v>428</x:v>
       </x:c>
       <x:c r="B198" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C198" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D198" s="1" t="s">
         <x:v>429</x:v>
@@ -6455,10 +6464,10 @@
         <x:v>430</x:v>
       </x:c>
       <x:c r="F198" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G198" s="2">
-        <x:v>42783</x:v>
+        <x:v>39010</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:7">
@@ -6478,10 +6487,10 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="F199" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G199" s="2">
-        <x:v>45692</x:v>
+        <x:v>42783</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
@@ -6489,10 +6498,10 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B200" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
         <x:v>435</x:v>
@@ -6501,10 +6510,10 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="F200" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G200" s="2">
-        <x:v>43799</x:v>
+        <x:v>45692</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
@@ -6512,45 +6521,45 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="B201" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C201" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F201" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G201" s="2">
-        <x:v>38075</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C202" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D202" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E202" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F202" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G202" s="2">
-        <x:v>45698</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
@@ -6573,7 +6582,7 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G203" s="2">
-        <x:v>45665</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
@@ -6581,10 +6590,10 @@
         <x:v>444</x:v>
       </x:c>
       <x:c r="B204" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C204" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D204" s="1" t="s">
         <x:v>445</x:v>
@@ -6593,10 +6602,10 @@
         <x:v>446</x:v>
       </x:c>
       <x:c r="F204" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G204" s="2">
-        <x:v>40724</x:v>
+        <x:v>45665</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:7">
@@ -6604,10 +6613,10 @@
         <x:v>447</x:v>
       </x:c>
       <x:c r="B205" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C205" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D205" s="1" t="s">
         <x:v>448</x:v>
@@ -6616,10 +6625,10 @@
         <x:v>449</x:v>
       </x:c>
       <x:c r="F205" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G205" s="2">
-        <x:v>46000</x:v>
+        <x:v>40724</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:7">
@@ -6627,10 +6636,10 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="B206" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
         <x:v>451</x:v>
@@ -6639,10 +6648,10 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="F206" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G206" s="2">
-        <x:v>43465</x:v>
+        <x:v>46000</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:7">
@@ -6650,10 +6659,10 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B207" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
         <x:v>454</x:v>
@@ -6662,10 +6671,10 @@
         <x:v>455</x:v>
       </x:c>
       <x:c r="F207" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G207" s="2">
-        <x:v>44845</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:7">
@@ -6673,10 +6682,10 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B208" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D208" s="1" t="s">
         <x:v>457</x:v>
@@ -6685,10 +6694,10 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="F208" s="1">
-        <x:v>-300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G208" s="2">
-        <x:v>44645</x:v>
+        <x:v>44845</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:7">
@@ -6696,10 +6705,10 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="B209" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C209" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D209" s="1" t="s">
         <x:v>460</x:v>
@@ -6708,33 +6717,33 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="F209" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G209" s="2">
-        <x:v>41900</x:v>
+        <x:v>44645</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:7">
       <x:c r="A210" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B210" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C210" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D210" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E210" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F210" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G210" s="2">
-        <x:v>41813</x:v>
+        <x:v>41900</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:7">
@@ -6742,10 +6751,10 @@
         <x:v>462</x:v>
       </x:c>
       <x:c r="B211" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C211" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D211" s="1" t="s">
         <x:v>463</x:v>
@@ -6754,10 +6763,10 @@
         <x:v>464</x:v>
       </x:c>
       <x:c r="F211" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G211" s="2">
-        <x:v>43573</x:v>
+        <x:v>41813</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:7">
@@ -6777,15 +6786,15 @@
         <x:v>467</x:v>
       </x:c>
       <x:c r="F212" s="1">
-        <x:v>-100</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G212" s="2">
-        <x:v>42236</x:v>
+        <x:v>43573</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:7">
       <x:c r="A213" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B213" s="1" t="s">
         <x:v>54</x:v>
@@ -6794,13 +6803,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F213" s="1">
-        <x:v>-10</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G213" s="2">
         <x:v>42236</x:v>
@@ -6811,10 +6820,10 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B214" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
         <x:v>469</x:v>
@@ -6823,10 +6832,10 @@
         <x:v>470</x:v>
       </x:c>
       <x:c r="F214" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G214" s="2">
-        <x:v>44804</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:7">
@@ -6834,10 +6843,10 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="B215" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C215" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D215" s="1" t="s">
         <x:v>472</x:v>
@@ -6849,7 +6858,7 @@
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G215" s="2">
-        <x:v>37787</x:v>
+        <x:v>44804</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:7">
@@ -6857,10 +6866,10 @@
         <x:v>474</x:v>
       </x:c>
       <x:c r="B216" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C216" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D216" s="1" t="s">
         <x:v>475</x:v>
@@ -6869,10 +6878,10 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="F216" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G216" s="2">
-        <x:v>45551</x:v>
+        <x:v>37787</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:7">
@@ -6880,10 +6889,10 @@
         <x:v>477</x:v>
       </x:c>
       <x:c r="B217" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C217" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D217" s="1" t="s">
         <x:v>478</x:v>
@@ -6892,33 +6901,33 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="F217" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G217" s="2">
-        <x:v>37736</x:v>
+        <x:v>45551</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:7">
       <x:c r="A218" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B218" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C218" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D218" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E218" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F218" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G218" s="2">
-        <x:v>41453</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:7">
@@ -6926,73 +6935,73 @@
         <x:v>480</x:v>
       </x:c>
       <x:c r="B219" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C219" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D219" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E219" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F219" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G219" s="2">
-        <x:v>37736</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:7">
       <x:c r="A220" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B220" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C220" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D220" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E220" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F220" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G220" s="2">
-        <x:v>41453</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:7">
       <x:c r="A221" s="1" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B221" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C221" s="1" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="D221" s="1" t="s">
         <x:v>481</x:v>
       </x:c>
-      <x:c r="B221" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C221" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D221" s="1" t="s">
+      <x:c r="E221" s="1" t="s">
         <x:v>482</x:v>
       </x:c>
-      <x:c r="E221" s="1" t="s">
-        <x:v>483</x:v>
-      </x:c>
       <x:c r="F221" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G221" s="2">
-        <x:v>45077</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:7">
       <x:c r="A222" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B222" s="1" t="s">
         <x:v>34</x:v>
@@ -7001,13 +7010,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D222" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E222" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F222" s="1">
-        <x:v>-950</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G222" s="2">
         <x:v>45077</x:v>
@@ -7015,7 +7024,7 @@
     </x:row>
     <x:row r="223" spans="1:7">
       <x:c r="A223" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B223" s="1" t="s">
         <x:v>34</x:v>
@@ -7024,13 +7033,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D223" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E223" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F223" s="1">
-        <x:v>-713</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G223" s="2">
         <x:v>45077</x:v>
@@ -7038,7 +7047,7 @@
     </x:row>
     <x:row r="224" spans="1:7">
       <x:c r="A224" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B224" s="1" t="s">
         <x:v>34</x:v>
@@ -7047,13 +7056,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D224" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E224" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F224" s="1">
-        <x:v>-475</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G224" s="2">
         <x:v>45077</x:v>
@@ -7061,7 +7070,7 @@
     </x:row>
     <x:row r="225" spans="1:7">
       <x:c r="A225" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B225" s="1" t="s">
         <x:v>34</x:v>
@@ -7070,13 +7079,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D225" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E225" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F225" s="1">
-        <x:v>-238</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G225" s="2">
         <x:v>45077</x:v>
@@ -7087,10 +7096,10 @@
         <x:v>484</x:v>
       </x:c>
       <x:c r="B226" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C226" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D226" s="1" t="s">
         <x:v>485</x:v>
@@ -7099,10 +7108,10 @@
         <x:v>486</x:v>
       </x:c>
       <x:c r="F226" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G226" s="2">
-        <x:v>40178</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
@@ -7110,10 +7119,10 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B227" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C227" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D227" s="1" t="s">
         <x:v>488</x:v>
@@ -7122,15 +7131,15 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="F227" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G227" s="2">
-        <x:v>39629</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="228" spans="1:7">
       <x:c r="A228" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B228" s="1" t="s">
         <x:v>74</x:v>
@@ -7139,15 +7148,38 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="D228" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="E228" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F228" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G228" s="2">
+        <x:v>39629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:7">
+      <x:c r="A229" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B229" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C229" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D229" s="1" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="E229" s="1" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="F229" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G229" s="2">
         <x:v>39660</x:v>
       </x:c>
     </x:row>
@@ -7167,7 +7199,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H164"/>
+  <x:dimension ref="A1:H165"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="9" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -7198,13 +7230,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -8114,7 +8146,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>526047</x:v>
+        <x:v>527848</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:8">
@@ -8998,7 +9030,7 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>31807</x:v>
+        <x:v>31858</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:8">
@@ -9050,7 +9082,7 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>249782</x:v>
+        <x:v>249783</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:8">
@@ -9128,7 +9160,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="H75" s="1">
-        <x:v>222523</x:v>
+        <x:v>222609</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:8">
@@ -9284,7 +9316,7 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>58803</x:v>
+        <x:v>65304</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:8">
@@ -9518,7 +9550,7 @@
         <x:v>294</x:v>
       </x:c>
       <x:c r="H90" s="1">
-        <x:v>183604</x:v>
+        <x:v>183610</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:8">
@@ -10038,7 +10070,7 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="H110" s="1">
-        <x:v>162020</x:v>
+        <x:v>162021</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:8">
@@ -10064,7 +10096,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="H111" s="1">
-        <x:v>162020</x:v>
+        <x:v>162021</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:8">
@@ -10644,30 +10676,30 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G134" s="1" t="s">
         <x:v>415</x:v>
       </x:c>
       <x:c r="H134" s="1">
-        <x:v>0</x:v>
+        <x:v>53221</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:8">
       <x:c r="A135" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
         <x:v>39</x:v>
@@ -10676,16 +10708,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F135" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G135" s="1" t="s">
         <x:v>418</x:v>
-      </x:c>
-      <x:c r="F135" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G135" s="1" t="s">
-        <x:v>416</x:v>
       </x:c>
       <x:c r="H135" s="1">
         <x:v>0</x:v>
@@ -10696,10 +10728,10 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
         <x:v>420</x:v>
@@ -10708,7 +10740,7 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="F136" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G136" s="1" t="s">
         <x:v>419</x:v>
@@ -10719,28 +10751,28 @@
     </x:row>
     <x:row r="137" spans="1:8">
       <x:c r="A137" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-1550</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G137" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="H137" s="1">
-        <x:v>193279</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:8">
@@ -10748,10 +10780,10 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
         <x:v>423</x:v>
@@ -10760,13 +10792,13 @@
         <x:v>424</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1550</x:v>
       </x:c>
       <x:c r="G138" s="1" t="s">
         <x:v>422</x:v>
       </x:c>
       <x:c r="H138" s="1">
-        <x:v>0</x:v>
+        <x:v>193279</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:8">
@@ -10774,10 +10806,10 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
         <x:v>426</x:v>
@@ -10800,10 +10832,10 @@
         <x:v>428</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
         <x:v>429</x:v>
@@ -10812,13 +10844,13 @@
         <x:v>430</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G140" s="1" t="s">
         <x:v>428</x:v>
       </x:c>
       <x:c r="H140" s="1">
-        <x:v>19596</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:8">
@@ -10838,13 +10870,13 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
         <x:v>431</x:v>
       </x:c>
       <x:c r="H141" s="1">
-        <x:v>17260</x:v>
+        <x:v>19596</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:8">
@@ -10852,10 +10884,10 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
         <x:v>435</x:v>
@@ -10864,13 +10896,13 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
         <x:v>434</x:v>
       </x:c>
       <x:c r="H142" s="1">
-        <x:v>6150</x:v>
+        <x:v>17260</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:8">
@@ -10878,51 +10910,51 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
         <x:v>437</x:v>
       </x:c>
       <x:c r="H143" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:8">
       <x:c r="A144" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F144" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H144" s="1">
-        <x:v>32943</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:8">
@@ -10948,7 +10980,7 @@
         <x:v>441</x:v>
       </x:c>
       <x:c r="H145" s="1">
-        <x:v>41676</x:v>
+        <x:v>32943</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:8">
@@ -10956,10 +10988,10 @@
         <x:v>444</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
         <x:v>445</x:v>
@@ -10968,13 +11000,13 @@
         <x:v>446</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
         <x:v>444</x:v>
       </x:c>
       <x:c r="H146" s="1">
-        <x:v>0</x:v>
+        <x:v>41676</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:8">
@@ -10982,10 +11014,10 @@
         <x:v>447</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
         <x:v>448</x:v>
@@ -10994,13 +11026,13 @@
         <x:v>449</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
         <x:v>447</x:v>
       </x:c>
       <x:c r="H147" s="1">
-        <x:v>84497</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:8">
@@ -11008,10 +11040,10 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
         <x:v>451</x:v>
@@ -11020,13 +11052,13 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
         <x:v>450</x:v>
       </x:c>
       <x:c r="H148" s="1">
-        <x:v>0</x:v>
+        <x:v>84497</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:8">
@@ -11034,10 +11066,10 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
         <x:v>454</x:v>
@@ -11046,13 +11078,13 @@
         <x:v>455</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
         <x:v>453</x:v>
       </x:c>
       <x:c r="H149" s="1">
-        <x:v>28400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:8">
@@ -11060,10 +11092,10 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
         <x:v>457</x:v>
@@ -11072,13 +11104,13 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
         <x:v>456</x:v>
       </x:c>
       <x:c r="H150" s="1">
-        <x:v>22566</x:v>
+        <x:v>28400</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:8">
@@ -11086,10 +11118,10 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
         <x:v>460</x:v>
@@ -11098,39 +11130,39 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
         <x:v>459</x:v>
       </x:c>
       <x:c r="H151" s="1">
-        <x:v>3750</x:v>
+        <x:v>22566</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:8">
       <x:c r="A152" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="H152" s="1">
-        <x:v>10000</x:v>
+        <x:v>3750</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:8">
@@ -11138,10 +11170,10 @@
         <x:v>462</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
         <x:v>463</x:v>
@@ -11150,13 +11182,13 @@
         <x:v>464</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
         <x:v>462</x:v>
       </x:c>
       <x:c r="H153" s="1">
-        <x:v>18414</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:8">
@@ -11176,13 +11208,13 @@
         <x:v>467</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>-110</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
         <x:v>465</x:v>
       </x:c>
       <x:c r="H154" s="1">
-        <x:v>5170</x:v>
+        <x:v>18414</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:8">
@@ -11190,10 +11222,10 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B155" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
         <x:v>469</x:v>
@@ -11202,13 +11234,13 @@
         <x:v>470</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-110</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
         <x:v>468</x:v>
       </x:c>
       <x:c r="H155" s="1">
-        <x:v>6000</x:v>
+        <x:v>5170</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:8">
@@ -11216,10 +11248,10 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
         <x:v>472</x:v>
@@ -11234,7 +11266,7 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="H156" s="1">
-        <x:v>10972</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:8">
@@ -11242,10 +11274,10 @@
         <x:v>474</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
         <x:v>475</x:v>
@@ -11254,13 +11286,13 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="F157" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
         <x:v>474</x:v>
       </x:c>
       <x:c r="H157" s="1">
-        <x:v>57350</x:v>
+        <x:v>10972</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:8">
@@ -11268,10 +11300,10 @@
         <x:v>477</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
         <x:v>478</x:v>
@@ -11280,39 +11312,39 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="F158" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
         <x:v>477</x:v>
       </x:c>
       <x:c r="H158" s="1">
-        <x:v>2500</x:v>
+        <x:v>57350</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:8">
       <x:c r="A159" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F159" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="H159" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:8">
@@ -11320,77 +11352,77 @@
         <x:v>480</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F160" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
         <x:v>480</x:v>
       </x:c>
       <x:c r="H160" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:8">
       <x:c r="A161" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B161" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F161" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="H161" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:8">
       <x:c r="A162" s="1" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B162" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C162" s="1" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="D162" s="1" t="s">
         <x:v>481</x:v>
       </x:c>
-      <x:c r="B162" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C162" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D162" s="1" t="s">
+      <x:c r="E162" s="1" t="s">
         <x:v>482</x:v>
       </x:c>
-      <x:c r="E162" s="1" t="s">
+      <x:c r="F162" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G162" s="1" t="s">
         <x:v>483</x:v>
       </x:c>
-      <x:c r="F162" s="1">
-        <x:v>-5131</x:v>
-      </x:c>
-      <x:c r="G162" s="1" t="s">
-        <x:v>481</x:v>
-      </x:c>
       <x:c r="H162" s="1">
-        <x:v>83966</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:8">
@@ -11398,10 +11430,10 @@
         <x:v>484</x:v>
       </x:c>
       <x:c r="B163" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
         <x:v>485</x:v>
@@ -11410,13 +11442,13 @@
         <x:v>486</x:v>
       </x:c>
       <x:c r="F163" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5131</x:v>
       </x:c>
       <x:c r="G163" s="1" t="s">
         <x:v>484</x:v>
       </x:c>
       <x:c r="H163" s="1">
-        <x:v>6000</x:v>
+        <x:v>83966</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:8">
@@ -11424,10 +11456,10 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B164" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D164" s="1" t="s">
         <x:v>488</x:v>
@@ -11442,6 +11474,32 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="H164" s="1">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:8">
+      <x:c r="A165" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B165" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C165" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D165" s="1" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="E165" s="1" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="F165" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G165" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="H165" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -630,6 +630,15 @@
   </x:si>
   <x:si>
     <x:t>GIBBS FOR CONGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00816660</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAN GOLDMAN FOR NEW YORK</x:t>
   </x:si>
   <x:si>
     <x:t>GONZALES, ERNEST ANTHONY TONY II</x:t>
@@ -1583,8 +1592,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G229" totalsRowShown="0">
-  <x:autoFilter ref="A1:G229"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G232" totalsRowShown="0">
+  <x:autoFilter ref="A1:G232"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1599,8 +1608,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H165" totalsRowShown="0">
-  <x:autoFilter ref="A1:H165"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:H166" totalsRowShown="0">
+  <x:autoFilter ref="A1:H166"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1903,7 +1912,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G229"/>
+  <x:dimension ref="A1:G232"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3796,268 +3805,268 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-175</x:v>
       </x:c>
       <x:c r="G82" s="2">
-        <x:v>45980</x:v>
+        <x:v>46123</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="G83" s="2">
-        <x:v>38184</x:v>
+        <x:v>46123</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>-250</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G84" s="2">
-        <x:v>43410</x:v>
+        <x:v>46123</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>-20</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G85" s="2">
-        <x:v>43410</x:v>
+        <x:v>45980</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G86" s="2">
-        <x:v>42017</x:v>
+        <x:v>38184</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G87" s="2">
-        <x:v>38764</x:v>
+        <x:v>43410</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G88" s="2">
-        <x:v>41284</x:v>
+        <x:v>43410</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F89" s="1">
         <x:v>-2500</x:v>
       </x:c>
       <x:c r="G89" s="2">
-        <x:v>44893</x:v>
+        <x:v>42017</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>-25</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G90" s="2">
-        <x:v>41711</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G91" s="2">
-        <x:v>45698</x:v>
+        <x:v>41284</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G92" s="2">
-        <x:v>45629</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>-500</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G93" s="2">
-        <x:v>39813</x:v>
+        <x:v>41711</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
         <x:v>34</x:v>
@@ -4066,67 +4075,67 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F94" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G94" s="2">
-        <x:v>46044</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>-2800</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G95" s="2">
-        <x:v>41893</x:v>
+        <x:v>45629</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F96" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G96" s="2">
-        <x:v>38717</x:v>
+        <x:v>39813</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
         <x:v>34</x:v>
@@ -4135,292 +4144,292 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F97" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G97" s="2">
-        <x:v>46051</x:v>
+        <x:v>46044</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2800</x:v>
       </x:c>
       <x:c r="G98" s="2">
-        <x:v>45617</x:v>
+        <x:v>41893</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G99" s="2">
-        <x:v>40602</x:v>
+        <x:v>38717</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G100" s="2">
-        <x:v>40602</x:v>
+        <x:v>46051</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G101" s="2">
-        <x:v>44727</x:v>
+        <x:v>45617</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G102" s="2">
-        <x:v>38990</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G103" s="2">
-        <x:v>38292</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="F104" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G104" s="2">
-        <x:v>45638</x:v>
+        <x:v>44727</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F105" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G105" s="2">
-        <x:v>39512</x:v>
+        <x:v>38990</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G106" s="2">
-        <x:v>45517</x:v>
+        <x:v>38292</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G107" s="2">
-        <x:v>40178</x:v>
+        <x:v>45638</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G108" s="2">
-        <x:v>45533</x:v>
+        <x:v>39512</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-9</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G109" s="2">
-        <x:v>45533</x:v>
+        <x:v>45517</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
@@ -4428,10 +4437,10 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
         <x:v>280</x:v>
@@ -4440,10 +4449,10 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>-1</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G110" s="2">
-        <x:v>45533</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
@@ -4451,10 +4460,10 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
         <x:v>283</x:v>
@@ -4463,15 +4472,15 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G111" s="2">
-        <x:v>44893</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
         <x:v>34</x:v>
@@ -4480,67 +4489,67 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>-475</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G112" s="2">
-        <x:v>45077</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G113" s="2">
-        <x:v>43799</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F114" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G114" s="2">
-        <x:v>37855</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
         <x:v>34</x:v>
@@ -4549,119 +4558,119 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F115" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G115" s="2">
-        <x:v>45638</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F116" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G116" s="2">
-        <x:v>44716</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F117" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G117" s="2">
-        <x:v>42004</x:v>
+        <x:v>37855</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
       <x:c r="A118" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F118" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G118" s="2">
-        <x:v>43167</x:v>
+        <x:v>45638</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
       <x:c r="A119" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F119" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G119" s="2">
-        <x:v>44893</x:v>
+        <x:v>44716</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7">
       <x:c r="A120" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
         <x:v>304</x:v>
@@ -4670,10 +4679,10 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G120" s="2">
-        <x:v>43167</x:v>
+        <x:v>42004</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
@@ -4681,344 +4690,344 @@
         <x:v>306</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F121" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G121" s="2">
-        <x:v>44893</x:v>
+        <x:v>43167</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7">
       <x:c r="A122" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B122" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C122" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D122" s="1" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="B122" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C122" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D122" s="1" t="s">
+      <x:c r="E122" s="1" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="E122" s="1" t="s">
-        <x:v>309</x:v>
-      </x:c>
       <x:c r="F122" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G122" s="2">
-        <x:v>40602</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:7">
       <x:c r="A123" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F123" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G123" s="2">
-        <x:v>40422</x:v>
+        <x:v>43167</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E124" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F124" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G124" s="2">
-        <x:v>42818</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F125" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G125" s="2">
-        <x:v>45107</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:7">
       <x:c r="A126" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F126" s="1">
-        <x:v>-1</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G126" s="2">
-        <x:v>45408</x:v>
+        <x:v>40422</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7">
       <x:c r="A127" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="F127" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G127" s="2">
-        <x:v>43390</x:v>
+        <x:v>42818</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7">
       <x:c r="A128" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F128" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G128" s="2">
-        <x:v>43282</x:v>
+        <x:v>45107</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
       <x:c r="A129" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G129" s="2">
-        <x:v>44013</x:v>
+        <x:v>45408</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="F130" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G130" s="2">
-        <x:v>44022</x:v>
+        <x:v>43390</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G131" s="2">
-        <x:v>41926</x:v>
+        <x:v>43282</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>-20</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G132" s="2">
-        <x:v>41698</x:v>
+        <x:v>44013</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G133" s="2">
-        <x:v>45484</x:v>
+        <x:v>44022</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G134" s="2">
-        <x:v>45957</x:v>
+        <x:v>41926</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F135" s="1">
-        <x:v>-1650</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G135" s="2">
-        <x:v>45959</x:v>
+        <x:v>41698</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:7">
@@ -5026,10 +5035,10 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
         <x:v>345</x:v>
@@ -5038,15 +5047,15 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F136" s="1">
-        <x:v>-1650</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G136" s="2">
-        <x:v>45977</x:v>
+        <x:v>45484</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
         <x:v>34</x:v>
@@ -5055,21 +5064,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F137" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G137" s="2">
-        <x:v>45977</x:v>
+        <x:v>45957</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
         <x:v>34</x:v>
@@ -5078,21 +5087,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="G138" s="2">
-        <x:v>45977</x:v>
+        <x:v>45959</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:7">
       <x:c r="A139" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
         <x:v>34</x:v>
@@ -5101,13 +5110,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-36</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="G139" s="2">
         <x:v>45977</x:v>
@@ -5115,7 +5124,7 @@
     </x:row>
     <x:row r="140" spans="1:7">
       <x:c r="A140" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
         <x:v>34</x:v>
@@ -5124,13 +5133,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-9</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G140" s="2">
         <x:v>45977</x:v>
@@ -5138,7 +5147,7 @@
     </x:row>
     <x:row r="141" spans="1:7">
       <x:c r="A141" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
         <x:v>34</x:v>
@@ -5147,13 +5156,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-3</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G141" s="2">
         <x:v>45977</x:v>
@@ -5161,7 +5170,7 @@
     </x:row>
     <x:row r="142" spans="1:7">
       <x:c r="A142" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
         <x:v>34</x:v>
@@ -5170,13 +5179,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-2</x:v>
+        <x:v>-36</x:v>
       </x:c>
       <x:c r="G142" s="2">
         <x:v>45977</x:v>
@@ -5184,7 +5193,7 @@
     </x:row>
     <x:row r="143" spans="1:7">
       <x:c r="A143" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
         <x:v>34</x:v>
@@ -5193,13 +5202,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-1</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G143" s="2">
         <x:v>45977</x:v>
@@ -5207,7 +5216,7 @@
     </x:row>
     <x:row r="144" spans="1:7">
       <x:c r="A144" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
         <x:v>34</x:v>
@@ -5216,13 +5225,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="G144" s="2">
         <x:v>45977</x:v>
@@ -5230,7 +5239,7 @@
     </x:row>
     <x:row r="145" spans="1:7">
       <x:c r="A145" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
         <x:v>34</x:v>
@@ -5239,13 +5248,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="G145" s="2">
         <x:v>45977</x:v>
@@ -5253,7 +5262,7 @@
     </x:row>
     <x:row r="146" spans="1:7">
       <x:c r="A146" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
         <x:v>34</x:v>
@@ -5262,13 +5271,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-1800</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G146" s="2">
         <x:v>45977</x:v>
@@ -5276,7 +5285,7 @@
     </x:row>
     <x:row r="147" spans="1:7">
       <x:c r="A147" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
         <x:v>34</x:v>
@@ -5285,16 +5294,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G147" s="2">
-        <x:v>45980</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:7">
@@ -5314,10 +5323,10 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-238</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G148" s="2">
-        <x:v>45077</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
@@ -5337,10 +5346,10 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-1425</x:v>
+        <x:v>-1800</x:v>
       </x:c>
       <x:c r="G149" s="2">
-        <x:v>45077</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:7">
@@ -5360,15 +5369,15 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-950</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G150" s="2">
-        <x:v>45077</x:v>
+        <x:v>45980</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
         <x:v>34</x:v>
@@ -5377,13 +5386,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-713</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G151" s="2">
         <x:v>45077</x:v>
@@ -5391,7 +5400,7 @@
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
         <x:v>34</x:v>
@@ -5400,13 +5409,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>-475</x:v>
+        <x:v>-1425</x:v>
       </x:c>
       <x:c r="G152" s="2">
         <x:v>45077</x:v>
@@ -5414,7 +5423,7 @@
     </x:row>
     <x:row r="153" spans="1:7">
       <x:c r="A153" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
         <x:v>34</x:v>
@@ -5423,13 +5432,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G153" s="2">
         <x:v>45077</x:v>
@@ -5437,7 +5446,7 @@
     </x:row>
     <x:row r="154" spans="1:7">
       <x:c r="A154" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
         <x:v>34</x:v>
@@ -5446,13 +5455,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>-1900</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G154" s="2">
         <x:v>45077</x:v>
@@ -5469,13 +5478,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>-1900</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G155" s="2">
         <x:v>45077</x:v>
@@ -5492,10 +5501,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F156" s="1">
         <x:v>-2755</x:v>
@@ -5515,13 +5524,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F157" s="1">
-        <x:v>-475</x:v>
+        <x:v>-1900</x:v>
       </x:c>
       <x:c r="G157" s="2">
         <x:v>45077</x:v>
@@ -5529,7 +5538,7 @@
     </x:row>
     <x:row r="158" spans="1:7">
       <x:c r="A158" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
         <x:v>34</x:v>
@@ -5538,13 +5547,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F158" s="1">
-        <x:v>-713</x:v>
+        <x:v>-1900</x:v>
       </x:c>
       <x:c r="G158" s="2">
         <x:v>45077</x:v>
@@ -5552,7 +5561,7 @@
     </x:row>
     <x:row r="159" spans="1:7">
       <x:c r="A159" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
         <x:v>34</x:v>
@@ -5561,13 +5570,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F159" s="1">
-        <x:v>-950</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G159" s="2">
         <x:v>45077</x:v>
@@ -5575,7 +5584,7 @@
     </x:row>
     <x:row r="160" spans="1:7">
       <x:c r="A160" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
         <x:v>34</x:v>
@@ -5584,13 +5593,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F160" s="1">
-        <x:v>-1425</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G160" s="2">
         <x:v>45077</x:v>
@@ -5598,7 +5607,7 @@
     </x:row>
     <x:row r="161" spans="1:7">
       <x:c r="A161" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B161" s="1" t="s">
         <x:v>34</x:v>
@@ -5607,13 +5616,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F161" s="1">
-        <x:v>-238</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G161" s="2">
         <x:v>45077</x:v>
@@ -5621,99 +5630,99 @@
     </x:row>
     <x:row r="162" spans="1:7">
       <x:c r="A162" s="1" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B162" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C162" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D162" s="1" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="B162" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C162" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D162" s="1" t="s">
+      <x:c r="E162" s="1" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="E162" s="1" t="s">
-        <x:v>353</x:v>
-      </x:c>
       <x:c r="F162" s="1">
-        <x:v>-800</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G162" s="2">
-        <x:v>40602</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:7">
       <x:c r="A163" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B163" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F163" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1425</x:v>
       </x:c>
       <x:c r="G163" s="2">
-        <x:v>37736</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:7">
       <x:c r="A164" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B164" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D164" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F164" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G164" s="2">
-        <x:v>39810</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:7">
       <x:c r="A165" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="F165" s="1">
-        <x:v>-300</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="G165" s="2">
-        <x:v>44767</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:7">
       <x:c r="A166" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
         <x:v>39</x:v>
@@ -5722,113 +5731,113 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F166" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G166" s="2">
-        <x:v>41010</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:7">
       <x:c r="A167" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F167" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G167" s="2">
-        <x:v>41840</x:v>
+        <x:v>39810</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:7">
       <x:c r="A168" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B168" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F168" s="1">
-        <x:v>-100</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G168" s="2">
-        <x:v>40602</x:v>
+        <x:v>44767</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:7">
       <x:c r="A169" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B169" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F169" s="1">
-        <x:v>-9</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G169" s="2">
-        <x:v>45972</x:v>
+        <x:v>41010</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:7">
       <x:c r="A170" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B170" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D170" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F170" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G170" s="2">
-        <x:v>40602</x:v>
+        <x:v>41840</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:7">
       <x:c r="A171" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B171" s="1" t="s">
         <x:v>54</x:v>
@@ -5837,13 +5846,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D171" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F171" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G171" s="2">
         <x:v>40602</x:v>
@@ -5854,10 +5863,10 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="B172" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
         <x:v>376</x:v>
@@ -5866,15 +5875,15 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="F172" s="1">
-        <x:v>-500</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G172" s="2">
-        <x:v>40602</x:v>
+        <x:v>45972</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:7">
       <x:c r="A173" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
         <x:v>54</x:v>
@@ -5883,13 +5892,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F173" s="1">
-        <x:v>-50</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G173" s="2">
         <x:v>40602</x:v>
@@ -5897,7 +5906,7 @@
     </x:row>
     <x:row r="174" spans="1:7">
       <x:c r="A174" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
         <x:v>54</x:v>
@@ -5906,13 +5915,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F174" s="1">
-        <x:v>-5</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G174" s="2">
         <x:v>40602</x:v>
@@ -5935,7 +5944,7 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="F175" s="1">
-        <x:v>-250</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G175" s="2">
         <x:v>40602</x:v>
@@ -5943,99 +5952,99 @@
     </x:row>
     <x:row r="176" spans="1:7">
       <x:c r="A176" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B176" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F176" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G176" s="2">
-        <x:v>38075</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:7">
       <x:c r="A177" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B177" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F177" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="G177" s="2">
-        <x:v>41455</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:7">
       <x:c r="A178" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B178" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F178" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G178" s="2">
-        <x:v>45698</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:7">
       <x:c r="A179" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B179" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F179" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G179" s="2">
-        <x:v>43646</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:7">
       <x:c r="A180" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B180" s="1" t="s">
         <x:v>74</x:v>
@@ -6044,315 +6053,315 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F180" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G180" s="2">
-        <x:v>39940</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:7">
       <x:c r="A181" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B181" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F181" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G181" s="2">
-        <x:v>41455</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:7">
       <x:c r="A182" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B182" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F182" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G182" s="2">
-        <x:v>38322</x:v>
+        <x:v>43646</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:7">
       <x:c r="A183" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B183" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F183" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G183" s="2">
-        <x:v>38322</x:v>
+        <x:v>39940</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:7">
       <x:c r="A184" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B184" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F184" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G184" s="2">
-        <x:v>44377</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:7">
       <x:c r="A185" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B185" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F185" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G185" s="2">
-        <x:v>44377</x:v>
+        <x:v>38322</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:7">
       <x:c r="A186" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E186" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F186" s="1">
-        <x:v>-500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G186" s="2">
-        <x:v>40682</x:v>
+        <x:v>38322</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:7">
       <x:c r="A187" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B187" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E187" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F187" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G187" s="2">
-        <x:v>39318</x:v>
+        <x:v>44377</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:7">
       <x:c r="A188" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B188" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F188" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G188" s="2">
-        <x:v>45879</x:v>
+        <x:v>44377</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:7">
       <x:c r="A189" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B189" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F189" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G189" s="2">
-        <x:v>46112</x:v>
+        <x:v>40682</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
       <x:c r="A190" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B190" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C190" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F190" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G190" s="2">
-        <x:v>38075</x:v>
+        <x:v>39318</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
       <x:c r="A191" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="F191" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G191" s="2">
-        <x:v>38764</x:v>
+        <x:v>45879</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:7">
       <x:c r="A192" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B192" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="F192" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G192" s="2">
-        <x:v>43201</x:v>
+        <x:v>46112</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:7">
       <x:c r="A193" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B193" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C193" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F193" s="1">
-        <x:v>-250</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G193" s="2">
-        <x:v>43201</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:7">
@@ -6360,10 +6369,10 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="B194" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C194" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
         <x:v>423</x:v>
@@ -6372,15 +6381,15 @@
         <x:v>424</x:v>
       </x:c>
       <x:c r="F194" s="1">
-        <x:v>-200</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G194" s="2">
-        <x:v>43201</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:7">
       <x:c r="A195" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B195" s="1" t="s">
         <x:v>54</x:v>
@@ -6389,13 +6398,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E195" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F195" s="1">
-        <x:v>-100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G195" s="2">
         <x:v>43201</x:v>
@@ -6403,25 +6412,25 @@
     </x:row>
     <x:row r="196" spans="1:7">
       <x:c r="A196" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B196" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D196" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F196" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G196" s="2">
-        <x:v>39777</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:7">
@@ -6429,10 +6438,10 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B197" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C197" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D197" s="1" t="s">
         <x:v>426</x:v>
@@ -6441,199 +6450,199 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F197" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G197" s="2">
-        <x:v>43465</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:7">
       <x:c r="A198" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B198" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C198" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D198" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E198" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F198" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G198" s="2">
-        <x:v>39010</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:7">
       <x:c r="A199" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B199" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C199" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D199" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E199" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F199" s="1">
-        <x:v>-750</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G199" s="2">
-        <x:v>42783</x:v>
+        <x:v>39777</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
       <x:c r="A200" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B200" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="E200" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F200" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G200" s="2">
-        <x:v>45692</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
       <x:c r="A201" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B201" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C201" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F201" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G201" s="2">
-        <x:v>43799</x:v>
+        <x:v>39010</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C202" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D202" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E202" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F202" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G202" s="2">
-        <x:v>38075</x:v>
+        <x:v>42783</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
       <x:c r="A203" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B203" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C203" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D203" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F203" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G203" s="2">
-        <x:v>45698</x:v>
+        <x:v>45692</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
       <x:c r="A204" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B204" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C204" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D204" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E204" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F204" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G204" s="2">
-        <x:v>45665</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:7">
       <x:c r="A205" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B205" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C205" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D205" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E205" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F205" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G205" s="2">
-        <x:v>40724</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:7">
       <x:c r="A206" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B206" s="1" t="s">
         <x:v>34</x:v>
@@ -6642,136 +6651,136 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F206" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G206" s="2">
-        <x:v>46000</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:7">
       <x:c r="A207" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B207" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F207" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G207" s="2">
-        <x:v>43465</x:v>
+        <x:v>45665</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:7">
       <x:c r="A208" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B208" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D208" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="E208" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F208" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G208" s="2">
-        <x:v>44845</x:v>
+        <x:v>40724</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:7">
       <x:c r="A209" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B209" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C209" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D209" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E209" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F209" s="1">
-        <x:v>-300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G209" s="2">
-        <x:v>44645</x:v>
+        <x:v>46000</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:7">
       <x:c r="A210" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B210" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C210" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D210" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E210" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F210" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G210" s="2">
-        <x:v>41900</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:7">
       <x:c r="A211" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B211" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C211" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D211" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="E211" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F211" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G211" s="2">
-        <x:v>41813</x:v>
+        <x:v>44845</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:7">
       <x:c r="A212" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B212" s="1" t="s">
         <x:v>54</x:v>
@@ -6780,188 +6789,188 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D212" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E212" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F212" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G212" s="2">
-        <x:v>43573</x:v>
+        <x:v>44645</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:7">
       <x:c r="A213" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B213" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F213" s="1">
-        <x:v>-100</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G213" s="2">
-        <x:v>42236</x:v>
+        <x:v>41900</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:7">
       <x:c r="A214" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B214" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F214" s="1">
-        <x:v>-10</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G214" s="2">
-        <x:v>42236</x:v>
+        <x:v>41813</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:7">
       <x:c r="A215" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B215" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C215" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D215" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E215" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F215" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G215" s="2">
-        <x:v>44804</x:v>
+        <x:v>43573</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:7">
       <x:c r="A216" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B216" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C216" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D216" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="E216" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="F216" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G216" s="2">
-        <x:v>37787</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:7">
       <x:c r="A217" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B217" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C217" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D217" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="E217" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="F217" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G217" s="2">
-        <x:v>45551</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:7">
       <x:c r="A218" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B218" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C218" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D218" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="E218" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="F218" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G218" s="2">
-        <x:v>37736</x:v>
+        <x:v>44804</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:7">
       <x:c r="A219" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B219" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C219" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D219" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="E219" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="F219" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G219" s="2">
-        <x:v>41453</x:v>
+        <x:v>37787</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:7">
       <x:c r="A220" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B220" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C220" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D220" s="1" t="s">
         <x:v>481</x:v>
@@ -6970,10 +6979,10 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="F220" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G220" s="2">
-        <x:v>37736</x:v>
+        <x:v>45551</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:7">
@@ -6981,96 +6990,96 @@
         <x:v>483</x:v>
       </x:c>
       <x:c r="B221" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C221" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D221" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E221" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F221" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G221" s="2">
-        <x:v>41453</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:7">
       <x:c r="A222" s="1" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B222" s="1" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C222" s="1" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D222" s="1" t="s">
         <x:v>484</x:v>
       </x:c>
-      <x:c r="B222" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C222" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D222" s="1" t="s">
+      <x:c r="E222" s="1" t="s">
         <x:v>485</x:v>
       </x:c>
-      <x:c r="E222" s="1" t="s">
-        <x:v>486</x:v>
-      </x:c>
       <x:c r="F222" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G222" s="2">
-        <x:v>45077</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
       <x:c r="A223" s="1" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B223" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C223" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D223" s="1" t="s">
         <x:v>484</x:v>
       </x:c>
-      <x:c r="B223" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C223" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D223" s="1" t="s">
+      <x:c r="E223" s="1" t="s">
         <x:v>485</x:v>
       </x:c>
-      <x:c r="E223" s="1" t="s">
-        <x:v>486</x:v>
-      </x:c>
       <x:c r="F223" s="1">
-        <x:v>-950</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G223" s="2">
-        <x:v>45077</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
       <x:c r="A224" s="1" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B224" s="1" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C224" s="1" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D224" s="1" t="s">
         <x:v>484</x:v>
       </x:c>
-      <x:c r="B224" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C224" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D224" s="1" t="s">
+      <x:c r="E224" s="1" t="s">
         <x:v>485</x:v>
       </x:c>
-      <x:c r="E224" s="1" t="s">
-        <x:v>486</x:v>
-      </x:c>
       <x:c r="F224" s="1">
-        <x:v>-713</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G224" s="2">
-        <x:v>45077</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
       <x:c r="A225" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B225" s="1" t="s">
         <x:v>34</x:v>
@@ -7079,13 +7088,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D225" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E225" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F225" s="1">
-        <x:v>-475</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G225" s="2">
         <x:v>45077</x:v>
@@ -7093,7 +7102,7 @@
     </x:row>
     <x:row r="226" spans="1:7">
       <x:c r="A226" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B226" s="1" t="s">
         <x:v>34</x:v>
@@ -7102,13 +7111,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D226" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E226" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F226" s="1">
-        <x:v>-238</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G226" s="2">
         <x:v>45077</x:v>
@@ -7119,10 +7128,10 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B227" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C227" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D227" s="1" t="s">
         <x:v>488</x:v>
@@ -7131,55 +7140,124 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="F227" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G227" s="2">
-        <x:v>40178</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="228" spans="1:7">
       <x:c r="A228" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B228" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C228" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D228" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E228" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F228" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G228" s="2">
-        <x:v>39629</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="229" spans="1:7">
       <x:c r="A229" s="1" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B229" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C229" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D229" s="1" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="E229" s="1" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="F229" s="1">
+        <x:v>-238</x:v>
+      </x:c>
+      <x:c r="G229" s="2">
+        <x:v>45077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" spans="1:7">
+      <x:c r="A230" s="1" t="s">
         <x:v>490</x:v>
       </x:c>
-      <x:c r="B229" s="1" t="s">
+      <x:c r="B230" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C230" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D230" s="1" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="E230" s="1" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="F230" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G230" s="2">
+        <x:v>40178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:7">
+      <x:c r="A231" s="1" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B231" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C229" s="1" t="s">
+      <x:c r="C231" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D229" s="1" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="E229" s="1" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="F229" s="1">
+      <x:c r="D231" s="1" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="E231" s="1" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="F231" s="1">
         <x:v>-1000</x:v>
       </x:c>
-      <x:c r="G229" s="2">
+      <x:c r="G231" s="2">
+        <x:v>39629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" spans="1:7">
+      <x:c r="A232" s="1" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B232" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C232" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D232" s="1" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="E232" s="1" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="F232" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G232" s="2">
         <x:v>39660</x:v>
       </x:c>
     </x:row>
@@ -7199,7 +7277,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H165"/>
+  <x:dimension ref="A1:H166"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="9" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -7230,13 +7308,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -8146,7 +8224,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>527848</x:v>
+        <x:v>527857</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:8">
@@ -8790,13 +8868,13 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-350</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="H61" s="1">
-        <x:v>622244</x:v>
+        <x:v>397605</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:8">
@@ -8804,10 +8882,10 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
         <x:v>209</x:v>
@@ -8816,13 +8894,13 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>208</x:v>
       </x:c>
       <x:c r="H62" s="1">
-        <x:v>3000</x:v>
+        <x:v>622244</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:8">
@@ -8830,10 +8908,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
         <x:v>212</x:v>
@@ -8842,13 +8920,13 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>-270</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>211</x:v>
       </x:c>
       <x:c r="H63" s="1">
-        <x:v>13265</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:8">
@@ -8856,10 +8934,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
         <x:v>215</x:v>
@@ -8868,13 +8946,13 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-270</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>214</x:v>
       </x:c>
       <x:c r="H64" s="1">
-        <x:v>5000</x:v>
+        <x:v>13265</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:8">
@@ -8882,10 +8960,10 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
         <x:v>218</x:v>
@@ -8894,13 +8972,13 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>217</x:v>
       </x:c>
       <x:c r="H65" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:8">
@@ -8908,10 +8986,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
         <x:v>221</x:v>
@@ -8920,13 +8998,13 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>220</x:v>
       </x:c>
       <x:c r="H66" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:8">
@@ -8934,10 +9012,10 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
         <x:v>224</x:v>
@@ -8946,13 +9024,13 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>223</x:v>
       </x:c>
       <x:c r="H67" s="1">
-        <x:v>3461</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:8">
@@ -8960,10 +9038,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
         <x:v>227</x:v>
@@ -8972,13 +9050,13 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>-25</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="H68" s="1">
-        <x:v>38904</x:v>
+        <x:v>3461</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:8">
@@ -8986,10 +9064,10 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
         <x:v>230</x:v>
@@ -8998,13 +9076,13 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>229</x:v>
       </x:c>
       <x:c r="H69" s="1">
-        <x:v>51848</x:v>
+        <x:v>38904</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:8">
@@ -9030,7 +9108,7 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>31858</x:v>
+        <x:v>51848</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:8">
@@ -9038,10 +9116,10 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
         <x:v>236</x:v>
@@ -9050,13 +9128,13 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>235</x:v>
       </x:c>
       <x:c r="H71" s="1">
-        <x:v>0</x:v>
+        <x:v>31867</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:8">
@@ -9064,10 +9142,10 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
         <x:v>239</x:v>
@@ -9076,13 +9154,13 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>238</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>249783</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:8">
@@ -9090,36 +9168,36 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C73" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D73" s="1" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="C73" s="1" t="s">
+      <x:c r="E73" s="1" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="D73" s="1" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="E73" s="1" t="s">
-        <x:v>245</x:v>
-      </x:c>
       <x:c r="F73" s="1">
-        <x:v>-2800</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>241</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>0</x:v>
+        <x:v>249792</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:8">
       <x:c r="A74" s="1" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B74" s="1" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C74" s="1" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="B74" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C74" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
         <x:v>247</x:v>
@@ -9128,13 +9206,13 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2800</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="H74" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:8">
@@ -9142,10 +9220,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
         <x:v>250</x:v>
@@ -9154,13 +9232,13 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>249</x:v>
       </x:c>
       <x:c r="H75" s="1">
-        <x:v>222609</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:8">
@@ -9168,10 +9246,10 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
         <x:v>253</x:v>
@@ -9180,13 +9258,13 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>252</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>2000</x:v>
+        <x:v>229618</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -9194,10 +9272,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
         <x:v>256</x:v>
@@ -9206,13 +9284,13 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>-3400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>255</x:v>
       </x:c>
       <x:c r="H77" s="1">
-        <x:v>28982</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:8">
@@ -9220,10 +9298,10 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>259</x:v>
@@ -9232,13 +9310,13 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-3400</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>258</x:v>
       </x:c>
       <x:c r="H78" s="1">
-        <x:v>0</x:v>
+        <x:v>28982</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:8">
@@ -9246,10 +9324,10 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>262</x:v>
@@ -9258,13 +9336,13 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>261</x:v>
       </x:c>
       <x:c r="H79" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:8">
@@ -9272,10 +9350,10 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
         <x:v>265</x:v>
@@ -9284,13 +9362,13 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>264</x:v>
       </x:c>
       <x:c r="H80" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:8">
@@ -9298,10 +9376,10 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
         <x:v>268</x:v>
@@ -9316,7 +9394,7 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>65304</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:8">
@@ -9324,10 +9402,10 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
         <x:v>271</x:v>
@@ -9336,13 +9414,13 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
         <x:v>270</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>0</x:v>
+        <x:v>65313</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:8">
@@ -9350,10 +9428,10 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
         <x:v>274</x:v>
@@ -9362,13 +9440,13 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
         <x:v>273</x:v>
       </x:c>
       <x:c r="H83" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:8">
@@ -9376,10 +9454,10 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
         <x:v>277</x:v>
@@ -9388,13 +9466,13 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
         <x:v>276</x:v>
       </x:c>
       <x:c r="H84" s="1">
-        <x:v>4000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:8">
@@ -9402,10 +9480,10 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
         <x:v>280</x:v>
@@ -9414,13 +9492,13 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>-510</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>279</x:v>
       </x:c>
       <x:c r="H85" s="1">
-        <x:v>42500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:8">
@@ -9428,10 +9506,10 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
         <x:v>283</x:v>
@@ -9440,13 +9518,13 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-510</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
         <x:v>282</x:v>
       </x:c>
       <x:c r="H86" s="1">
-        <x:v>2000</x:v>
+        <x:v>42500</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:8">
@@ -9454,10 +9532,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
         <x:v>286</x:v>
@@ -9466,13 +9544,13 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>-475</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
         <x:v>285</x:v>
       </x:c>
       <x:c r="H87" s="1">
-        <x:v>131385</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:8">
@@ -9480,10 +9558,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
         <x:v>289</x:v>
@@ -9492,13 +9570,13 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>-250</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
         <x:v>288</x:v>
       </x:c>
       <x:c r="H88" s="1">
-        <x:v>69371</x:v>
+        <x:v>131385</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:8">
@@ -9506,10 +9584,10 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
         <x:v>292</x:v>
@@ -9518,13 +9596,13 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
         <x:v>291</x:v>
       </x:c>
       <x:c r="H89" s="1">
-        <x:v>500</x:v>
+        <x:v>69371</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:8">
@@ -9532,10 +9610,10 @@
         <x:v>294</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
         <x:v>295</x:v>
@@ -9544,13 +9622,13 @@
         <x:v>296</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
         <x:v>294</x:v>
       </x:c>
       <x:c r="H90" s="1">
-        <x:v>183610</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:8">
@@ -9570,13 +9648,13 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
         <x:v>297</x:v>
       </x:c>
       <x:c r="H91" s="1">
-        <x:v>111188</x:v>
+        <x:v>183618</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:8">
@@ -9584,10 +9662,10 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
         <x:v>301</x:v>
@@ -9596,13 +9674,13 @@
         <x:v>302</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
         <x:v>300</x:v>
       </x:c>
       <x:c r="H92" s="1">
-        <x:v>1000</x:v>
+        <x:v>111188</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:8">
@@ -9610,10 +9688,10 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
         <x:v>304</x:v>
@@ -9622,39 +9700,39 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
         <x:v>303</x:v>
       </x:c>
       <x:c r="H93" s="1">
-        <x:v>10000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:8">
       <x:c r="A94" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H94" s="1">
-        <x:v>1150</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:8">
@@ -9662,77 +9740,77 @@
         <x:v>306</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
         <x:v>306</x:v>
       </x:c>
       <x:c r="H95" s="1">
-        <x:v>10000</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:8">
       <x:c r="A96" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="H96" s="1">
-        <x:v>1150</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:8">
       <x:c r="A97" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B97" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C97" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D97" s="1" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="B97" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C97" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D97" s="1" t="s">
+      <x:c r="E97" s="1" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="E97" s="1" t="s">
+      <x:c r="F97" s="1">
+        <x:v>-1350</x:v>
+      </x:c>
+      <x:c r="G97" s="1" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="F97" s="1">
-        <x:v>-500</x:v>
-      </x:c>
-      <x:c r="G97" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
       <x:c r="H97" s="1">
-        <x:v>33320</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:8">
@@ -9740,10 +9818,10 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
         <x:v>311</x:v>
@@ -9752,13 +9830,13 @@
         <x:v>312</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
         <x:v>310</x:v>
       </x:c>
       <x:c r="H98" s="1">
-        <x:v>0</x:v>
+        <x:v>33320</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:8">
@@ -9766,10 +9844,10 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
         <x:v>314</x:v>
@@ -9778,13 +9856,13 @@
         <x:v>315</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
         <x:v>313</x:v>
       </x:c>
       <x:c r="H99" s="1">
-        <x:v>21095</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:8">
@@ -9792,10 +9870,10 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
         <x:v>317</x:v>
@@ -9804,13 +9882,13 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
         <x:v>316</x:v>
       </x:c>
       <x:c r="H100" s="1">
-        <x:v>0</x:v>
+        <x:v>21095</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:8">
@@ -9818,10 +9896,10 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
         <x:v>320</x:v>
@@ -9830,13 +9908,13 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>-1</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
         <x:v>319</x:v>
       </x:c>
       <x:c r="H101" s="1">
-        <x:v>26650</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:8">
@@ -9844,10 +9922,10 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
         <x:v>323</x:v>
@@ -9856,13 +9934,13 @@
         <x:v>324</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
         <x:v>322</x:v>
       </x:c>
       <x:c r="H102" s="1">
-        <x:v>5000</x:v>
+        <x:v>26650</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:8">
@@ -9870,16 +9948,16 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C103" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D103" s="1" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="C103" s="1" t="s">
+      <x:c r="E103" s="1" t="s">
         <x:v>327</x:v>
-      </x:c>
-      <x:c r="D103" s="1" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="E103" s="1" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="F103" s="1">
         <x:v>-5000</x:v>
@@ -9888,18 +9966,18 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="H103" s="1">
-        <x:v>12000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:8">
       <x:c r="A104" s="1" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B104" s="1" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="C104" s="1" t="s">
         <x:v>330</x:v>
-      </x:c>
-      <x:c r="B104" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C104" s="1" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
         <x:v>331</x:v>
@@ -9911,33 +9989,33 @@
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="H104" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:8">
       <x:c r="A105" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="H105" s="1">
         <x:v>0</x:v>
@@ -9948,36 +10026,36 @@
         <x:v>333</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C106" s="1" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D106" s="1" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="C106" s="1" t="s">
+      <x:c r="E106" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="D106" s="1" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="E106" s="1" t="s">
-        <x:v>337</x:v>
-      </x:c>
       <x:c r="F106" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
         <x:v>333</x:v>
       </x:c>
       <x:c r="H106" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:8">
       <x:c r="A107" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B107" s="1" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C107" s="1" t="s">
         <x:v>338</x:v>
-      </x:c>
-      <x:c r="B107" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C107" s="1" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
         <x:v>339</x:v>
@@ -9986,13 +10064,13 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-20</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="H107" s="1">
-        <x:v>14900</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:8">
@@ -10000,10 +10078,10 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
         <x:v>342</x:v>
@@ -10012,13 +10090,13 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="H108" s="1">
-        <x:v>5000</x:v>
+        <x:v>14900</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:8">
@@ -10026,10 +10104,10 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
         <x:v>345</x:v>
@@ -10038,13 +10116,13 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-19701</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
       <x:c r="H109" s="1">
-        <x:v>49967</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:8">
@@ -10064,13 +10142,13 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>-8456</x:v>
+        <x:v>-19701</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
         <x:v>347</x:v>
       </x:c>
       <x:c r="H110" s="1">
-        <x:v>162021</x:v>
+        <x:v>49967</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:8">
@@ -10084,10 +10162,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F111" s="1">
         <x:v>-8456</x:v>
@@ -10101,28 +10179,28 @@
     </x:row>
     <x:row r="112" spans="1:8">
       <x:c r="A112" s="1" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B112" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C112" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D112" s="1" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="B112" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C112" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D112" s="1" t="s">
+      <x:c r="E112" s="1" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="E112" s="1" t="s">
+      <x:c r="F112" s="1">
+        <x:v>-8456</x:v>
+      </x:c>
+      <x:c r="G112" s="1" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="F112" s="1">
-        <x:v>-800</x:v>
-      </x:c>
-      <x:c r="G112" s="1" t="s">
-        <x:v>351</x:v>
-      </x:c>
       <x:c r="H112" s="1">
-        <x:v>58679</x:v>
+        <x:v>162021</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:8">
@@ -10130,10 +10208,10 @@
         <x:v>354</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
         <x:v>355</x:v>
@@ -10142,13 +10220,13 @@
         <x:v>356</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
         <x:v>354</x:v>
       </x:c>
       <x:c r="H113" s="1">
-        <x:v>0</x:v>
+        <x:v>58679</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:8">
@@ -10156,10 +10234,10 @@
         <x:v>357</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
         <x:v>358</x:v>
@@ -10168,13 +10246,13 @@
         <x:v>359</x:v>
       </x:c>
       <x:c r="F114" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G114" s="1" t="s">
         <x:v>357</x:v>
       </x:c>
       <x:c r="H114" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:8">
@@ -10182,10 +10260,10 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
         <x:v>361</x:v>
@@ -10194,13 +10272,13 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="F115" s="1">
-        <x:v>-300</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G115" s="1" t="s">
         <x:v>360</x:v>
       </x:c>
       <x:c r="H115" s="1">
-        <x:v>36900</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:8">
@@ -10208,10 +10286,10 @@
         <x:v>363</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
         <x:v>364</x:v>
@@ -10220,13 +10298,13 @@
         <x:v>365</x:v>
       </x:c>
       <x:c r="F116" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G116" s="1" t="s">
         <x:v>363</x:v>
       </x:c>
       <x:c r="H116" s="1">
-        <x:v>0</x:v>
+        <x:v>36900</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:8">
@@ -10234,10 +10312,10 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
         <x:v>367</x:v>
@@ -10260,10 +10338,10 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
         <x:v>370</x:v>
@@ -10272,13 +10350,13 @@
         <x:v>371</x:v>
       </x:c>
       <x:c r="F118" s="1">
-        <x:v>-100</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G118" s="1" t="s">
         <x:v>369</x:v>
       </x:c>
       <x:c r="H118" s="1">
-        <x:v>58000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:8">
@@ -10286,10 +10364,10 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
         <x:v>373</x:v>
@@ -10298,13 +10376,13 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="F119" s="1">
-        <x:v>-9</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G119" s="1" t="s">
         <x:v>372</x:v>
       </x:c>
       <x:c r="H119" s="1">
-        <x:v>15349</x:v>
+        <x:v>58000</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:8">
@@ -10312,10 +10390,10 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
         <x:v>376</x:v>
@@ -10324,13 +10402,13 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-4955</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G120" s="1" t="s">
         <x:v>375</x:v>
       </x:c>
       <x:c r="H120" s="1">
-        <x:v>64475</x:v>
+        <x:v>15349</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:8">
@@ -10350,13 +10428,13 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="F121" s="1">
-        <x:v>-250</x:v>
+        <x:v>-4955</x:v>
       </x:c>
       <x:c r="G121" s="1" t="s">
         <x:v>378</x:v>
       </x:c>
       <x:c r="H121" s="1">
-        <x:v>42061</x:v>
+        <x:v>64475</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:8">
@@ -10364,48 +10442,48 @@
         <x:v>381</x:v>
       </x:c>
       <x:c r="B122" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E122" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F122" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G122" s="1" t="s">
         <x:v>381</x:v>
       </x:c>
       <x:c r="H122" s="1">
-        <x:v>0</x:v>
+        <x:v>42061</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:8">
       <x:c r="A123" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F123" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G123" s="1" t="s">
         <x:v>384</x:v>
-      </x:c>
-      <x:c r="F123" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G123" s="1" t="s">
-        <x:v>382</x:v>
       </x:c>
       <x:c r="H123" s="1">
         <x:v>0</x:v>
@@ -10416,10 +10494,10 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
         <x:v>386</x:v>
@@ -10428,13 +10506,13 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="F124" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G124" s="1" t="s">
         <x:v>385</x:v>
       </x:c>
       <x:c r="H124" s="1">
-        <x:v>7380</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:8">
@@ -10442,10 +10520,10 @@
         <x:v>388</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
         <x:v>389</x:v>
@@ -10460,7 +10538,7 @@
         <x:v>388</x:v>
       </x:c>
       <x:c r="H125" s="1">
-        <x:v>3000</x:v>
+        <x:v>7380</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:8">
@@ -10468,10 +10546,10 @@
         <x:v>391</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
         <x:v>392</x:v>
@@ -10480,13 +10558,13 @@
         <x:v>393</x:v>
       </x:c>
       <x:c r="F126" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G126" s="1" t="s">
         <x:v>391</x:v>
       </x:c>
       <x:c r="H126" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:8">
@@ -10506,13 +10584,13 @@
         <x:v>396</x:v>
       </x:c>
       <x:c r="F127" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G127" s="1" t="s">
         <x:v>394</x:v>
       </x:c>
       <x:c r="H127" s="1">
-        <x:v>2400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:8">
@@ -10520,10 +10598,10 @@
         <x:v>397</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
         <x:v>398</x:v>
@@ -10532,13 +10610,13 @@
         <x:v>399</x:v>
       </x:c>
       <x:c r="F128" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G128" s="1" t="s">
         <x:v>397</x:v>
       </x:c>
       <x:c r="H128" s="1">
-        <x:v>0</x:v>
+        <x:v>2400</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:8">
@@ -10558,13 +10636,13 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-250</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G129" s="1" t="s">
         <x:v>400</x:v>
       </x:c>
       <x:c r="H129" s="1">
-        <x:v>6727</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:8">
@@ -10572,10 +10650,10 @@
         <x:v>403</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
         <x:v>404</x:v>
@@ -10584,13 +10662,13 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>-7500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G130" s="1" t="s">
         <x:v>403</x:v>
       </x:c>
       <x:c r="H130" s="1">
-        <x:v>5000</x:v>
+        <x:v>6727</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:8">
@@ -10598,10 +10676,10 @@
         <x:v>406</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
         <x:v>407</x:v>
@@ -10610,13 +10688,13 @@
         <x:v>408</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>-500</x:v>
+        <x:v>-7500</x:v>
       </x:c>
       <x:c r="G131" s="1" t="s">
         <x:v>406</x:v>
       </x:c>
       <x:c r="H131" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:8">
@@ -10624,10 +10702,10 @@
         <x:v>409</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
         <x:v>410</x:v>
@@ -10636,13 +10714,13 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G132" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
       <x:c r="H132" s="1">
-        <x:v>2000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:8">
@@ -10650,10 +10728,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
         <x:v>413</x:v>
@@ -10662,13 +10740,13 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G133" s="1" t="s">
         <x:v>412</x:v>
       </x:c>
       <x:c r="H133" s="1">
-        <x:v>159727</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:8">
@@ -10688,13 +10766,13 @@
         <x:v>417</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G134" s="1" t="s">
         <x:v>415</x:v>
       </x:c>
       <x:c r="H134" s="1">
-        <x:v>53221</x:v>
+        <x:v>159727</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:8">
@@ -10702,30 +10780,30 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="F135" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G135" s="1" t="s">
         <x:v>418</x:v>
       </x:c>
       <x:c r="H135" s="1">
-        <x:v>0</x:v>
+        <x:v>53230</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:8">
       <x:c r="A136" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
         <x:v>39</x:v>
@@ -10734,16 +10812,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F136" s="1">
+        <x:v>-5000</x:v>
+      </x:c>
+      <x:c r="G136" s="1" t="s">
         <x:v>421</x:v>
-      </x:c>
-      <x:c r="F136" s="1">
-        <x:v>-1000</x:v>
-      </x:c>
-      <x:c r="G136" s="1" t="s">
-        <x:v>419</x:v>
       </x:c>
       <x:c r="H136" s="1">
         <x:v>0</x:v>
@@ -10754,10 +10832,10 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
         <x:v>423</x:v>
@@ -10766,7 +10844,7 @@
         <x:v>424</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G137" s="1" t="s">
         <x:v>422</x:v>
@@ -10777,28 +10855,28 @@
     </x:row>
     <x:row r="138" spans="1:8">
       <x:c r="A138" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-1550</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G138" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H138" s="1">
-        <x:v>193279</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:8">
@@ -10806,10 +10884,10 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
         <x:v>426</x:v>
@@ -10818,13 +10896,13 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1550</x:v>
       </x:c>
       <x:c r="G139" s="1" t="s">
         <x:v>425</x:v>
       </x:c>
       <x:c r="H139" s="1">
-        <x:v>0</x:v>
+        <x:v>193279</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:8">
@@ -10832,10 +10910,10 @@
         <x:v>428</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
         <x:v>429</x:v>
@@ -10858,10 +10936,10 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
         <x:v>432</x:v>
@@ -10870,13 +10948,13 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G141" s="1" t="s">
         <x:v>431</x:v>
       </x:c>
       <x:c r="H141" s="1">
-        <x:v>19596</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:8">
@@ -10896,13 +10974,13 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G142" s="1" t="s">
         <x:v>434</x:v>
       </x:c>
       <x:c r="H142" s="1">
-        <x:v>17260</x:v>
+        <x:v>19596</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:8">
@@ -10910,10 +10988,10 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
         <x:v>438</x:v>
@@ -10922,13 +11000,13 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
         <x:v>437</x:v>
       </x:c>
       <x:c r="H143" s="1">
-        <x:v>6150</x:v>
+        <x:v>17260</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:8">
@@ -10936,51 +11014,51 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B144" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
         <x:v>440</x:v>
       </x:c>
       <x:c r="H144" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:8">
       <x:c r="A145" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F145" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G145" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="H145" s="1">
-        <x:v>32943</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:8">
@@ -11006,7 +11084,7 @@
         <x:v>444</x:v>
       </x:c>
       <x:c r="H146" s="1">
-        <x:v>41676</x:v>
+        <x:v>32943</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:8">
@@ -11014,10 +11092,10 @@
         <x:v>447</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
         <x:v>448</x:v>
@@ -11026,13 +11104,13 @@
         <x:v>449</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
         <x:v>447</x:v>
       </x:c>
       <x:c r="H147" s="1">
-        <x:v>0</x:v>
+        <x:v>41676</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:8">
@@ -11040,10 +11118,10 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
         <x:v>451</x:v>
@@ -11052,13 +11130,13 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
         <x:v>450</x:v>
       </x:c>
       <x:c r="H148" s="1">
-        <x:v>84497</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:8">
@@ -11066,10 +11144,10 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B149" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
         <x:v>454</x:v>
@@ -11078,13 +11156,13 @@
         <x:v>455</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
         <x:v>453</x:v>
       </x:c>
       <x:c r="H149" s="1">
-        <x:v>0</x:v>
+        <x:v>84497</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:8">
@@ -11092,10 +11170,10 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
         <x:v>457</x:v>
@@ -11104,13 +11182,13 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
         <x:v>456</x:v>
       </x:c>
       <x:c r="H150" s="1">
-        <x:v>28400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:8">
@@ -11118,10 +11196,10 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
         <x:v>460</x:v>
@@ -11130,13 +11208,13 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
         <x:v>459</x:v>
       </x:c>
       <x:c r="H151" s="1">
-        <x:v>22566</x:v>
+        <x:v>28400</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:8">
@@ -11144,10 +11222,10 @@
         <x:v>462</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
         <x:v>463</x:v>
@@ -11156,39 +11234,39 @@
         <x:v>464</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
         <x:v>462</x:v>
       </x:c>
       <x:c r="H152" s="1">
-        <x:v>3750</x:v>
+        <x:v>22566</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:8">
       <x:c r="A153" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="H153" s="1">
-        <x:v>10000</x:v>
+        <x:v>3750</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:8">
@@ -11196,10 +11274,10 @@
         <x:v>465</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
         <x:v>466</x:v>
@@ -11208,13 +11286,13 @@
         <x:v>467</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
         <x:v>465</x:v>
       </x:c>
       <x:c r="H154" s="1">
-        <x:v>18414</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:8">
@@ -11234,13 +11312,13 @@
         <x:v>470</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>-110</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
         <x:v>468</x:v>
       </x:c>
       <x:c r="H155" s="1">
-        <x:v>5170</x:v>
+        <x:v>18414</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:8">
@@ -11248,10 +11326,10 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
         <x:v>472</x:v>
@@ -11260,13 +11338,13 @@
         <x:v>473</x:v>
       </x:c>
       <x:c r="F156" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-110</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
         <x:v>471</x:v>
       </x:c>
       <x:c r="H156" s="1">
-        <x:v>6000</x:v>
+        <x:v>5170</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:8">
@@ -11274,10 +11352,10 @@
         <x:v>474</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
         <x:v>475</x:v>
@@ -11292,7 +11370,7 @@
         <x:v>474</x:v>
       </x:c>
       <x:c r="H157" s="1">
-        <x:v>10972</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:8">
@@ -11300,10 +11378,10 @@
         <x:v>477</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
         <x:v>478</x:v>
@@ -11312,13 +11390,13 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="F158" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
         <x:v>477</x:v>
       </x:c>
       <x:c r="H158" s="1">
-        <x:v>57350</x:v>
+        <x:v>10972</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:8">
@@ -11326,10 +11404,10 @@
         <x:v>480</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
         <x:v>481</x:v>
@@ -11338,39 +11416,39 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="F159" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
         <x:v>480</x:v>
       </x:c>
       <x:c r="H159" s="1">
-        <x:v>2500</x:v>
+        <x:v>57350</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:8">
       <x:c r="A160" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F160" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="H160" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:8">
@@ -11378,77 +11456,77 @@
         <x:v>483</x:v>
       </x:c>
       <x:c r="B161" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F161" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
         <x:v>483</x:v>
       </x:c>
       <x:c r="H161" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:8">
       <x:c r="A162" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B162" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F162" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="H162" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:8">
       <x:c r="A163" s="1" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B163" s="1" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C163" s="1" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D163" s="1" t="s">
         <x:v>484</x:v>
       </x:c>
-      <x:c r="B163" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C163" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D163" s="1" t="s">
+      <x:c r="E163" s="1" t="s">
         <x:v>485</x:v>
       </x:c>
-      <x:c r="E163" s="1" t="s">
+      <x:c r="F163" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G163" s="1" t="s">
         <x:v>486</x:v>
       </x:c>
-      <x:c r="F163" s="1">
-        <x:v>-5131</x:v>
-      </x:c>
-      <x:c r="G163" s="1" t="s">
-        <x:v>484</x:v>
-      </x:c>
       <x:c r="H163" s="1">
-        <x:v>83966</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:8">
@@ -11456,10 +11534,10 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B164" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D164" s="1" t="s">
         <x:v>488</x:v>
@@ -11468,13 +11546,13 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="F164" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5131</x:v>
       </x:c>
       <x:c r="G164" s="1" t="s">
         <x:v>487</x:v>
       </x:c>
       <x:c r="H164" s="1">
-        <x:v>6000</x:v>
+        <x:v>83966</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:8">
@@ -11482,10 +11560,10 @@
         <x:v>490</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
         <x:v>491</x:v>
@@ -11500,6 +11578,32 @@
         <x:v>490</x:v>
       </x:c>
       <x:c r="H165" s="1">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:8">
+      <x:c r="A166" s="1" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B166" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C166" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D166" s="1" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="E166" s="1" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="F166" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G166" s="1" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="H166" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -9186,7 +9186,7 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>249792</x:v>
+        <x:v>291042</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:8">
@@ -9264,7 +9264,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>229618</x:v>
+        <x:v>229873</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -9420,7 +9420,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>65313</x:v>
+        <x:v>96316</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:8">
@@ -9654,7 +9654,7 @@
         <x:v>297</x:v>
       </x:c>
       <x:c r="H91" s="1">
-        <x:v>183618</x:v>
+        <x:v>183873</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:8">
@@ -10798,7 +10798,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="H135" s="1">
-        <x:v>53230</x:v>
+        <x:v>56230</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:8">

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -8068,7 +8068,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>5133</x:v>
+        <x:v>6885</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:8">

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -8224,7 +8224,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>527857</x:v>
+        <x:v>527860</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:8">
@@ -9134,7 +9134,7 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="H71" s="1">
-        <x:v>31867</x:v>
+        <x:v>32621</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:8">
@@ -9186,7 +9186,7 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>291042</x:v>
+        <x:v>306396</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:8">
@@ -9264,7 +9264,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>229873</x:v>
+        <x:v>265382</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -9420,7 +9420,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>96316</x:v>
+        <x:v>98832</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:8">
@@ -9654,7 +9654,7 @@
         <x:v>297</x:v>
       </x:c>
       <x:c r="H91" s="1">
-        <x:v>183873</x:v>
+        <x:v>185839</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:8">
@@ -10798,7 +10798,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="H135" s="1">
-        <x:v>56230</x:v>
+        <x:v>56234</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:8">

--- a/reports/pro-israel/pro-israel-refunds-report.xlsx
+++ b/reports/pro-israel/pro-israel-refunds-report.xlsx
@@ -1592,8 +1592,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G232" totalsRowShown="0">
-  <x:autoFilter ref="A1:G232"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G234" totalsRowShown="0">
+  <x:autoFilter ref="A1:G234"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_id" dataDxfId="0"/>
@@ -1912,7 +1912,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G232"/>
+  <x:dimension ref="A1:G234"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3859,7 +3859,7 @@
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
         <x:v>34</x:v>
@@ -3868,274 +3868,274 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-3500</x:v>
       </x:c>
       <x:c r="G85" s="2">
-        <x:v>45980</x:v>
+        <x:v>46205</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G86" s="2">
-        <x:v>38184</x:v>
+        <x:v>46205</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>-250</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G87" s="2">
-        <x:v>43410</x:v>
+        <x:v>45980</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>-20</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G88" s="2">
-        <x:v>43410</x:v>
+        <x:v>38184</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G89" s="2">
-        <x:v>42017</x:v>
+        <x:v>43410</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G90" s="2">
-        <x:v>38764</x:v>
+        <x:v>43410</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G91" s="2">
-        <x:v>41284</x:v>
+        <x:v>42017</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G92" s="2">
-        <x:v>44893</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>-25</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G93" s="2">
-        <x:v>41711</x:v>
+        <x:v>41284</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G94" s="2">
-        <x:v>45698</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="G95" s="2">
-        <x:v>45629</x:v>
+        <x:v>41711</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G96" s="2">
-        <x:v>39813</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
         <x:v>34</x:v>
@@ -4144,251 +4144,251 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F97" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G97" s="2">
-        <x:v>46044</x:v>
+        <x:v>45629</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>-2800</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G98" s="2">
-        <x:v>41893</x:v>
+        <x:v>39813</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G99" s="2">
-        <x:v>38717</x:v>
+        <x:v>46044</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2800</x:v>
       </x:c>
       <x:c r="G100" s="2">
-        <x:v>46051</x:v>
+        <x:v>41893</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G101" s="2">
-        <x:v>45617</x:v>
+        <x:v>38717</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G102" s="2">
-        <x:v>40602</x:v>
+        <x:v>46051</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F103" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G103" s="2">
-        <x:v>40602</x:v>
+        <x:v>45617</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G104" s="2">
-        <x:v>44727</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F105" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G105" s="2">
-        <x:v>38990</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="F106" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G106" s="2">
-        <x:v>38292</x:v>
+        <x:v>44727</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G107" s="2">
-        <x:v>45638</x:v>
+        <x:v>38990</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
         <x:v>74</x:v>
@@ -4397,108 +4397,108 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G108" s="2">
-        <x:v>39512</x:v>
+        <x:v>38292</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G109" s="2">
-        <x:v>45517</x:v>
+        <x:v>45638</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F110" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G110" s="2">
-        <x:v>40178</x:v>
+        <x:v>39512</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>-500</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G111" s="2">
-        <x:v>45533</x:v>
+        <x:v>45517</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>-9</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G112" s="2">
-        <x:v>45533</x:v>
+        <x:v>40178</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
@@ -4518,7 +4518,7 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>-1</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G113" s="2">
         <x:v>45533</x:v>
@@ -4526,30 +4526,30 @@
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F114" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G114" s="2">
-        <x:v>44893</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
         <x:v>34</x:v>
@@ -4558,182 +4558,182 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F115" s="1">
-        <x:v>-475</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G115" s="2">
-        <x:v>45077</x:v>
+        <x:v>45533</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F116" s="1">
-        <x:v>-250</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G116" s="2">
-        <x:v>43799</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F117" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G117" s="2">
-        <x:v>37855</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
       <x:c r="A118" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F118" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G118" s="2">
-        <x:v>45638</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
       <x:c r="A119" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F119" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G119" s="2">
-        <x:v>44716</x:v>
+        <x:v>37855</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7">
       <x:c r="A120" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G120" s="2">
-        <x:v>42004</x:v>
+        <x:v>45638</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
       <x:c r="A121" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F121" s="1">
-        <x:v>-1350</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G121" s="2">
-        <x:v>43167</x:v>
+        <x:v>44716</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7">
       <x:c r="A122" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B122" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E122" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F122" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G122" s="2">
-        <x:v>44893</x:v>
+        <x:v>42004</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:7">
       <x:c r="A123" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
         <x:v>90</x:v>
@@ -4756,7 +4756,7 @@
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
         <x:v>109</x:v>
@@ -4779,53 +4779,53 @@
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F125" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1350</x:v>
       </x:c>
       <x:c r="G125" s="2">
-        <x:v>40602</x:v>
+        <x:v>43167</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:7">
       <x:c r="A126" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F126" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G126" s="2">
-        <x:v>40422</x:v>
+        <x:v>44893</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7">
       <x:c r="A127" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
         <x:v>54</x:v>
@@ -4834,269 +4834,269 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F127" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G127" s="2">
-        <x:v>42818</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7">
       <x:c r="A128" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F128" s="1">
         <x:v>-2000</x:v>
       </x:c>
       <x:c r="G128" s="2">
-        <x:v>45107</x:v>
+        <x:v>40422</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
       <x:c r="A129" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>-1</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G129" s="2">
-        <x:v>45408</x:v>
+        <x:v>42818</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G130" s="2">
-        <x:v>43390</x:v>
+        <x:v>45107</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G131" s="2">
-        <x:v>43282</x:v>
+        <x:v>45408</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G132" s="2">
-        <x:v>44013</x:v>
+        <x:v>43390</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F133" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G133" s="2">
-        <x:v>44022</x:v>
+        <x:v>43282</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G134" s="2">
-        <x:v>41926</x:v>
+        <x:v>44013</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F135" s="1">
-        <x:v>-20</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G135" s="2">
-        <x:v>41698</x:v>
+        <x:v>44022</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:7">
       <x:c r="A136" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F136" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G136" s="2">
-        <x:v>45484</x:v>
+        <x:v>41926</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="G137" s="2">
-        <x:v>45957</x:v>
+        <x:v>41698</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>-1650</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G138" s="2">
-        <x:v>45959</x:v>
+        <x:v>45484</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:7">
@@ -5116,10 +5116,10 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>-1650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G139" s="2">
-        <x:v>45977</x:v>
+        <x:v>45957</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:7">
@@ -5139,10 +5139,10 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="G140" s="2">
-        <x:v>45977</x:v>
+        <x:v>45959</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
@@ -5162,7 +5162,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="G141" s="2">
         <x:v>45977</x:v>
@@ -5185,7 +5185,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>-36</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G142" s="2">
         <x:v>45977</x:v>
@@ -5208,7 +5208,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>-9</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G143" s="2">
         <x:v>45977</x:v>
@@ -5231,7 +5231,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F144" s="1">
-        <x:v>-3</x:v>
+        <x:v>-36</x:v>
       </x:c>
       <x:c r="G144" s="2">
         <x:v>45977</x:v>
@@ -5254,7 +5254,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F145" s="1">
-        <x:v>-2</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G145" s="2">
         <x:v>45977</x:v>
@@ -5277,7 +5277,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>-1</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="G146" s="2">
         <x:v>45977</x:v>
@@ -5300,7 +5300,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>-7000</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="G147" s="2">
         <x:v>45977</x:v>
@@ -5323,7 +5323,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>-3300</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="G148" s="2">
         <x:v>45977</x:v>
@@ -5346,7 +5346,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>-1800</x:v>
+        <x:v>-7000</x:v>
       </x:c>
       <x:c r="G149" s="2">
         <x:v>45977</x:v>
@@ -5369,15 +5369,15 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-3300</x:v>
       </x:c>
       <x:c r="G150" s="2">
-        <x:v>45980</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
         <x:v>34</x:v>
@@ -5386,21 +5386,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>-238</x:v>
+        <x:v>-1800</x:v>
       </x:c>
       <x:c r="G151" s="2">
-        <x:v>45077</x:v>
+        <x:v>45977</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
         <x:v>34</x:v>
@@ -5409,16 +5409,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>-1425</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G152" s="2">
-        <x:v>45077</x:v>
+        <x:v>45980</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:7">
@@ -5438,7 +5438,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>-950</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G153" s="2">
         <x:v>45077</x:v>
@@ -5461,7 +5461,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>-713</x:v>
+        <x:v>-1425</x:v>
       </x:c>
       <x:c r="G154" s="2">
         <x:v>45077</x:v>
@@ -5484,7 +5484,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>-475</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G155" s="2">
         <x:v>45077</x:v>
@@ -5507,7 +5507,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F156" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G156" s="2">
         <x:v>45077</x:v>
@@ -5530,7 +5530,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F157" s="1">
-        <x:v>-1900</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G157" s="2">
         <x:v>45077</x:v>
@@ -5538,7 +5538,7 @@
     </x:row>
     <x:row r="158" spans="1:7">
       <x:c r="A158" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
         <x:v>34</x:v>
@@ -5553,7 +5553,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F158" s="1">
-        <x:v>-1900</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G158" s="2">
         <x:v>45077</x:v>
@@ -5561,7 +5561,7 @@
     </x:row>
     <x:row r="159" spans="1:7">
       <x:c r="A159" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
         <x:v>34</x:v>
@@ -5576,7 +5576,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F159" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-1900</x:v>
       </x:c>
       <x:c r="G159" s="2">
         <x:v>45077</x:v>
@@ -5599,7 +5599,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F160" s="1">
-        <x:v>-475</x:v>
+        <x:v>-1900</x:v>
       </x:c>
       <x:c r="G160" s="2">
         <x:v>45077</x:v>
@@ -5622,7 +5622,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F161" s="1">
-        <x:v>-713</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G161" s="2">
         <x:v>45077</x:v>
@@ -5645,7 +5645,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F162" s="1">
-        <x:v>-950</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G162" s="2">
         <x:v>45077</x:v>
@@ -5668,7 +5668,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F163" s="1">
-        <x:v>-1425</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G163" s="2">
         <x:v>45077</x:v>
@@ -5691,7 +5691,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="F164" s="1">
-        <x:v>-238</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G164" s="2">
         <x:v>45077</x:v>
@@ -5699,191 +5699,191 @@
     </x:row>
     <x:row r="165" spans="1:7">
       <x:c r="A165" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F165" s="1">
-        <x:v>-800</x:v>
+        <x:v>-1425</x:v>
       </x:c>
       <x:c r="G165" s="2">
-        <x:v>40602</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:7">
       <x:c r="A166" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F166" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G166" s="2">
-        <x:v>37736</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:7">
       <x:c r="A167" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="F167" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="G167" s="2">
-        <x:v>39810</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:7">
       <x:c r="A168" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B168" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F168" s="1">
-        <x:v>-300</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G168" s="2">
-        <x:v>44767</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:7">
       <x:c r="A169" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B169" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F169" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G169" s="2">
-        <x:v>41010</x:v>
+        <x:v>39810</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:7">
       <x:c r="A170" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B170" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D170" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F170" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G170" s="2">
-        <x:v>41840</x:v>
+        <x:v>44767</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:7">
       <x:c r="A171" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B171" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D171" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F171" s="1">
-        <x:v>-100</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G171" s="2">
-        <x:v>40602</x:v>
+        <x:v>41010</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:7">
       <x:c r="A172" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B172" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F172" s="1">
-        <x:v>-9</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G172" s="2">
-        <x:v>45972</x:v>
+        <x:v>41840</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:7">
       <x:c r="A173" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
         <x:v>54</x:v>
@@ -5892,13 +5892,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F173" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G173" s="2">
         <x:v>40602</x:v>
@@ -5906,25 +5906,25 @@
     </x:row>
     <x:row r="174" spans="1:7">
       <x:c r="A174" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C174" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="F174" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="G174" s="2">
-        <x:v>40602</x:v>
+        <x:v>45972</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:7">
@@ -5944,7 +5944,7 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="F175" s="1">
-        <x:v>-500</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G175" s="2">
         <x:v>40602</x:v>
@@ -5967,7 +5967,7 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="F176" s="1">
-        <x:v>-50</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G176" s="2">
         <x:v>40602</x:v>
@@ -5990,7 +5990,7 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="F177" s="1">
-        <x:v>-5</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G177" s="2">
         <x:v>40602</x:v>
@@ -5998,7 +5998,7 @@
     </x:row>
     <x:row r="178" spans="1:7">
       <x:c r="A178" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B178" s="1" t="s">
         <x:v>54</x:v>
@@ -6007,13 +6007,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F178" s="1">
-        <x:v>-250</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="G178" s="2">
         <x:v>40602</x:v>
@@ -6021,416 +6021,416 @@
     </x:row>
     <x:row r="179" spans="1:7">
       <x:c r="A179" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B179" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F179" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="G179" s="2">
-        <x:v>38075</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:7">
       <x:c r="A180" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B180" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F180" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G180" s="2">
-        <x:v>41455</x:v>
+        <x:v>40602</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:7">
       <x:c r="A181" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B181" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F181" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G181" s="2">
-        <x:v>45698</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:7">
       <x:c r="A182" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B182" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F182" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G182" s="2">
-        <x:v>43646</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:7">
       <x:c r="A183" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B183" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F183" s="1">
-        <x:v>-1500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G183" s="2">
-        <x:v>39940</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:7">
       <x:c r="A184" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B184" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F184" s="1">
-        <x:v>-2400</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G184" s="2">
-        <x:v>41455</x:v>
+        <x:v>43646</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:7">
       <x:c r="A185" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B185" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F185" s="1">
-        <x:v>-500</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="G185" s="2">
-        <x:v>38322</x:v>
+        <x:v>39940</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:7">
       <x:c r="A186" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E186" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F186" s="1">
-        <x:v>-250</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="G186" s="2">
-        <x:v>38322</x:v>
+        <x:v>41455</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:7">
       <x:c r="A187" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B187" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E187" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F187" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G187" s="2">
-        <x:v>44377</x:v>
+        <x:v>38322</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:7">
       <x:c r="A188" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B188" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F188" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G188" s="2">
-        <x:v>44377</x:v>
+        <x:v>38322</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:7">
       <x:c r="A189" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B189" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F189" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G189" s="2">
-        <x:v>40682</x:v>
+        <x:v>44377</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
       <x:c r="A190" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B190" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C190" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F190" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G190" s="2">
-        <x:v>39318</x:v>
+        <x:v>44377</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
       <x:c r="A191" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F191" s="1">
         <x:v>-500</x:v>
       </x:c>
       <x:c r="G191" s="2">
-        <x:v>45879</x:v>
+        <x:v>40682</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:7">
       <x:c r="A192" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B192" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F192" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G192" s="2">
-        <x:v>46112</x:v>
+        <x:v>39318</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:7">
       <x:c r="A193" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B193" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C193" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="F193" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G193" s="2">
-        <x:v>38075</x:v>
+        <x:v>45879</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:7">
       <x:c r="A194" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B194" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C194" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="F194" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G194" s="2">
-        <x:v>38764</x:v>
+        <x:v>46112</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:7">
       <x:c r="A195" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B195" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C195" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E195" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F195" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G195" s="2">
-        <x:v>43201</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:7">
       <x:c r="A196" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B196" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D196" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F196" s="1">
-        <x:v>-250</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G196" s="2">
-        <x:v>43201</x:v>
+        <x:v>38764</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:7">
@@ -6450,7 +6450,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F197" s="1">
-        <x:v>-200</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G197" s="2">
         <x:v>43201</x:v>
@@ -6473,7 +6473,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F198" s="1">
-        <x:v>-100</x:v>
+        <x:v>-250</x:v>
       </x:c>
       <x:c r="G198" s="2">
         <x:v>43201</x:v>
@@ -6484,10 +6484,10 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B199" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C199" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D199" s="1" t="s">
         <x:v>426</x:v>
@@ -6496,222 +6496,222 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="F199" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="G199" s="2">
-        <x:v>39777</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
       <x:c r="A200" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B200" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E200" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F200" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G200" s="2">
-        <x:v>43465</x:v>
+        <x:v>43201</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
       <x:c r="A201" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B201" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C201" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F201" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G201" s="2">
-        <x:v>39010</x:v>
+        <x:v>39777</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C202" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D202" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="E202" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F202" s="1">
-        <x:v>-750</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G202" s="2">
-        <x:v>42783</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
       <x:c r="A203" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B203" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C203" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D203" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F203" s="1">
-        <x:v>-1400</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G203" s="2">
-        <x:v>45692</x:v>
+        <x:v>39010</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
       <x:c r="A204" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B204" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C204" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D204" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E204" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F204" s="1">
-        <x:v>-300</x:v>
+        <x:v>-750</x:v>
       </x:c>
       <x:c r="G204" s="2">
-        <x:v>43799</x:v>
+        <x:v>42783</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:7">
       <x:c r="A205" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B205" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C205" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D205" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E205" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F205" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1400</x:v>
       </x:c>
       <x:c r="G205" s="2">
-        <x:v>38075</x:v>
+        <x:v>45692</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:7">
       <x:c r="A206" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B206" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F206" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G206" s="2">
-        <x:v>45698</x:v>
+        <x:v>43799</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:7">
       <x:c r="A207" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B207" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F207" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G207" s="2">
-        <x:v>45665</x:v>
+        <x:v>38075</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:7">
       <x:c r="A208" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B208" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D208" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E208" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F208" s="1">
-        <x:v>-500</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G208" s="2">
-        <x:v>40724</x:v>
+        <x:v>45698</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:7">
       <x:c r="A209" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B209" s="1" t="s">
         <x:v>34</x:v>
@@ -6720,21 +6720,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D209" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="E209" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F209" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G209" s="2">
-        <x:v>46000</x:v>
+        <x:v>45665</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:7">
       <x:c r="A210" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B210" s="1" t="s">
         <x:v>109</x:v>
@@ -6743,21 +6743,21 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="D210" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="E210" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F210" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-500</x:v>
       </x:c>
       <x:c r="G210" s="2">
-        <x:v>43465</x:v>
+        <x:v>40724</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:7">
       <x:c r="A211" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B211" s="1" t="s">
         <x:v>34</x:v>
@@ -6766,136 +6766,136 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D211" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E211" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F211" s="1">
         <x:v>-5000</x:v>
       </x:c>
       <x:c r="G211" s="2">
-        <x:v>44845</x:v>
+        <x:v>46000</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:7">
       <x:c r="A212" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B212" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C212" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D212" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E212" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F212" s="1">
-        <x:v>-300</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G212" s="2">
-        <x:v>44645</x:v>
+        <x:v>43465</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:7">
       <x:c r="A213" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B213" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D213" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="E213" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F213" s="1">
-        <x:v>-3000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G213" s="2">
-        <x:v>41900</x:v>
+        <x:v>44845</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:7">
       <x:c r="A214" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B214" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D214" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E214" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F214" s="1">
-        <x:v>-2500</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="G214" s="2">
-        <x:v>41813</x:v>
+        <x:v>44645</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:7">
       <x:c r="A215" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B215" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C215" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D215" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E215" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F215" s="1">
-        <x:v>-6250</x:v>
+        <x:v>-3000</x:v>
       </x:c>
       <x:c r="G215" s="2">
-        <x:v>43573</x:v>
+        <x:v>41900</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:7">
       <x:c r="A216" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B216" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C216" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D216" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E216" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F216" s="1">
-        <x:v>-100</x:v>
+        <x:v>-2500</x:v>
       </x:c>
       <x:c r="G216" s="2">
-        <x:v>42236</x:v>
+        <x:v>41813</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:7">
       <x:c r="A217" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B217" s="1" t="s">
         <x:v>54</x:v>
@@ -6904,67 +6904,67 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D217" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E217" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F217" s="1">
-        <x:v>-10</x:v>
+        <x:v>-6250</x:v>
       </x:c>
       <x:c r="G217" s="2">
-        <x:v>42236</x:v>
+        <x:v>43573</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:7">
       <x:c r="A218" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B218" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C218" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D218" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="E218" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="F218" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="G218" s="2">
-        <x:v>44804</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:7">
       <x:c r="A219" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B219" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C219" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D219" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="E219" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="F219" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="G219" s="2">
-        <x:v>37787</x:v>
+        <x:v>42236</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:7">
       <x:c r="A220" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B220" s="1" t="s">
         <x:v>34</x:v>
@@ -6973,67 +6973,67 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D220" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="E220" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="F220" s="1">
-        <x:v>-5000</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G220" s="2">
-        <x:v>45551</x:v>
+        <x:v>44804</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:7">
       <x:c r="A221" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B221" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C221" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D221" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="E221" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="F221" s="1">
         <x:v>-1000</x:v>
       </x:c>
       <x:c r="G221" s="2">
-        <x:v>37736</x:v>
+        <x:v>37787</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:7">
       <x:c r="A222" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B222" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C222" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D222" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E222" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F222" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-5000</x:v>
       </x:c>
       <x:c r="G222" s="2">
-        <x:v>41453</x:v>
+        <x:v>45551</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
       <x:c r="A223" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B223" s="1" t="s">
         <x:v>39</x:v>
@@ -7056,7 +7056,7 @@
     </x:row>
     <x:row r="224" spans="1:7">
       <x:c r="A224" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B224" s="1" t="s">
         <x:v>337</x:v>
@@ -7079,48 +7079,48 @@
     </x:row>
     <x:row r="225" spans="1:7">
       <x:c r="A225" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B225" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C225" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D225" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E225" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F225" s="1">
-        <x:v>-2755</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="G225" s="2">
-        <x:v>45077</x:v>
+        <x:v>37736</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:7">
       <x:c r="A226" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B226" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C226" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="D226" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E226" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F226" s="1">
-        <x:v>-950</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="G226" s="2">
-        <x:v>45077</x:v>
+        <x:v>41453</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
@@ -7140,7 +7140,7 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="F227" s="1">
-        <x:v>-713</x:v>
+        <x:v>-2755</x:v>
       </x:c>
       <x:c r="G227" s="2">
         <x:v>45077</x:v>
@@ -7163,7 +7163,7 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="F228" s="1">
-        <x:v>-475</x:v>
+        <x:v>-950</x:v>
       </x:c>
       <x:c r="G228" s="2">
         <x:v>45077</x:v>
@@ -7186,7 +7186,7 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="F229" s="1">
-        <x:v>-238</x:v>
+        <x:v>-713</x:v>
       </x:c>
       <x:c r="G229" s="2">
         <x:v>45077</x:v>
@@ -7194,70 +7194,116 @@
     </x:row>
     <x:row r="230" spans="1:7">
       <x:c r="A230" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B230" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C230" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D230" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E230" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F230" s="1">
-        <x:v>-2000</x:v>
+        <x:v>-475</x:v>
       </x:c>
       <x:c r="G230" s="2">
-        <x:v>40178</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="231" spans="1:7">
       <x:c r="A231" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B231" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C231" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D231" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E231" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F231" s="1">
-        <x:v>-1000</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="G231" s="2">
-        <x:v>39629</x:v>
+        <x:v>45077</x:v>
       </x:c>
     </x:row>
     <x:row r="232" spans="1:7">
       <x:c r="A232" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B232" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C232" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D232" s="1" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="E232" s="1" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="F232" s="1">
+        <x:v>-2000</x:v>
+      </x:c>
+      <x:c r="G232" s="2">
+        <x:v>40178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:7">
+      <x:c r="A233" s="1" t="s">
         <x:v>493</x:v>
       </x:c>
-      <x:c r="B232" s="1" t="s">
+      <x:c r="B233" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C232" s="1" t="s">
+      <x:c r="C233" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D232" s="1" t="s">
+      <x:c r="D233" s="1" t="s">
         <x:v>494</x:v>
       </x:c>
-      <x:c r="E232" s="1" t="s">
+      <x:c r="E233" s="1" t="s">
         <x:v>495</x:v>
       </x:c>
-      <x:c r="F232" s="1">
+      <x:c r="F233" s="1">
         <x:v>-1000</x:v>
       </x:c>
-      <x:c r="G232" s="2">
+      <x:c r="G233" s="2">
+        <x:v>39629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:7">
+      <x:c r="A234" s="1" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B234" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C234" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D234" s="1" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="E234" s="1" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="F234" s="1">
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="G234" s="2">
         <x:v>39660</x:v>
       </x:c>
     </x:row>
@@ -8868,13 +8914,13 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>-350</x:v>
+        <x:v>-5350</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>205</x:v>
       </x:c>
       <x:c r="H61" s="1">
-        <x:v>397605</x:v>
+        <x:v>392605</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:8">
@@ -9134,7 +9180,7 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="H71" s="1">
-        <x:v>32621</x:v>
+        <x:v>49121</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:8">
@@ -9264,7 +9310,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>265382</x:v>
+        <x:v>287517</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:8">
@@ -9420,7 +9466,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>98832</x:v>
+        <x:v>100382</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:8">
@@ -11266,7 +11312,7 @@
         <x:v>465</x:v>
       </x:c>
       <x:c r="H153" s="1">
-        <x:v>3750</x:v>
+        <x:v>8750</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:8">
